--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -466,385 +466,385 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -20,587 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-1956622</v>
+        <v>5643449</v>
       </c>
       <c r="E2" t="n">
-        <v>10214227</v>
+        <v>27960674</v>
       </c>
       <c r="F2" t="n">
-        <v>34007934</v>
+        <v>-3389805</v>
       </c>
       <c r="G2" t="n">
-        <v>39976020</v>
+        <v>17197528</v>
       </c>
       <c r="H2" t="n">
-        <v>-20002881</v>
+        <v>58584617</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -33,680 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-19911926</v>
+        <v>-44426223</v>
       </c>
       <c r="E3" t="n">
-        <v>10246775</v>
+        <v>45227120</v>
       </c>
       <c r="F3" t="n">
-        <v>-35054452</v>
+        <v>-5173895</v>
       </c>
       <c r="G3" t="n">
-        <v>-28231647</v>
+        <v>28506329</v>
       </c>
       <c r="H3" t="n">
-        <v>1993824</v>
+        <v>26260053</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -11,070 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>26025516</v>
+        <v>-1028944</v>
       </c>
       <c r="E4" t="n">
-        <v>30496334</v>
+        <v>-1956622</v>
       </c>
       <c r="F4" t="n">
-        <v>40857502</v>
+        <v>28783401</v>
       </c>
       <c r="G4" t="n">
-        <v>51927884</v>
+        <v>34007934</v>
       </c>
       <c r="H4" t="n">
-        <v>-28925938</v>
+        <v>-20959708</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -14,829 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -9,662 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-29474185</v>
+        <v>7661571</v>
       </c>
       <c r="E5" t="n">
-        <v>-16437846</v>
+        <v>26025516</v>
       </c>
       <c r="F5" t="n">
-        <v>-18531211</v>
+        <v>31195069</v>
       </c>
       <c r="G5" t="n">
-        <v>-3702035</v>
+        <v>40857502</v>
       </c>
       <c r="H5" t="n">
-        <v>61139440</v>
+        <v>-36400672</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -10,309 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>8877774</v>
+        <v>-83197181</v>
       </c>
       <c r="E6" t="n">
-        <v>19013989</v>
+        <v>-80785282</v>
       </c>
       <c r="F6" t="n">
-        <v>9264250</v>
+        <v>-114097650</v>
       </c>
       <c r="G6" t="n">
-        <v>14491033</v>
+        <v>-103788976</v>
       </c>
       <c r="H6" t="n">
-        <v>-134081343</v>
+        <v>138941692</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 11,488 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-1858027</v>
+        <v>-18026110</v>
       </c>
       <c r="E7" t="n">
-        <v>-2328594</v>
+        <v>-29474185</v>
       </c>
       <c r="F7" t="n">
-        <v>14987241</v>
+        <v>-7043631</v>
       </c>
       <c r="G7" t="n">
-        <v>14518305</v>
+        <v>-18531211</v>
       </c>
       <c r="H7" t="n">
-        <v>23973854</v>
+        <v>71929596</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 9,216 千)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2289845</v>
+        <v>-17122734</v>
       </c>
       <c r="E8" t="n">
-        <v>1167329</v>
+        <v>-19911926</v>
       </c>
       <c r="F8" t="n">
-        <v>-19450013</v>
+        <v>-25838539</v>
       </c>
       <c r="G8" t="n">
-        <v>-27012390</v>
+        <v>-35054452</v>
       </c>
       <c r="H8" t="n">
-        <v>-66225179</v>
+        <v>45672103</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-80785282</v>
+        <v>-155839</v>
       </c>
       <c r="E9" t="n">
-        <v>-60119017</v>
+        <v>108230</v>
       </c>
       <c r="F9" t="n">
-        <v>-103788976</v>
+        <v>9445037</v>
       </c>
       <c r="G9" t="n">
-        <v>-107603778</v>
+        <v>9571239</v>
       </c>
       <c r="H9" t="n">
-        <v>131108443</v>
+        <v>11818537</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-12413589</v>
+        <v>3334681</v>
       </c>
       <c r="E10" t="n">
-        <v>-6937120</v>
+        <v>2289845</v>
       </c>
       <c r="F10" t="n">
-        <v>-12240223</v>
+        <v>-14881883</v>
       </c>
       <c r="G10" t="n">
-        <v>-12919781</v>
+        <v>-19450013</v>
       </c>
       <c r="H10" t="n">
-        <v>75614325</v>
+        <v>-64954455</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-96513</v>
+        <v>-1600522</v>
       </c>
       <c r="E11" t="n">
-        <v>1252892</v>
+        <v>-12413589</v>
       </c>
       <c r="F11" t="n">
-        <v>1352310</v>
+        <v>-9998157</v>
       </c>
       <c r="G11" t="n">
-        <v>3164534</v>
+        <v>-12240223</v>
       </c>
       <c r="H11" t="n">
-        <v>10457964</v>
+        <v>64294448</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 24,163 千)</t>
+          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -15,633 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>8196467</v>
+        <v>-18448562</v>
       </c>
       <c r="E12" t="n">
-        <v>-2309475</v>
+        <v>8877774</v>
       </c>
       <c r="F12" t="n">
-        <v>76309054</v>
+        <v>-6368431</v>
       </c>
       <c r="G12" t="n">
-        <v>52146302</v>
+        <v>9264250</v>
       </c>
       <c r="H12" t="n">
-        <v>526131776</v>
+        <v>-149333724</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
@@ -863,19 +863,19 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
+        <v>-4606790</v>
+      </c>
+      <c r="E13" t="n">
         <v>-316461</v>
       </c>
-      <c r="E13" t="n">
-        <v>12359</v>
-      </c>
       <c r="F13" t="n">
+        <v>371360</v>
+      </c>
+      <c r="G13" t="n">
         <v>1492025</v>
       </c>
-      <c r="G13" t="n">
-        <v>3386702</v>
-      </c>
       <c r="H13" t="n">
-        <v>10847044</v>
+        <v>12702008</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -886,175 +886,175 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📈 20d 巨變(加碼 16,703 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-5641323</v>
+        <v>3043389</v>
       </c>
       <c r="E14" t="n">
-        <v>18470978</v>
+        <v>1754411</v>
       </c>
       <c r="F14" t="n">
-        <v>-26946699</v>
+        <v>-986949</v>
       </c>
       <c r="G14" t="n">
-        <v>-43649480</v>
+        <v>-2159820</v>
       </c>
       <c r="H14" t="n">
-        <v>-69358463</v>
+        <v>-10647712</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>1754411</v>
+        <v>593705</v>
       </c>
       <c r="E15" t="n">
-        <v>959066</v>
+        <v>-1858027</v>
       </c>
       <c r="F15" t="n">
-        <v>-2159820</v>
+        <v>15235938</v>
       </c>
       <c r="G15" t="n">
-        <v>-3144835</v>
+        <v>14987241</v>
       </c>
       <c r="H15" t="n">
-        <v>-15843684</v>
+        <v>23098720</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1661861</v>
+        <v>539018</v>
       </c>
       <c r="E16" t="n">
-        <v>-399669</v>
+        <v>-611183</v>
       </c>
       <c r="F16" t="n">
-        <v>-542475</v>
+        <v>-8796536</v>
       </c>
       <c r="G16" t="n">
-        <v>-3245178</v>
+        <v>-9742886</v>
       </c>
       <c r="H16" t="n">
-        <v>-9498920</v>
+        <v>-7787687</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14,199 千)</t>
+          <t>📉 20d 巨變(減碼 -22,494 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25199166</v>
+        <v>13308687</v>
       </c>
       <c r="E17" t="n">
-        <v>16846399</v>
+        <v>8196467</v>
       </c>
       <c r="F17" t="n">
-        <v>26962211</v>
+        <v>53814945</v>
       </c>
       <c r="G17" t="n">
-        <v>12762927</v>
+        <v>76309054</v>
       </c>
       <c r="H17" t="n">
-        <v>52599333</v>
+        <v>567202558</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -87,069 千)</t>
+          <t>📈 20d 巨變(加碼 13,336 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>45227120</v>
+        <v>36088567</v>
       </c>
       <c r="E18" t="n">
-        <v>81759531</v>
+        <v>25199166</v>
       </c>
       <c r="F18" t="n">
-        <v>28506329</v>
+        <v>40297762</v>
       </c>
       <c r="G18" t="n">
-        <v>115574939</v>
+        <v>26962211</v>
       </c>
       <c r="H18" t="n">
-        <v>3318165</v>
+        <v>92307108</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -20,587 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -8,917 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
+        <v>-35204437</v>
+      </c>
+      <c r="E2" t="n">
         <v>5643449</v>
       </c>
-      <c r="E2" t="n">
-        <v>27960674</v>
-      </c>
       <c r="F2" t="n">
+        <v>-12306613</v>
+      </c>
+      <c r="G2" t="n">
         <v>-3389805</v>
       </c>
-      <c r="G2" t="n">
-        <v>17197528</v>
-      </c>
       <c r="H2" t="n">
-        <v>58584617</v>
+        <v>45807391</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,558 +501,453 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -33,680 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-44426223</v>
+        <v>13079639</v>
       </c>
       <c r="E3" t="n">
-        <v>45227120</v>
+        <v>-1028944</v>
       </c>
       <c r="F3" t="n">
-        <v>-5173895</v>
+        <v>29016789</v>
       </c>
       <c r="G3" t="n">
-        <v>28506329</v>
+        <v>28783401</v>
       </c>
       <c r="H3" t="n">
-        <v>26260053</v>
+        <v>-19077156</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,785 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-1028944</v>
+        <v>-1867365</v>
       </c>
       <c r="E4" t="n">
-        <v>-1956622</v>
+        <v>-1600522</v>
       </c>
       <c r="F4" t="n">
-        <v>28783401</v>
+        <v>-22783426</v>
       </c>
       <c r="G4" t="n">
-        <v>34007934</v>
+        <v>-9998157</v>
       </c>
       <c r="H4" t="n">
-        <v>-20959708</v>
+        <v>57916547</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -9,662 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>7661571</v>
+        <v>4101197</v>
       </c>
       <c r="E5" t="n">
-        <v>26025516</v>
+        <v>3334681</v>
       </c>
       <c r="F5" t="n">
-        <v>31195069</v>
+        <v>-13701406</v>
       </c>
       <c r="G5" t="n">
-        <v>40857502</v>
+        <v>-14881883</v>
       </c>
       <c r="H5" t="n">
-        <v>-36400672</v>
+        <v>-63727582</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -10,309 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-83197181</v>
+        <v>-7457376</v>
       </c>
       <c r="E6" t="n">
-        <v>-80785282</v>
+        <v>-4606790</v>
       </c>
       <c r="F6" t="n">
-        <v>-114097650</v>
+        <v>2302769</v>
       </c>
       <c r="G6" t="n">
-        <v>-103788976</v>
+        <v>371360</v>
       </c>
       <c r="H6" t="n">
-        <v>138941692</v>
+        <v>10565757</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 11,488 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-18026110</v>
+        <v>419818</v>
       </c>
       <c r="E7" t="n">
-        <v>-29474185</v>
+        <v>7661571</v>
       </c>
       <c r="F7" t="n">
-        <v>-7043631</v>
+        <v>25734731</v>
       </c>
       <c r="G7" t="n">
-        <v>-18531211</v>
+        <v>31195069</v>
       </c>
       <c r="H7" t="n">
-        <v>71929596</v>
+        <v>-41781720</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 9,216 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-17122734</v>
+        <v>-38830336</v>
       </c>
       <c r="E8" t="n">
-        <v>-19911926</v>
+        <v>-83197181</v>
       </c>
       <c r="F8" t="n">
-        <v>-25838539</v>
+        <v>-108275409</v>
       </c>
       <c r="G8" t="n">
-        <v>-35054452</v>
+        <v>-114097650</v>
       </c>
       <c r="H8" t="n">
-        <v>45672103</v>
+        <v>145615415</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-155839</v>
+        <v>-1386713</v>
       </c>
       <c r="E9" t="n">
-        <v>108230</v>
+        <v>-18026110</v>
       </c>
       <c r="F9" t="n">
-        <v>9445037</v>
+        <v>-5111730</v>
       </c>
       <c r="G9" t="n">
-        <v>9571239</v>
+        <v>-7043631</v>
       </c>
       <c r="H9" t="n">
-        <v>11818537</v>
+        <v>73856727</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>3334681</v>
+        <v>-6226405</v>
       </c>
       <c r="E10" t="n">
-        <v>2289845</v>
+        <v>-17122734</v>
       </c>
       <c r="F10" t="n">
-        <v>-14881883</v>
+        <v>-20371886</v>
       </c>
       <c r="G10" t="n">
-        <v>-19450013</v>
+        <v>-25838539</v>
       </c>
       <c r="H10" t="n">
-        <v>-64954455</v>
+        <v>68526450</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-1600522</v>
+        <v>216411</v>
       </c>
       <c r="E11" t="n">
-        <v>-12413589</v>
+        <v>499335</v>
       </c>
       <c r="F11" t="n">
-        <v>-9998157</v>
+        <v>-3227832</v>
       </c>
       <c r="G11" t="n">
-        <v>-12240223</v>
+        <v>-2659816</v>
       </c>
       <c r="H11" t="n">
-        <v>64294448</v>
+        <v>-13092049</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -15,633 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-18448562</v>
+        <v>2098171</v>
       </c>
       <c r="E12" t="n">
-        <v>8877774</v>
+        <v>1555751</v>
       </c>
       <c r="F12" t="n">
-        <v>-6368431</v>
+        <v>-796018</v>
       </c>
       <c r="G12" t="n">
-        <v>9264250</v>
+        <v>368137</v>
       </c>
       <c r="H12" t="n">
-        <v>-149333724</v>
+        <v>-10554380</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-4606790</v>
+        <v>919078</v>
       </c>
       <c r="E13" t="n">
-        <v>-316461</v>
+        <v>539018</v>
       </c>
       <c r="F13" t="n">
-        <v>371360</v>
+        <v>-7611331</v>
       </c>
       <c r="G13" t="n">
-        <v>1492025</v>
+        <v>-8796536</v>
       </c>
       <c r="H13" t="n">
-        <v>12702008</v>
+        <v>-8072390</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>📉 20d 巨變(減碼 -16,146 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3043389</v>
+        <v>3200128</v>
       </c>
       <c r="E14" t="n">
-        <v>1754411</v>
+        <v>13308687</v>
       </c>
       <c r="F14" t="n">
-        <v>-986949</v>
+        <v>37669057</v>
       </c>
       <c r="G14" t="n">
-        <v>-2159820</v>
+        <v>53814945</v>
       </c>
       <c r="H14" t="n">
-        <v>-10647712</v>
+        <v>568590569</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>📈 20d 巨變(加碼 13,841 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>593705</v>
+        <v>42107380</v>
       </c>
       <c r="E15" t="n">
-        <v>-1858027</v>
+        <v>36088567</v>
       </c>
       <c r="F15" t="n">
-        <v>15235938</v>
+        <v>54138286</v>
       </c>
       <c r="G15" t="n">
-        <v>14987241</v>
+        <v>40297762</v>
       </c>
       <c r="H15" t="n">
-        <v>23098720</v>
+        <v>114503675</v>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>建準</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>539018</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-611183</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-8796536</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-9742886</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-7787687</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -22,494 千)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>13308687</v>
-      </c>
-      <c r="E17" t="n">
-        <v>8196467</v>
-      </c>
-      <c r="F17" t="n">
-        <v>53814945</v>
-      </c>
-      <c r="G17" t="n">
-        <v>76309054</v>
-      </c>
-      <c r="H17" t="n">
-        <v>567202558</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 13,336 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>36088567</v>
-      </c>
-      <c r="E18" t="n">
-        <v>25199166</v>
-      </c>
-      <c r="F18" t="n">
-        <v>40297762</v>
-      </c>
-      <c r="G18" t="n">
-        <v>26962211</v>
-      </c>
-      <c r="H18" t="n">
-        <v>92307108</v>
-      </c>
-      <c r="I18" t="inlineStr">
         <is>
           <t>中華電</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,35 +466,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -8,917 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>-35204437</v>
+        <v>-5780922</v>
       </c>
       <c r="E2" t="n">
-        <v>5643449</v>
+        <v>419818</v>
       </c>
       <c r="F2" t="n">
-        <v>-12306613</v>
+        <v>26017364</v>
       </c>
       <c r="G2" t="n">
-        <v>-3389805</v>
+        <v>25734731</v>
       </c>
       <c r="H2" t="n">
-        <v>45807391</v>
+        <v>-20837915</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
@@ -506,26 +506,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
+        <v>-176747</v>
+      </c>
+      <c r="E3" t="n">
         <v>13079639</v>
       </c>
-      <c r="E3" t="n">
-        <v>-1028944</v>
-      </c>
       <c r="F3" t="n">
+        <v>25631958</v>
+      </c>
+      <c r="G3" t="n">
         <v>29016789</v>
       </c>
-      <c r="G3" t="n">
-        <v>28783401</v>
-      </c>
       <c r="H3" t="n">
-        <v>-19077156</v>
+        <v>-20464641</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -536,420 +536,490 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,785 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-1867365</v>
+        <v>-3056869</v>
       </c>
       <c r="E4" t="n">
-        <v>-1600522</v>
+        <v>3200128</v>
       </c>
       <c r="F4" t="n">
-        <v>-22783426</v>
+        <v>31878739</v>
       </c>
       <c r="G4" t="n">
-        <v>-9998157</v>
+        <v>37669057</v>
       </c>
       <c r="H4" t="n">
-        <v>57916547</v>
+        <v>570598436</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 20,255 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>4101197</v>
+        <v>-24297060</v>
       </c>
       <c r="E5" t="n">
-        <v>3334681</v>
+        <v>-35204437</v>
       </c>
       <c r="F5" t="n">
-        <v>-13701406</v>
+        <v>7948555</v>
       </c>
       <c r="G5" t="n">
-        <v>-14881883</v>
+        <v>-12306613</v>
       </c>
       <c r="H5" t="n">
-        <v>-63727582</v>
+        <v>59718127</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 8,376 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-7457376</v>
+        <v>-11047969</v>
       </c>
       <c r="E6" t="n">
-        <v>-4606790</v>
+        <v>-6226405</v>
       </c>
       <c r="F6" t="n">
-        <v>2302769</v>
+        <v>-11995730</v>
       </c>
       <c r="G6" t="n">
-        <v>371360</v>
+        <v>-20371886</v>
       </c>
       <c r="H6" t="n">
-        <v>10565757</v>
+        <v>66251947</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 23,115 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>419818</v>
+        <v>-64654213</v>
       </c>
       <c r="E7" t="n">
-        <v>7661571</v>
+        <v>-141118626</v>
       </c>
       <c r="F7" t="n">
-        <v>25734731</v>
+        <v>12948485</v>
       </c>
       <c r="G7" t="n">
-        <v>31195069</v>
+        <v>-10166434</v>
       </c>
       <c r="H7" t="n">
-        <v>-41781720</v>
+        <v>9564928</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-38830336</v>
+        <v>-1272477</v>
       </c>
       <c r="E8" t="n">
-        <v>-83197181</v>
+        <v>88450</v>
       </c>
       <c r="F8" t="n">
-        <v>-108275409</v>
+        <v>8457783</v>
       </c>
       <c r="G8" t="n">
-        <v>-114097650</v>
+        <v>9415690</v>
       </c>
       <c r="H8" t="n">
-        <v>145615415</v>
+        <v>10714390</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-1386713</v>
+        <v>3018222</v>
       </c>
       <c r="E9" t="n">
-        <v>-18026110</v>
+        <v>4101197</v>
       </c>
       <c r="F9" t="n">
-        <v>-5111730</v>
+        <v>-11943903</v>
       </c>
       <c r="G9" t="n">
-        <v>-7043631</v>
+        <v>-13701406</v>
       </c>
       <c r="H9" t="n">
-        <v>73856727</v>
+        <v>-63472853</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-6226405</v>
+        <v>-7219533</v>
       </c>
       <c r="E10" t="n">
-        <v>-17122734</v>
+        <v>-7457376</v>
       </c>
       <c r="F10" t="n">
-        <v>-20371886</v>
+        <v>2676611</v>
       </c>
       <c r="G10" t="n">
-        <v>-25838539</v>
+        <v>2302769</v>
       </c>
       <c r="H10" t="n">
-        <v>68526450</v>
+        <v>10652922</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>216411</v>
+        <v>-54905250</v>
       </c>
       <c r="E11" t="n">
-        <v>499335</v>
+        <v>-38830336</v>
       </c>
       <c r="F11" t="n">
-        <v>-3227832</v>
+        <v>-114915491</v>
       </c>
       <c r="G11" t="n">
-        <v>-2659816</v>
+        <v>-108275409</v>
       </c>
       <c r="H11" t="n">
-        <v>-13092049</v>
+        <v>142192254</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>2098171</v>
+        <v>-4802590</v>
       </c>
       <c r="E12" t="n">
-        <v>1555751</v>
+        <v>-1867365</v>
       </c>
       <c r="F12" t="n">
-        <v>-796018</v>
+        <v>-23125948</v>
       </c>
       <c r="G12" t="n">
-        <v>368137</v>
+        <v>-22783426</v>
       </c>
       <c r="H12" t="n">
-        <v>-10554380</v>
+        <v>54849897</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>919078</v>
+        <v>-10100528</v>
       </c>
       <c r="E13" t="n">
-        <v>539018</v>
+        <v>-1386713</v>
       </c>
       <c r="F13" t="n">
-        <v>-7611331</v>
+        <v>-7995207</v>
       </c>
       <c r="G13" t="n">
-        <v>-8796536</v>
+        <v>-5111730</v>
       </c>
       <c r="H13" t="n">
-        <v>-8072390</v>
+        <v>72825662</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -16,146 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>3200128</v>
+        <v>-1138518</v>
       </c>
       <c r="E14" t="n">
-        <v>13308687</v>
+        <v>-1223194</v>
       </c>
       <c r="F14" t="n">
-        <v>37669057</v>
+        <v>2067082</v>
       </c>
       <c r="G14" t="n">
-        <v>53814945</v>
+        <v>2666974</v>
       </c>
       <c r="H14" t="n">
-        <v>568590569</v>
+        <v>10072329</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13,841 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>691770</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1390357</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-3661689</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-3750193</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-2638784</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1671012</v>
+      </c>
+      <c r="E16" t="n">
+        <v>919078</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-6796663</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-7611331</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-8049956</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -16,398 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>1</v>
       </c>
-      <c r="D15" t="n">
-        <v>42107380</v>
-      </c>
-      <c r="E15" t="n">
-        <v>36088567</v>
-      </c>
-      <c r="F15" t="n">
-        <v>54138286</v>
-      </c>
-      <c r="G15" t="n">
-        <v>40297762</v>
-      </c>
-      <c r="H15" t="n">
-        <v>114503675</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>中華電</t>
+      <c r="D17" t="n">
+        <v>10963481</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11959992</v>
+      </c>
+      <c r="F17" t="n">
+        <v>69854759</v>
+      </c>
+      <c r="G17" t="n">
+        <v>86252968</v>
+      </c>
+      <c r="H17" t="n">
+        <v>199535841</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>台灣大</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
+        <v>-8087993</v>
+      </c>
+      <c r="E2" t="n">
         <v>-5780922</v>
       </c>
-      <c r="E2" t="n">
-        <v>419818</v>
-      </c>
       <c r="F2" t="n">
+        <v>27410116</v>
+      </c>
+      <c r="G2" t="n">
         <v>26017364</v>
       </c>
-      <c r="G2" t="n">
-        <v>25734731</v>
-      </c>
       <c r="H2" t="n">
-        <v>-20837915</v>
+        <v>-18374569</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -506,26 +506,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
+        <v>6120524</v>
+      </c>
+      <c r="E3" t="n">
         <v>-176747</v>
       </c>
-      <c r="E3" t="n">
-        <v>13079639</v>
-      </c>
       <c r="F3" t="n">
+        <v>31972283</v>
+      </c>
+      <c r="G3" t="n">
         <v>25631958</v>
       </c>
-      <c r="G3" t="n">
-        <v>29016789</v>
-      </c>
       <c r="H3" t="n">
-        <v>-20464641</v>
+        <v>-15675082</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -536,490 +536,490 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -25,969 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-3056869</v>
+        <v>-21478390</v>
       </c>
       <c r="E4" t="n">
-        <v>3200128</v>
+        <v>-24297060</v>
       </c>
       <c r="F4" t="n">
-        <v>31878739</v>
+        <v>-18020476</v>
       </c>
       <c r="G4" t="n">
-        <v>37669057</v>
+        <v>7948555</v>
       </c>
       <c r="H4" t="n">
-        <v>570598436</v>
+        <v>60026709</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 20,255 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 14,133 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-24297060</v>
+        <v>-12324778</v>
       </c>
       <c r="E5" t="n">
-        <v>-35204437</v>
+        <v>-54905250</v>
       </c>
       <c r="F5" t="n">
-        <v>7948555</v>
+        <v>-100782356</v>
       </c>
       <c r="G5" t="n">
-        <v>-12306613</v>
+        <v>-114915491</v>
       </c>
       <c r="H5" t="n">
-        <v>59718127</v>
+        <v>151018650</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 8,376 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-11047969</v>
+        <v>-1530237</v>
       </c>
       <c r="E6" t="n">
-        <v>-6226405</v>
+        <v>-1272477</v>
       </c>
       <c r="F6" t="n">
-        <v>-11995730</v>
+        <v>8379729</v>
       </c>
       <c r="G6" t="n">
-        <v>-20371886</v>
+        <v>8457783</v>
       </c>
       <c r="H6" t="n">
-        <v>66251947</v>
+        <v>10592721</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 23,115 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-64654213</v>
+        <v>-4067225</v>
       </c>
       <c r="E7" t="n">
-        <v>-141118626</v>
+        <v>-4802590</v>
       </c>
       <c r="F7" t="n">
-        <v>12948485</v>
+        <v>-15352223</v>
       </c>
       <c r="G7" t="n">
-        <v>-10166434</v>
+        <v>-23125948</v>
       </c>
       <c r="H7" t="n">
-        <v>9564928</v>
+        <v>54874022</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-1272477</v>
+        <v>23945</v>
       </c>
       <c r="E8" t="n">
-        <v>88450</v>
+        <v>-3969403</v>
       </c>
       <c r="F8" t="n">
-        <v>8457783</v>
+        <v>-4634763</v>
       </c>
       <c r="G8" t="n">
-        <v>9415690</v>
+        <v>-4629221</v>
       </c>
       <c r="H8" t="n">
-        <v>10714390</v>
+        <v>-33482818</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3018222</v>
+        <v>-3219142</v>
       </c>
       <c r="E9" t="n">
-        <v>4101197</v>
+        <v>-10100528</v>
       </c>
       <c r="F9" t="n">
-        <v>-11943903</v>
+        <v>-7531248</v>
       </c>
       <c r="G9" t="n">
-        <v>-13701406</v>
+        <v>-7995207</v>
       </c>
       <c r="H9" t="n">
-        <v>-63472853</v>
+        <v>72605693</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-7219533</v>
+        <v>39169</v>
       </c>
       <c r="E10" t="n">
-        <v>-7457376</v>
+        <v>-616225</v>
       </c>
       <c r="F10" t="n">
-        <v>2676611</v>
+        <v>-6243970</v>
       </c>
       <c r="G10" t="n">
-        <v>2302769</v>
+        <v>-7031911</v>
       </c>
       <c r="H10" t="n">
-        <v>10652922</v>
+        <v>-13487885</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 13,122 千)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-54905250</v>
+        <v>1227270</v>
       </c>
       <c r="E11" t="n">
-        <v>-38830336</v>
+        <v>-11047969</v>
       </c>
       <c r="F11" t="n">
-        <v>-114915491</v>
+        <v>1125790</v>
       </c>
       <c r="G11" t="n">
-        <v>-108275409</v>
+        <v>-11995730</v>
       </c>
       <c r="H11" t="n">
-        <v>142192254</v>
+        <v>75132200</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-4802590</v>
+        <v>-348803</v>
       </c>
       <c r="E12" t="n">
-        <v>-1867365</v>
+        <v>3018222</v>
       </c>
       <c r="F12" t="n">
-        <v>-23125948</v>
+        <v>-13595837</v>
       </c>
       <c r="G12" t="n">
-        <v>-22783426</v>
+        <v>-11943903</v>
       </c>
       <c r="H12" t="n">
-        <v>54849897</v>
+        <v>-67909818</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-10100528</v>
+        <v>4348602</v>
       </c>
       <c r="E13" t="n">
-        <v>-1386713</v>
+        <v>-3056869</v>
       </c>
       <c r="F13" t="n">
-        <v>-7995207</v>
+        <v>28128099</v>
       </c>
       <c r="G13" t="n">
-        <v>-5111730</v>
+        <v>31878739</v>
       </c>
       <c r="H13" t="n">
-        <v>72825662</v>
+        <v>574546280</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-1138518</v>
+        <v>-6150088</v>
       </c>
       <c r="E14" t="n">
-        <v>-1223194</v>
+        <v>-7219533</v>
       </c>
       <c r="F14" t="n">
-        <v>2067082</v>
+        <v>702689</v>
       </c>
       <c r="G14" t="n">
-        <v>2666974</v>
+        <v>2676611</v>
       </c>
       <c r="H14" t="n">
-        <v>10072329</v>
+        <v>9726897</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>691770</v>
+        <v>-1360213</v>
       </c>
       <c r="E15" t="n">
-        <v>-1390357</v>
+        <v>1671012</v>
       </c>
       <c r="F15" t="n">
-        <v>-3661689</v>
+        <v>-9526438</v>
       </c>
       <c r="G15" t="n">
-        <v>-3750193</v>
+        <v>-6796663</v>
       </c>
       <c r="H15" t="n">
-        <v>-2638784</v>
+        <v>-11719431</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>📈 20d 巨變(加碼 9,778 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1671012</v>
+        <v>49524280</v>
       </c>
       <c r="E16" t="n">
-        <v>919078</v>
+        <v>43395130</v>
       </c>
       <c r="F16" t="n">
-        <v>-6796663</v>
+        <v>70894993</v>
       </c>
       <c r="G16" t="n">
-        <v>-7611331</v>
+        <v>61116687</v>
       </c>
       <c r="H16" t="n">
-        <v>-8049956</v>
+        <v>140499073</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -16,398 千)</t>
+          <t>📉 20d 巨變(減碼 -33,382 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>10963481</v>
+        <v>-69311123</v>
       </c>
       <c r="E17" t="n">
-        <v>11959992</v>
+        <v>-64654213</v>
       </c>
       <c r="F17" t="n">
-        <v>69854759</v>
+        <v>-20433393</v>
       </c>
       <c r="G17" t="n">
-        <v>86252968</v>
+        <v>12948485</v>
       </c>
       <c r="H17" t="n">
-        <v>199535841</v>
+        <v>-680534</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,252 +466,252 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>-8087993</v>
+        <v>-670768</v>
       </c>
       <c r="E2" t="n">
-        <v>-5780922</v>
+        <v>6120524</v>
       </c>
       <c r="F2" t="n">
-        <v>27410116</v>
+        <v>26140424</v>
       </c>
       <c r="G2" t="n">
-        <v>26017364</v>
+        <v>31972283</v>
       </c>
       <c r="H2" t="n">
-        <v>-18374569</v>
+        <v>-21800439</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -22,188 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>6120524</v>
+        <v>-15044921</v>
       </c>
       <c r="E3" t="n">
-        <v>-176747</v>
+        <v>4348602</v>
       </c>
       <c r="F3" t="n">
-        <v>31972283</v>
+        <v>5940109</v>
       </c>
       <c r="G3" t="n">
-        <v>25631958</v>
+        <v>28128099</v>
       </c>
       <c r="H3" t="n">
-        <v>-15675082</v>
+        <v>563191832</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -25,969 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-21478390</v>
+        <v>3478025</v>
       </c>
       <c r="E4" t="n">
-        <v>-24297060</v>
+        <v>-2924887</v>
       </c>
       <c r="F4" t="n">
-        <v>-18020476</v>
+        <v>-11946950</v>
       </c>
       <c r="G4" t="n">
-        <v>7948555</v>
+        <v>-14834469</v>
       </c>
       <c r="H4" t="n">
-        <v>60026709</v>
+        <v>-48601616</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 14,133 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>-12324778</v>
+        <v>7179234</v>
       </c>
       <c r="E5" t="n">
-        <v>-54905250</v>
+        <v>-8087993</v>
       </c>
       <c r="F5" t="n">
-        <v>-100782356</v>
+        <v>32209473</v>
       </c>
       <c r="G5" t="n">
-        <v>-114915491</v>
+        <v>27410116</v>
       </c>
       <c r="H5" t="n">
-        <v>151018650</v>
+        <v>-11159593</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>-1530237</v>
+        <v>-1719450</v>
       </c>
       <c r="E6" t="n">
-        <v>-1272477</v>
+        <v>1227270</v>
       </c>
       <c r="F6" t="n">
-        <v>8379729</v>
+        <v>-2042935</v>
       </c>
       <c r="G6" t="n">
-        <v>8457783</v>
+        <v>1125790</v>
       </c>
       <c r="H6" t="n">
-        <v>10592721</v>
+        <v>68434570</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,021 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-4067225</v>
+        <v>-4481844</v>
       </c>
       <c r="E7" t="n">
-        <v>-4802590</v>
+        <v>-6150088</v>
       </c>
       <c r="F7" t="n">
-        <v>-15352223</v>
+        <v>-11318698</v>
       </c>
       <c r="G7" t="n">
-        <v>-23125948</v>
+        <v>702689</v>
       </c>
       <c r="H7" t="n">
-        <v>54874022</v>
+        <v>9457057</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>23945</v>
+        <v>-1164487</v>
       </c>
       <c r="E8" t="n">
-        <v>-3969403</v>
+        <v>-1530237</v>
       </c>
       <c r="F8" t="n">
-        <v>-4634763</v>
+        <v>8621562</v>
       </c>
       <c r="G8" t="n">
-        <v>-4629221</v>
+        <v>8379729</v>
       </c>
       <c r="H8" t="n">
-        <v>-33482818</v>
+        <v>10642639</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,268 +723,268 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-3219142</v>
+        <v>-19086172</v>
       </c>
       <c r="E9" t="n">
-        <v>-10100528</v>
+        <v>-12324778</v>
       </c>
       <c r="F9" t="n">
-        <v>-7531248</v>
+        <v>-94692066</v>
       </c>
       <c r="G9" t="n">
-        <v>-7995207</v>
+        <v>-100782356</v>
       </c>
       <c r="H9" t="n">
-        <v>72605693</v>
+        <v>147516296</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>39169</v>
+        <v>-6506870</v>
       </c>
       <c r="E10" t="n">
-        <v>-616225</v>
+        <v>-4067225</v>
       </c>
       <c r="F10" t="n">
-        <v>-6243970</v>
+        <v>-18839137</v>
       </c>
       <c r="G10" t="n">
-        <v>-7031911</v>
+        <v>-15352223</v>
       </c>
       <c r="H10" t="n">
-        <v>-13487885</v>
+        <v>51732761</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 13,122 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1227270</v>
+        <v>-3938296</v>
       </c>
       <c r="E11" t="n">
-        <v>-11047969</v>
+        <v>-3219142</v>
       </c>
       <c r="F11" t="n">
-        <v>1125790</v>
+        <v>-11594702</v>
       </c>
       <c r="G11" t="n">
-        <v>-11995730</v>
+        <v>-7531248</v>
       </c>
       <c r="H11" t="n">
-        <v>75132200</v>
+        <v>72294382</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-348803</v>
+        <v>182483</v>
       </c>
       <c r="E12" t="n">
-        <v>3018222</v>
+        <v>39169</v>
       </c>
       <c r="F12" t="n">
-        <v>-13595837</v>
+        <v>-5701351</v>
       </c>
       <c r="G12" t="n">
-        <v>-11943903</v>
+        <v>-6243970</v>
       </c>
       <c r="H12" t="n">
-        <v>-67909818</v>
+        <v>-13547360</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>4348602</v>
+        <v>1260134</v>
       </c>
       <c r="E13" t="n">
-        <v>-3056869</v>
+        <v>-639297</v>
       </c>
       <c r="F13" t="n">
-        <v>28128099</v>
+        <v>-2605451</v>
       </c>
       <c r="G13" t="n">
-        <v>31878739</v>
+        <v>-3656169</v>
       </c>
       <c r="H13" t="n">
-        <v>574546280</v>
+        <v>-20440525</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-6150088</v>
+        <v>-487181</v>
       </c>
       <c r="E14" t="n">
-        <v>-7219533</v>
+        <v>394545</v>
       </c>
       <c r="F14" t="n">
-        <v>702689</v>
+        <v>350466</v>
       </c>
       <c r="G14" t="n">
-        <v>2676611</v>
+        <v>3858187</v>
       </c>
       <c r="H14" t="n">
-        <v>9726897</v>
+        <v>11149670</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 26,200 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-1360213</v>
+        <v>23857230</v>
       </c>
       <c r="E15" t="n">
-        <v>1671012</v>
+        <v>-21478390</v>
       </c>
       <c r="F15" t="n">
-        <v>-9526438</v>
+        <v>8179766</v>
       </c>
       <c r="G15" t="n">
-        <v>-6796663</v>
+        <v>-18020476</v>
       </c>
       <c r="H15" t="n">
-        <v>-11719431</v>
+        <v>92259715</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,778 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>49524280</v>
+        <v>796929</v>
       </c>
       <c r="E16" t="n">
-        <v>43395130</v>
+        <v>23945</v>
       </c>
       <c r="F16" t="n">
-        <v>70894993</v>
+        <v>-4604889</v>
       </c>
       <c r="G16" t="n">
-        <v>61116687</v>
+        <v>-4634763</v>
       </c>
       <c r="H16" t="n">
-        <v>140499073</v>
+        <v>-33410964</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
@@ -996,30 +996,135 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -33,382 千)</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 27,853 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4640801</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-69311123</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7419144</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-20433393</v>
+      </c>
+      <c r="H17" t="n">
+        <v>42093698</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>🟢 5d 翻綠</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1889496</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2654576</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-553262</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-3310973</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1984711</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -9,458 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="n">
-        <v>-69311123</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-64654213</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-20433393</v>
-      </c>
-      <c r="G17" t="n">
-        <v>12948485</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-680534</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>華邦電</t>
+      <c r="D19" t="n">
+        <v>-9193144</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-224950</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-12297744</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-2840237</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-15553447</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 8,074 千)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>47016221</v>
+      </c>
+      <c r="E20" t="n">
+        <v>49524280</v>
+      </c>
+      <c r="F20" t="n">
+        <v>78969213</v>
+      </c>
+      <c r="G20" t="n">
+        <v>70894993</v>
+      </c>
+      <c r="H20" t="n">
+        <v>147928019</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>中華電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,322 +466,322 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -19,066 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-670768</v>
+        <v>23695530</v>
       </c>
       <c r="E2" t="n">
-        <v>6120524</v>
+        <v>4640801</v>
       </c>
       <c r="F2" t="n">
-        <v>26140424</v>
+        <v>-11647115</v>
       </c>
       <c r="G2" t="n">
-        <v>31972283</v>
+        <v>7419144</v>
       </c>
       <c r="H2" t="n">
-        <v>-21800439</v>
+        <v>29500890</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -22,188 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-15044921</v>
+        <v>-2226357</v>
       </c>
       <c r="E3" t="n">
-        <v>4348602</v>
+        <v>-670768</v>
       </c>
       <c r="F3" t="n">
-        <v>5940109</v>
+        <v>23706646</v>
       </c>
       <c r="G3" t="n">
-        <v>28128099</v>
+        <v>26140424</v>
       </c>
       <c r="H3" t="n">
-        <v>563191832</v>
+        <v>-9554785</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,337 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3478025</v>
+        <v>-1797139</v>
       </c>
       <c r="E4" t="n">
-        <v>-2924887</v>
+        <v>-4481844</v>
       </c>
       <c r="F4" t="n">
-        <v>-11946950</v>
+        <v>-20655865</v>
       </c>
       <c r="G4" t="n">
-        <v>-14834469</v>
+        <v>-11318698</v>
       </c>
       <c r="H4" t="n">
-        <v>-48601616</v>
+        <v>10027502</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>7179234</v>
+        <v>1116580</v>
       </c>
       <c r="E5" t="n">
-        <v>-8087993</v>
+        <v>-639289</v>
       </c>
       <c r="F5" t="n">
-        <v>32209473</v>
+        <v>-7090103</v>
       </c>
       <c r="G5" t="n">
-        <v>27410116</v>
+        <v>-8229822</v>
       </c>
       <c r="H5" t="n">
-        <v>-11159593</v>
+        <v>-16093484</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-1719450</v>
+        <v>551906</v>
       </c>
       <c r="E6" t="n">
-        <v>1227270</v>
+        <v>-13328620</v>
       </c>
       <c r="F6" t="n">
-        <v>-2042935</v>
+        <v>-61917</v>
       </c>
       <c r="G6" t="n">
-        <v>1125790</v>
+        <v>-4372146</v>
       </c>
       <c r="H6" t="n">
-        <v>68434570</v>
+        <v>-119678648</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,021 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-4481844</v>
+        <v>-1083126</v>
       </c>
       <c r="E7" t="n">
-        <v>-6150088</v>
+        <v>-1164487</v>
       </c>
       <c r="F7" t="n">
-        <v>-11318698</v>
+        <v>7729620</v>
       </c>
       <c r="G7" t="n">
-        <v>702689</v>
+        <v>8621562</v>
       </c>
       <c r="H7" t="n">
-        <v>9457057</v>
+        <v>12033362</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-1164487</v>
+        <v>5444224</v>
       </c>
       <c r="E8" t="n">
-        <v>-1530237</v>
+        <v>3478025</v>
       </c>
       <c r="F8" t="n">
-        <v>8621562</v>
+        <v>-9313210</v>
       </c>
       <c r="G8" t="n">
-        <v>8379729</v>
+        <v>-11946950</v>
       </c>
       <c r="H8" t="n">
-        <v>10642639</v>
+        <v>-42046160</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-19086172</v>
+        <v>-1210981</v>
       </c>
       <c r="E9" t="n">
-        <v>-12324778</v>
+        <v>-1284004</v>
       </c>
       <c r="F9" t="n">
-        <v>-94692066</v>
+        <v>19886</v>
       </c>
       <c r="G9" t="n">
-        <v>-100782356</v>
+        <v>-1086135</v>
       </c>
       <c r="H9" t="n">
-        <v>147516296</v>
+        <v>-10849948</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-6506870</v>
+        <v>-14546783</v>
       </c>
       <c r="E10" t="n">
-        <v>-4067225</v>
+        <v>-15044921</v>
       </c>
       <c r="F10" t="n">
-        <v>-18839137</v>
+        <v>1205063</v>
       </c>
       <c r="G10" t="n">
-        <v>-15352223</v>
+        <v>5940109</v>
       </c>
       <c r="H10" t="n">
-        <v>51732761</v>
+        <v>491027414</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,163 +793,163 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-3938296</v>
+        <v>-3955531</v>
       </c>
       <c r="E11" t="n">
-        <v>-3219142</v>
+        <v>-19086172</v>
       </c>
       <c r="F11" t="n">
-        <v>-11594702</v>
+        <v>-88484636</v>
       </c>
       <c r="G11" t="n">
-        <v>-7531248</v>
+        <v>-94692066</v>
       </c>
       <c r="H11" t="n">
-        <v>72294382</v>
+        <v>171598970</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>182483</v>
+        <v>-5940683</v>
       </c>
       <c r="E12" t="n">
-        <v>39169</v>
+        <v>-6506870</v>
       </c>
       <c r="F12" t="n">
-        <v>-5701351</v>
+        <v>-25930206</v>
       </c>
       <c r="G12" t="n">
-        <v>-6243970</v>
+        <v>-18839137</v>
       </c>
       <c r="H12" t="n">
-        <v>-13547360</v>
+        <v>48099131</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1260134</v>
+        <v>-5120170</v>
       </c>
       <c r="E13" t="n">
-        <v>-639297</v>
+        <v>-3938296</v>
       </c>
       <c r="F13" t="n">
-        <v>-2605451</v>
+        <v>-14286055</v>
       </c>
       <c r="G13" t="n">
-        <v>-3656169</v>
+        <v>-11594702</v>
       </c>
       <c r="H13" t="n">
-        <v>-20440525</v>
+        <v>91210103</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-487181</v>
+        <v>-7602548</v>
       </c>
       <c r="E14" t="n">
-        <v>394545</v>
+        <v>-1719450</v>
       </c>
       <c r="F14" t="n">
-        <v>350466</v>
+        <v>-201381</v>
       </c>
       <c r="G14" t="n">
-        <v>3858187</v>
+        <v>-2042935</v>
       </c>
       <c r="H14" t="n">
-        <v>11149670</v>
+        <v>89826456</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 26,200 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>23857230</v>
+        <v>669536</v>
       </c>
       <c r="E15" t="n">
-        <v>-21478390</v>
+        <v>1260134</v>
       </c>
       <c r="F15" t="n">
-        <v>8179766</v>
+        <v>-3165856</v>
       </c>
       <c r="G15" t="n">
-        <v>-18020476</v>
+        <v>-2605451</v>
       </c>
       <c r="H15" t="n">
-        <v>92259715</v>
+        <v>-17542768</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
@@ -968,19 +968,19 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
+        <v>791703</v>
+      </c>
+      <c r="E16" t="n">
         <v>796929</v>
       </c>
-      <c r="E16" t="n">
-        <v>23945</v>
-      </c>
       <c r="F16" t="n">
+        <v>-4710884</v>
+      </c>
+      <c r="G16" t="n">
         <v>-4604889</v>
       </c>
-      <c r="G16" t="n">
-        <v>-4634763</v>
-      </c>
       <c r="H16" t="n">
-        <v>-33410964</v>
+        <v>-35464352</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,140 +991,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 27,853 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>4640801</v>
+        <v>264303</v>
       </c>
       <c r="E17" t="n">
-        <v>-69311123</v>
+        <v>182483</v>
       </c>
       <c r="F17" t="n">
-        <v>7419144</v>
+        <v>-4569412</v>
       </c>
       <c r="G17" t="n">
-        <v>-20433393</v>
+        <v>-5701351</v>
       </c>
       <c r="H17" t="n">
-        <v>42093698</v>
+        <v>-13568085</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>🟢 5d 翻綠</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1889496</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-2654576</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-553262</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-3310973</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-1984711</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -9,458 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-9193144</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-224950</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-12297744</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-2840237</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-15553447</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>藥華藥</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 8,074 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>47016221</v>
-      </c>
-      <c r="E20" t="n">
-        <v>49524280</v>
-      </c>
-      <c r="F20" t="n">
-        <v>78969213</v>
-      </c>
-      <c r="G20" t="n">
-        <v>70894993</v>
-      </c>
-      <c r="H20" t="n">
-        <v>147928019</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>中華電</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,280 +466,280 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -19,066 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -22,012 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>23695530</v>
+        <v>12482165</v>
       </c>
       <c r="E2" t="n">
-        <v>4640801</v>
+        <v>28358558</v>
       </c>
       <c r="F2" t="n">
-        <v>-11647115</v>
+        <v>-6465908</v>
       </c>
       <c r="G2" t="n">
-        <v>7419144</v>
+        <v>15545992</v>
       </c>
       <c r="H2" t="n">
-        <v>29500890</v>
+        <v>51692071</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 10,132 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-2226357</v>
+        <v>35574502</v>
       </c>
       <c r="E3" t="n">
-        <v>-670768</v>
+        <v>23695530</v>
       </c>
       <c r="F3" t="n">
-        <v>23706646</v>
+        <v>-1515536</v>
       </c>
       <c r="G3" t="n">
-        <v>26140424</v>
+        <v>-11647115</v>
       </c>
       <c r="H3" t="n">
-        <v>-9554785</v>
+        <v>44084205</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,337 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-1797139</v>
+        <v>2999995</v>
       </c>
       <c r="E4" t="n">
-        <v>-4481844</v>
+        <v>-5557918</v>
       </c>
       <c r="F4" t="n">
-        <v>-20655865</v>
+        <v>-8900948</v>
       </c>
       <c r="G4" t="n">
-        <v>-11318698</v>
+        <v>-15320298</v>
       </c>
       <c r="H4" t="n">
-        <v>10027502</v>
+        <v>-79090485</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>1116580</v>
+        <v>-4793575</v>
       </c>
       <c r="E5" t="n">
-        <v>-639289</v>
+        <v>-2226357</v>
       </c>
       <c r="F5" t="n">
-        <v>-7090103</v>
+        <v>20272878</v>
       </c>
       <c r="G5" t="n">
-        <v>-8229822</v>
+        <v>23706646</v>
       </c>
       <c r="H5" t="n">
-        <v>-16093484</v>
+        <v>-7094160</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -20,964 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>551906</v>
+        <v>-32812476</v>
       </c>
       <c r="E6" t="n">
-        <v>-13328620</v>
+        <v>-3955531</v>
       </c>
       <c r="F6" t="n">
-        <v>-61917</v>
+        <v>-109448520</v>
       </c>
       <c r="G6" t="n">
-        <v>-4372146</v>
+        <v>-88484636</v>
       </c>
       <c r="H6" t="n">
-        <v>-119678648</v>
+        <v>146463131</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-1083126</v>
+        <v>743155</v>
       </c>
       <c r="E7" t="n">
-        <v>-1164487</v>
+        <v>1116580</v>
       </c>
       <c r="F7" t="n">
-        <v>7729620</v>
+        <v>-6222989</v>
       </c>
       <c r="G7" t="n">
-        <v>8621562</v>
+        <v>-7090103</v>
       </c>
       <c r="H7" t="n">
-        <v>12033362</v>
+        <v>-16237363</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>5444224</v>
+        <v>-1304926</v>
       </c>
       <c r="E8" t="n">
-        <v>3478025</v>
+        <v>-1083126</v>
       </c>
       <c r="F8" t="n">
-        <v>-9313210</v>
+        <v>6896264</v>
       </c>
       <c r="G8" t="n">
-        <v>-11946950</v>
+        <v>7729620</v>
       </c>
       <c r="H8" t="n">
-        <v>-42046160</v>
+        <v>12217091</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-1210981</v>
+        <v>2273935</v>
       </c>
       <c r="E9" t="n">
-        <v>-1284004</v>
+        <v>5444224</v>
       </c>
       <c r="F9" t="n">
-        <v>19886</v>
+        <v>-8761282</v>
       </c>
       <c r="G9" t="n">
-        <v>-1086135</v>
+        <v>-9313210</v>
       </c>
       <c r="H9" t="n">
-        <v>-10849948</v>
+        <v>-42554232</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
+        <v>-1955200</v>
+      </c>
+      <c r="E10" t="n">
         <v>-14546783</v>
       </c>
-      <c r="E10" t="n">
-        <v>-15044921</v>
-      </c>
       <c r="F10" t="n">
+        <v>8465438</v>
+      </c>
+      <c r="G10" t="n">
         <v>1205063</v>
       </c>
-      <c r="G10" t="n">
-        <v>5940109</v>
-      </c>
       <c r="H10" t="n">
-        <v>491027414</v>
+        <v>463658727</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,23 +793,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-3955531</v>
+        <v>-705430</v>
       </c>
       <c r="E11" t="n">
-        <v>-19086172</v>
+        <v>-1797139</v>
       </c>
       <c r="F11" t="n">
-        <v>-88484636</v>
+        <v>-14883040</v>
       </c>
       <c r="G11" t="n">
-        <v>-94692066</v>
+        <v>-20655865</v>
       </c>
       <c r="H11" t="n">
-        <v>171598970</v>
+        <v>9058469</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
@@ -828,19 +828,19 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
+        <v>-2519724</v>
+      </c>
+      <c r="E12" t="n">
         <v>-5940683</v>
       </c>
-      <c r="E12" t="n">
-        <v>-6506870</v>
-      </c>
       <c r="F12" t="n">
+        <v>-25052637</v>
+      </c>
+      <c r="G12" t="n">
         <v>-25930206</v>
       </c>
-      <c r="G12" t="n">
-        <v>-18839137</v>
-      </c>
       <c r="H12" t="n">
-        <v>48099131</v>
+        <v>49119333</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -863,19 +863,19 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
+        <v>-5160953</v>
+      </c>
+      <c r="E13" t="n">
         <v>-5120170</v>
       </c>
-      <c r="E13" t="n">
-        <v>-3938296</v>
-      </c>
       <c r="F13" t="n">
+        <v>-14162537</v>
+      </c>
+      <c r="G13" t="n">
         <v>-14286055</v>
       </c>
-      <c r="G13" t="n">
-        <v>-11594702</v>
-      </c>
       <c r="H13" t="n">
-        <v>91210103</v>
+        <v>85883383</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -886,42 +886,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-7602548</v>
+        <v>449162</v>
       </c>
       <c r="E14" t="n">
-        <v>-1719450</v>
+        <v>551906</v>
       </c>
       <c r="F14" t="n">
-        <v>-201381</v>
+        <v>-3240294</v>
       </c>
       <c r="G14" t="n">
-        <v>-2042935</v>
+        <v>-61917</v>
       </c>
       <c r="H14" t="n">
-        <v>89826456</v>
+        <v>-111259611</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,58 +933,58 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>669536</v>
+        <v>754419</v>
       </c>
       <c r="E15" t="n">
-        <v>1260134</v>
+        <v>791703</v>
       </c>
       <c r="F15" t="n">
-        <v>-3165856</v>
+        <v>-4742299</v>
       </c>
       <c r="G15" t="n">
-        <v>-2605451</v>
+        <v>-4710884</v>
       </c>
       <c r="H15" t="n">
-        <v>-17542768</v>
+        <v>-31853120</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 22,333 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>791703</v>
+        <v>1602170</v>
       </c>
       <c r="E16" t="n">
-        <v>796929</v>
+        <v>-7602548</v>
       </c>
       <c r="F16" t="n">
-        <v>-4710884</v>
+        <v>22131664</v>
       </c>
       <c r="G16" t="n">
-        <v>-4604889</v>
+        <v>-201381</v>
       </c>
       <c r="H16" t="n">
-        <v>-35464352</v>
+        <v>90894801</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
@@ -1003,23 +1003,93 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
+        <v>311140</v>
+      </c>
+      <c r="E17" t="n">
         <v>264303</v>
       </c>
-      <c r="E17" t="n">
-        <v>182483</v>
-      </c>
       <c r="F17" t="n">
+        <v>-4517535</v>
+      </c>
+      <c r="G17" t="n">
         <v>-4569412</v>
       </c>
-      <c r="G17" t="n">
-        <v>-5701351</v>
-      </c>
       <c r="H17" t="n">
-        <v>-13568085</v>
+        <v>-15128782</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>長榮航太</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>🟢 5d 翻綠</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>916087</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1210981</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1323860</v>
+      </c>
+      <c r="G18" t="n">
+        <v>19886</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-9114160</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 8,137 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25887340</v>
+      </c>
+      <c r="E19" t="n">
+        <v>12310583</v>
+      </c>
+      <c r="F19" t="n">
+        <v>44905786</v>
+      </c>
+      <c r="G19" t="n">
+        <v>36768774</v>
+      </c>
+      <c r="H19" t="n">
+        <v>14205737</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,35 +466,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -22,012 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>12482165</v>
+        <v>-7399669</v>
       </c>
       <c r="E2" t="n">
-        <v>28358558</v>
+        <v>-4793575</v>
       </c>
       <c r="F2" t="n">
-        <v>-6465908</v>
+        <v>14742997</v>
       </c>
       <c r="G2" t="n">
-        <v>15545992</v>
+        <v>20272878</v>
       </c>
       <c r="H2" t="n">
-        <v>51692071</v>
+        <v>-9857896</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
@@ -506,26 +506,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 10,132 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
+        <v>27224635</v>
+      </c>
+      <c r="E3" t="n">
         <v>35574502</v>
       </c>
-      <c r="E3" t="n">
-        <v>23695530</v>
-      </c>
       <c r="F3" t="n">
+        <v>-5627928</v>
+      </c>
+      <c r="G3" t="n">
         <v>-1515536</v>
       </c>
-      <c r="G3" t="n">
-        <v>-11647115</v>
-      </c>
       <c r="H3" t="n">
-        <v>44084205</v>
+        <v>54208364</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -536,7 +536,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,100 +548,100 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>2999995</v>
+        <v>1194409</v>
       </c>
       <c r="E4" t="n">
-        <v>-5557918</v>
+        <v>-1882810</v>
       </c>
       <c r="F4" t="n">
-        <v>-8900948</v>
+        <v>-11069427</v>
       </c>
       <c r="G4" t="n">
-        <v>-15320298</v>
+        <v>-11837678</v>
       </c>
       <c r="H4" t="n">
-        <v>-79090485</v>
+        <v>-11761931</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -10,542 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-4793575</v>
+        <v>-6953167</v>
       </c>
       <c r="E5" t="n">
-        <v>-2226357</v>
+        <v>-5160953</v>
       </c>
       <c r="F5" t="n">
-        <v>20272878</v>
+        <v>-24704220</v>
       </c>
       <c r="G5" t="n">
-        <v>23706646</v>
+        <v>-14162537</v>
       </c>
       <c r="H5" t="n">
-        <v>-7094160</v>
+        <v>82028696</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -20,964 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-32812476</v>
+        <v>433621</v>
       </c>
       <c r="E6" t="n">
-        <v>-3955531</v>
+        <v>743155</v>
       </c>
       <c r="F6" t="n">
-        <v>-109448520</v>
+        <v>-5443885</v>
       </c>
       <c r="G6" t="n">
-        <v>-88484636</v>
+        <v>-6222989</v>
       </c>
       <c r="H6" t="n">
-        <v>146463131</v>
+        <v>-16256422</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,23 +653,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>743155</v>
+        <v>16316905</v>
       </c>
       <c r="E7" t="n">
-        <v>1116580</v>
+        <v>449162</v>
       </c>
       <c r="F7" t="n">
-        <v>-6222989</v>
+        <v>-1321263</v>
       </c>
       <c r="G7" t="n">
-        <v>-7090103</v>
+        <v>-3240294</v>
       </c>
       <c r="H7" t="n">
-        <v>-16237363</v>
+        <v>-104136248</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
+        <v>-95588</v>
+      </c>
+      <c r="E8" t="n">
         <v>-1304926</v>
       </c>
-      <c r="E8" t="n">
-        <v>-1083126</v>
-      </c>
       <c r="F8" t="n">
+        <v>7385846</v>
+      </c>
+      <c r="G8" t="n">
         <v>6896264</v>
       </c>
-      <c r="G8" t="n">
-        <v>7729620</v>
-      </c>
       <c r="H8" t="n">
-        <v>12217091</v>
+        <v>12308977</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -723,19 +723,19 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
+        <v>2979169</v>
+      </c>
+      <c r="E9" t="n">
         <v>2273935</v>
       </c>
-      <c r="E9" t="n">
-        <v>5444224</v>
-      </c>
       <c r="F9" t="n">
+        <v>-9506146</v>
+      </c>
+      <c r="G9" t="n">
         <v>-8761282</v>
       </c>
-      <c r="G9" t="n">
-        <v>-9313210</v>
-      </c>
       <c r="H9" t="n">
-        <v>-42554232</v>
+        <v>-42693241</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -746,77 +746,77 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1955200</v>
+        <v>-1004107</v>
       </c>
       <c r="E10" t="n">
-        <v>-14546783</v>
+        <v>-705430</v>
       </c>
       <c r="F10" t="n">
-        <v>8465438</v>
+        <v>-12860211</v>
       </c>
       <c r="G10" t="n">
-        <v>1205063</v>
+        <v>-14883040</v>
       </c>
       <c r="H10" t="n">
-        <v>463658727</v>
+        <v>8674447</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-705430</v>
+        <v>4190684</v>
       </c>
       <c r="E11" t="n">
-        <v>-1797139</v>
+        <v>2999995</v>
       </c>
       <c r="F11" t="n">
-        <v>-14883040</v>
+        <v>-14156943</v>
       </c>
       <c r="G11" t="n">
-        <v>-20655865</v>
+        <v>-8900948</v>
       </c>
       <c r="H11" t="n">
-        <v>9058469</v>
+        <v>-84296711</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,30 +828,30 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-2519724</v>
+        <v>-27146875</v>
       </c>
       <c r="E12" t="n">
-        <v>-5940683</v>
+        <v>-32812476</v>
       </c>
       <c r="F12" t="n">
-        <v>-25052637</v>
+        <v>-116883701</v>
       </c>
       <c r="G12" t="n">
-        <v>-25930206</v>
+        <v>-109448520</v>
       </c>
       <c r="H12" t="n">
-        <v>49119333</v>
+        <v>142441817</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,30 +863,30 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-5160953</v>
+        <v>-3202892</v>
       </c>
       <c r="E13" t="n">
-        <v>-5120170</v>
+        <v>-2519724</v>
       </c>
       <c r="F13" t="n">
-        <v>-14162537</v>
+        <v>-25111868</v>
       </c>
       <c r="G13" t="n">
-        <v>-14286055</v>
+        <v>-25052637</v>
       </c>
       <c r="H13" t="n">
-        <v>85883383</v>
+        <v>47156914</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,198 +898,93 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>449162</v>
+        <v>-48825</v>
       </c>
       <c r="E14" t="n">
-        <v>551906</v>
+        <v>1320154</v>
       </c>
       <c r="F14" t="n">
-        <v>-3240294</v>
+        <v>3811875</v>
       </c>
       <c r="G14" t="n">
-        <v>-61917</v>
+        <v>4651731</v>
       </c>
       <c r="H14" t="n">
-        <v>-111259611</v>
+        <v>14548777</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>754419</v>
+        <v>12150162</v>
       </c>
       <c r="E15" t="n">
-        <v>791703</v>
+        <v>-1955200</v>
       </c>
       <c r="F15" t="n">
-        <v>-4742299</v>
+        <v>10974847</v>
       </c>
       <c r="G15" t="n">
-        <v>-4710884</v>
+        <v>8465438</v>
       </c>
       <c r="H15" t="n">
-        <v>-31853120</v>
+        <v>474866402</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 22,333 千)</t>
+          <t>📈 20d 巨變(加碼 26,038 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1602170</v>
+        <v>35170358</v>
       </c>
       <c r="E16" t="n">
-        <v>-7602548</v>
+        <v>12482165</v>
       </c>
       <c r="F16" t="n">
-        <v>22131664</v>
+        <v>19572477</v>
       </c>
       <c r="G16" t="n">
-        <v>-201381</v>
+        <v>-6465908</v>
       </c>
       <c r="H16" t="n">
-        <v>90894801</v>
+        <v>80888242</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>311140</v>
-      </c>
-      <c r="E17" t="n">
-        <v>264303</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-4517535</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-4569412</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-15128782</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>長榮航太</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>🟢 5d 翻綠</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>916087</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-1210981</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1323860</v>
-      </c>
-      <c r="G18" t="n">
-        <v>19886</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-9114160</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>健鼎</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 8,137 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>25887340</v>
-      </c>
-      <c r="E19" t="n">
-        <v>12310583</v>
-      </c>
-      <c r="F19" t="n">
-        <v>44905786</v>
-      </c>
-      <c r="G19" t="n">
-        <v>36768774</v>
-      </c>
-      <c r="H19" t="n">
-        <v>14205737</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,385 +466,385 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -50,086 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-7399669</v>
+        <v>14909059</v>
       </c>
       <c r="E2" t="n">
-        <v>-4793575</v>
+        <v>35170358</v>
       </c>
       <c r="F2" t="n">
-        <v>14742997</v>
+        <v>-30513770</v>
       </c>
       <c r="G2" t="n">
-        <v>20272878</v>
+        <v>19572477</v>
       </c>
       <c r="H2" t="n">
-        <v>-9857896</v>
+        <v>60935525</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -42,122 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>27224635</v>
+        <v>-23601689</v>
       </c>
       <c r="E3" t="n">
-        <v>35574502</v>
+        <v>9151152</v>
       </c>
       <c r="F3" t="n">
-        <v>-5627928</v>
+        <v>-12058135</v>
       </c>
       <c r="G3" t="n">
-        <v>-1515536</v>
+        <v>30063426</v>
       </c>
       <c r="H3" t="n">
-        <v>54208364</v>
+        <v>72882967</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -47,956 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>1194409</v>
+        <v>19645741</v>
       </c>
       <c r="E4" t="n">
-        <v>-1882810</v>
+        <v>27224635</v>
       </c>
       <c r="F4" t="n">
-        <v>-11069427</v>
+        <v>-53584173</v>
       </c>
       <c r="G4" t="n">
-        <v>-11837678</v>
+        <v>-5627928</v>
       </c>
       <c r="H4" t="n">
-        <v>-11761931</v>
+        <v>36384008</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -10,542 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>-6953167</v>
+        <v>-15842819</v>
       </c>
       <c r="E5" t="n">
-        <v>-5160953</v>
+        <v>-7399669</v>
       </c>
       <c r="F5" t="n">
-        <v>-24704220</v>
+        <v>7589057</v>
       </c>
       <c r="G5" t="n">
-        <v>-14162537</v>
+        <v>14742997</v>
       </c>
       <c r="H5" t="n">
-        <v>82028696</v>
+        <v>-13511487</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -9,168 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>433621</v>
+        <v>6854883</v>
       </c>
       <c r="E6" t="n">
-        <v>743155</v>
+        <v>16316905</v>
       </c>
       <c r="F6" t="n">
-        <v>-5443885</v>
+        <v>-10489690</v>
       </c>
       <c r="G6" t="n">
-        <v>-6222989</v>
+        <v>-1321263</v>
       </c>
       <c r="H6" t="n">
-        <v>-16256422</v>
+        <v>-108804080</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -8,776 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>16316905</v>
+        <v>-3702664</v>
       </c>
       <c r="E7" t="n">
-        <v>449162</v>
+        <v>12150162</v>
       </c>
       <c r="F7" t="n">
-        <v>-1321263</v>
+        <v>2199194</v>
       </c>
       <c r="G7" t="n">
-        <v>-3240294</v>
+        <v>10974847</v>
       </c>
       <c r="H7" t="n">
-        <v>-104136248</v>
+        <v>462961420</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 14,561 千)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-95588</v>
+        <v>-28100187</v>
       </c>
       <c r="E8" t="n">
-        <v>-1304926</v>
+        <v>-27146875</v>
       </c>
       <c r="F8" t="n">
-        <v>7385846</v>
+        <v>-102323096</v>
       </c>
       <c r="G8" t="n">
-        <v>6896264</v>
+        <v>-116883701</v>
       </c>
       <c r="H8" t="n">
-        <v>12308977</v>
+        <v>150314901</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2979169</v>
+        <v>-22396</v>
       </c>
       <c r="E9" t="n">
-        <v>2273935</v>
+        <v>-95588</v>
       </c>
       <c r="F9" t="n">
-        <v>-9506146</v>
+        <v>6596116</v>
       </c>
       <c r="G9" t="n">
-        <v>-8761282</v>
+        <v>7385846</v>
       </c>
       <c r="H9" t="n">
-        <v>-42693241</v>
+        <v>12260500</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1004107</v>
+        <v>3314976</v>
       </c>
       <c r="E10" t="n">
-        <v>-705430</v>
+        <v>2979169</v>
       </c>
       <c r="F10" t="n">
-        <v>-12860211</v>
+        <v>-10549554</v>
       </c>
       <c r="G10" t="n">
-        <v>-14883040</v>
+        <v>-9506146</v>
       </c>
       <c r="H10" t="n">
-        <v>8674447</v>
+        <v>-43020411</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>4190684</v>
+        <v>-2168260</v>
       </c>
       <c r="E11" t="n">
-        <v>2999995</v>
+        <v>-1004107</v>
       </c>
       <c r="F11" t="n">
-        <v>-14156943</v>
+        <v>-14666067</v>
       </c>
       <c r="G11" t="n">
-        <v>-8900948</v>
+        <v>-12860211</v>
       </c>
       <c r="H11" t="n">
-        <v>-84296711</v>
+        <v>6584269</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-27146875</v>
+        <v>8376114</v>
       </c>
       <c r="E12" t="n">
-        <v>-32812476</v>
+        <v>4190684</v>
       </c>
       <c r="F12" t="n">
-        <v>-116883701</v>
+        <v>-11184678</v>
       </c>
       <c r="G12" t="n">
-        <v>-109448520</v>
+        <v>-14156943</v>
       </c>
       <c r="H12" t="n">
-        <v>142441817</v>
+        <v>-82164231</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
@@ -863,19 +863,19 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
+        <v>-2961794</v>
+      </c>
+      <c r="E13" t="n">
         <v>-3202892</v>
       </c>
-      <c r="E13" t="n">
-        <v>-2519724</v>
-      </c>
       <c r="F13" t="n">
+        <v>-21607041</v>
+      </c>
+      <c r="G13" t="n">
         <v>-25111868</v>
       </c>
-      <c r="G13" t="n">
-        <v>-25052637</v>
-      </c>
       <c r="H13" t="n">
-        <v>47156914</v>
+        <v>47422137</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -886,105 +886,140 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-48825</v>
+        <v>-11141148</v>
       </c>
       <c r="E14" t="n">
-        <v>1320154</v>
+        <v>-6953167</v>
       </c>
       <c r="F14" t="n">
-        <v>3811875</v>
+        <v>-24135641</v>
       </c>
       <c r="G14" t="n">
-        <v>4651731</v>
+        <v>-24704220</v>
       </c>
       <c r="H14" t="n">
-        <v>14548777</v>
+        <v>77620746</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>12150162</v>
+        <v>1174981</v>
       </c>
       <c r="E15" t="n">
-        <v>-1955200</v>
+        <v>1194409</v>
       </c>
       <c r="F15" t="n">
-        <v>10974847</v>
+        <v>-10719826</v>
       </c>
       <c r="G15" t="n">
-        <v>8465438</v>
+        <v>-11069427</v>
       </c>
       <c r="H15" t="n">
-        <v>474866402</v>
+        <v>-11716392</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 26,038 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>35170358</v>
+        <v>205305</v>
       </c>
       <c r="E16" t="n">
-        <v>12482165</v>
+        <v>433621</v>
       </c>
       <c r="F16" t="n">
-        <v>19572477</v>
+        <v>-4294919</v>
       </c>
       <c r="G16" t="n">
-        <v>-6465908</v>
+        <v>-5443885</v>
       </c>
       <c r="H16" t="n">
-        <v>80888242</v>
+        <v>-16587299</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>高力</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-343523</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-48825</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3888813</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3811875</v>
+      </c>
+      <c r="H17" t="n">
+        <v>14567230</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>立隆電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -50,086 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>14909059</v>
       </c>
       <c r="E2" t="n">
-        <v>35170358</v>
+        <v>14909059</v>
       </c>
       <c r="F2" t="n">
         <v>-30513770</v>
       </c>
       <c r="G2" t="n">
-        <v>19572477</v>
+        <v>-30513770</v>
       </c>
       <c r="H2" t="n">
         <v>60935525</v>
@@ -501,35 +501,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -42,122 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-23601689</v>
+        <v>-15842819</v>
       </c>
       <c r="E3" t="n">
-        <v>9151152</v>
+        <v>-15842819</v>
       </c>
       <c r="F3" t="n">
-        <v>-12058135</v>
+        <v>7589057</v>
       </c>
       <c r="G3" t="n">
-        <v>30063426</v>
+        <v>7589057</v>
       </c>
       <c r="H3" t="n">
-        <v>72882967</v>
+        <v>-13511487</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
@@ -541,23 +541,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -47,956 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>19645741</v>
       </c>
       <c r="E4" t="n">
-        <v>27224635</v>
+        <v>19645741</v>
       </c>
       <c r="F4" t="n">
         <v>-53584173</v>
       </c>
       <c r="G4" t="n">
-        <v>-5627928</v>
+        <v>-53584173</v>
       </c>
       <c r="H4" t="n">
         <v>36384008</v>
@@ -571,217 +571,217 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>-15842819</v>
+        <v>6854883</v>
       </c>
       <c r="E5" t="n">
-        <v>-7399669</v>
+        <v>6854883</v>
       </c>
       <c r="F5" t="n">
-        <v>7589057</v>
+        <v>-10489690</v>
       </c>
       <c r="G5" t="n">
-        <v>14742997</v>
+        <v>-10489690</v>
       </c>
       <c r="H5" t="n">
-        <v>-13511487</v>
+        <v>-108804080</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -9,168 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6854883</v>
+        <v>-22396</v>
       </c>
       <c r="E6" t="n">
-        <v>16316905</v>
+        <v>-22396</v>
       </c>
       <c r="F6" t="n">
-        <v>-10489690</v>
+        <v>6596116</v>
       </c>
       <c r="G6" t="n">
-        <v>-1321263</v>
+        <v>6596116</v>
       </c>
       <c r="H6" t="n">
-        <v>-108804080</v>
+        <v>12260500</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -8,776 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-3702664</v>
+        <v>3314976</v>
       </c>
       <c r="E7" t="n">
-        <v>12150162</v>
+        <v>3314976</v>
       </c>
       <c r="F7" t="n">
-        <v>2199194</v>
+        <v>-10549554</v>
       </c>
       <c r="G7" t="n">
-        <v>10974847</v>
+        <v>-10549554</v>
       </c>
       <c r="H7" t="n">
-        <v>462961420</v>
+        <v>-43020411</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 14,561 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-28100187</v>
+        <v>-2168260</v>
       </c>
       <c r="E8" t="n">
-        <v>-27146875</v>
+        <v>-2168260</v>
       </c>
       <c r="F8" t="n">
-        <v>-102323096</v>
+        <v>-14666067</v>
       </c>
       <c r="G8" t="n">
-        <v>-116883701</v>
+        <v>-14666067</v>
       </c>
       <c r="H8" t="n">
-        <v>150314901</v>
+        <v>6584269</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-22396</v>
+        <v>8376114</v>
       </c>
       <c r="E9" t="n">
-        <v>-95588</v>
+        <v>8376114</v>
       </c>
       <c r="F9" t="n">
-        <v>6596116</v>
+        <v>-11184678</v>
       </c>
       <c r="G9" t="n">
-        <v>7385846</v>
+        <v>-11184678</v>
       </c>
       <c r="H9" t="n">
-        <v>12260500</v>
+        <v>-82164231</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>3314976</v>
+        <v>-28100187</v>
       </c>
       <c r="E10" t="n">
-        <v>2979169</v>
+        <v>-28100187</v>
       </c>
       <c r="F10" t="n">
-        <v>-10549554</v>
+        <v>-102323096</v>
       </c>
       <c r="G10" t="n">
-        <v>-9506146</v>
+        <v>-102323096</v>
       </c>
       <c r="H10" t="n">
-        <v>-43020411</v>
+        <v>150314901</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,65 +793,65 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-2168260</v>
+        <v>-2961794</v>
       </c>
       <c r="E11" t="n">
-        <v>-1004107</v>
+        <v>-2961794</v>
       </c>
       <c r="F11" t="n">
-        <v>-14666067</v>
+        <v>-21607041</v>
       </c>
       <c r="G11" t="n">
-        <v>-12860211</v>
+        <v>-21607041</v>
       </c>
       <c r="H11" t="n">
-        <v>6584269</v>
+        <v>47422137</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>8376114</v>
+        <v>-11141148</v>
       </c>
       <c r="E12" t="n">
-        <v>4190684</v>
+        <v>-11141148</v>
       </c>
       <c r="F12" t="n">
-        <v>-11184678</v>
+        <v>-24135641</v>
       </c>
       <c r="G12" t="n">
-        <v>-14156943</v>
+        <v>-24135641</v>
       </c>
       <c r="H12" t="n">
-        <v>-82164231</v>
+        <v>77620746</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,100 +863,100 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-2961794</v>
+        <v>-23601689</v>
       </c>
       <c r="E13" t="n">
-        <v>-3202892</v>
+        <v>-23601689</v>
       </c>
       <c r="F13" t="n">
-        <v>-21607041</v>
+        <v>-12058135</v>
       </c>
       <c r="G13" t="n">
-        <v>-25111868</v>
+        <v>-12058135</v>
       </c>
       <c r="H13" t="n">
-        <v>47422137</v>
+        <v>72882967</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-11141148</v>
+        <v>1174981</v>
       </c>
       <c r="E14" t="n">
-        <v>-6953167</v>
+        <v>1174981</v>
       </c>
       <c r="F14" t="n">
-        <v>-24135641</v>
+        <v>-10719826</v>
       </c>
       <c r="G14" t="n">
-        <v>-24704220</v>
+        <v>-10719826</v>
       </c>
       <c r="H14" t="n">
-        <v>77620746</v>
+        <v>-11716392</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1174981</v>
+        <v>205305</v>
       </c>
       <c r="E15" t="n">
-        <v>1194409</v>
+        <v>205305</v>
       </c>
       <c r="F15" t="n">
-        <v>-10719826</v>
+        <v>-4294919</v>
       </c>
       <c r="G15" t="n">
-        <v>-11069427</v>
+        <v>-4294919</v>
       </c>
       <c r="H15" t="n">
-        <v>-11716392</v>
+        <v>-16587299</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,23 +968,23 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>205305</v>
+        <v>-3702664</v>
       </c>
       <c r="E16" t="n">
-        <v>433621</v>
+        <v>-3702664</v>
       </c>
       <c r="F16" t="n">
-        <v>-4294919</v>
+        <v>2199194</v>
       </c>
       <c r="G16" t="n">
-        <v>-5443885</v>
+        <v>2199194</v>
       </c>
       <c r="H16" t="n">
-        <v>-16587299</v>
+        <v>462961420</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
@@ -1006,13 +1006,13 @@
         <v>-343523</v>
       </c>
       <c r="E17" t="n">
-        <v>-48825</v>
+        <v>-343523</v>
       </c>
       <c r="F17" t="n">
         <v>3888813</v>
       </c>
       <c r="G17" t="n">
-        <v>3811875</v>
+        <v>3888813</v>
       </c>
       <c r="H17" t="n">
         <v>14567230</v>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -490,7 +490,7 @@
         <v>-30513770</v>
       </c>
       <c r="H2" t="n">
-        <v>60935525</v>
+        <v>85133794</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,245 +501,245 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-15842819</v>
+        <v>19645741</v>
       </c>
       <c r="E3" t="n">
-        <v>-15842819</v>
+        <v>19645741</v>
       </c>
       <c r="F3" t="n">
-        <v>7589057</v>
+        <v>-53584173</v>
       </c>
       <c r="G3" t="n">
-        <v>7589057</v>
+        <v>-53584173</v>
       </c>
       <c r="H3" t="n">
-        <v>-13511487</v>
+        <v>39066918</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>19645741</v>
+        <v>6854883</v>
       </c>
       <c r="E4" t="n">
-        <v>19645741</v>
+        <v>6854883</v>
       </c>
       <c r="F4" t="n">
-        <v>-53584173</v>
+        <v>-10489690</v>
       </c>
       <c r="G4" t="n">
-        <v>-53584173</v>
+        <v>-10489690</v>
       </c>
       <c r="H4" t="n">
-        <v>36384008</v>
+        <v>-90915788</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>6854883</v>
+        <v>-22396</v>
       </c>
       <c r="E5" t="n">
-        <v>6854883</v>
+        <v>-22396</v>
       </c>
       <c r="F5" t="n">
-        <v>-10489690</v>
+        <v>6596116</v>
       </c>
       <c r="G5" t="n">
-        <v>-10489690</v>
+        <v>6596116</v>
       </c>
       <c r="H5" t="n">
-        <v>-108804080</v>
+        <v>12664672</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-22396</v>
+        <v>3314976</v>
       </c>
       <c r="E6" t="n">
-        <v>-22396</v>
+        <v>3314976</v>
       </c>
       <c r="F6" t="n">
-        <v>6596116</v>
+        <v>-10549554</v>
       </c>
       <c r="G6" t="n">
-        <v>6596116</v>
+        <v>-10549554</v>
       </c>
       <c r="H6" t="n">
-        <v>12260500</v>
+        <v>-41406649</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>3314976</v>
+        <v>-2168260</v>
       </c>
       <c r="E7" t="n">
-        <v>3314976</v>
+        <v>-2168260</v>
       </c>
       <c r="F7" t="n">
-        <v>-10549554</v>
+        <v>-14666067</v>
       </c>
       <c r="G7" t="n">
-        <v>-10549554</v>
+        <v>-14666067</v>
       </c>
       <c r="H7" t="n">
-        <v>-43020411</v>
+        <v>6014182</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-2168260</v>
+        <v>8376114</v>
       </c>
       <c r="E8" t="n">
-        <v>-2168260</v>
+        <v>8376114</v>
       </c>
       <c r="F8" t="n">
-        <v>-14666067</v>
+        <v>-11184678</v>
       </c>
       <c r="G8" t="n">
-        <v>-14666067</v>
+        <v>-11184678</v>
       </c>
       <c r="H8" t="n">
-        <v>6584269</v>
+        <v>-81596439</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>8376114</v>
+        <v>-15842819</v>
       </c>
       <c r="E9" t="n">
-        <v>8376114</v>
+        <v>-15842819</v>
       </c>
       <c r="F9" t="n">
-        <v>-11184678</v>
+        <v>7589057</v>
       </c>
       <c r="G9" t="n">
-        <v>-11184678</v>
+        <v>7589057</v>
       </c>
       <c r="H9" t="n">
-        <v>-82164231</v>
+        <v>-3141643</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         <v>-102323096</v>
       </c>
       <c r="H10" t="n">
-        <v>150314901</v>
+        <v>148582238</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>-21607041</v>
       </c>
       <c r="H11" t="n">
-        <v>47422137</v>
+        <v>45390952</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>-24135641</v>
       </c>
       <c r="H12" t="n">
-        <v>77620746</v>
+        <v>108521747</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>-12058135</v>
       </c>
       <c r="H13" t="n">
-        <v>72882967</v>
+        <v>74220121</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>-10719826</v>
       </c>
       <c r="H14" t="n">
-        <v>-11716392</v>
+        <v>-11796117</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>-4294919</v>
       </c>
       <c r="H15" t="n">
-        <v>-16587299</v>
+        <v>-16535978</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>2199194</v>
       </c>
       <c r="H16" t="n">
-        <v>462961420</v>
+        <v>335514253</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>3888813</v>
       </c>
       <c r="H17" t="n">
-        <v>14567230</v>
+        <v>11171604</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,112 +466,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📈 20d 巨變(加碼 38,522 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>14909059</v>
+        <v>-15737743</v>
       </c>
       <c r="E2" t="n">
-        <v>14909059</v>
+        <v>19645741</v>
       </c>
       <c r="F2" t="n">
-        <v>-30513770</v>
+        <v>-15062067</v>
       </c>
       <c r="G2" t="n">
-        <v>-30513770</v>
+        <v>-53584173</v>
       </c>
       <c r="H2" t="n">
-        <v>85133794</v>
+        <v>53943968</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>19645741</v>
+        <v>-15042355</v>
       </c>
       <c r="E3" t="n">
-        <v>19645741</v>
+        <v>14909059</v>
       </c>
       <c r="F3" t="n">
-        <v>-53584173</v>
+        <v>-27459555</v>
       </c>
       <c r="G3" t="n">
-        <v>-53584173</v>
+        <v>-30513770</v>
       </c>
       <c r="H3" t="n">
-        <v>39066918</v>
+        <v>109347348</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 16,326 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>6854883</v>
+        <v>-16518093</v>
       </c>
       <c r="E4" t="n">
-        <v>6854883</v>
+        <v>-28100187</v>
       </c>
       <c r="F4" t="n">
-        <v>-10489690</v>
+        <v>-85997495</v>
       </c>
       <c r="G4" t="n">
-        <v>-10489690</v>
+        <v>-102323096</v>
       </c>
       <c r="H4" t="n">
-        <v>-90915788</v>
+        <v>146009046</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,65 +583,65 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>-22396</v>
+        <v>-1176797</v>
       </c>
       <c r="E5" t="n">
-        <v>-22396</v>
+        <v>-343523</v>
       </c>
       <c r="F5" t="n">
-        <v>6596116</v>
+        <v>5600198</v>
       </c>
       <c r="G5" t="n">
-        <v>6596116</v>
+        <v>3888813</v>
       </c>
       <c r="H5" t="n">
-        <v>12664672</v>
+        <v>10774486</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3314976</v>
+        <v>-2719624</v>
       </c>
       <c r="E6" t="n">
-        <v>3314976</v>
+        <v>-2168260</v>
       </c>
       <c r="F6" t="n">
-        <v>-10549554</v>
+        <v>-13863030</v>
       </c>
       <c r="G6" t="n">
-        <v>-10549554</v>
+        <v>-14666067</v>
       </c>
       <c r="H6" t="n">
-        <v>-41406649</v>
+        <v>5668086</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,373 +653,478 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-2168260</v>
+        <v>-3050749</v>
       </c>
       <c r="E7" t="n">
-        <v>-2168260</v>
+        <v>-2961794</v>
       </c>
       <c r="F7" t="n">
-        <v>-14666067</v>
+        <v>-28959290</v>
       </c>
       <c r="G7" t="n">
-        <v>-14666067</v>
+        <v>-21607041</v>
       </c>
       <c r="H7" t="n">
-        <v>6014182</v>
+        <v>40968871</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>8376114</v>
+        <v>-14889147</v>
       </c>
       <c r="E8" t="n">
-        <v>8376114</v>
+        <v>-11141148</v>
       </c>
       <c r="F8" t="n">
-        <v>-11184678</v>
+        <v>-24757674</v>
       </c>
       <c r="G8" t="n">
-        <v>-11184678</v>
+        <v>-24135641</v>
       </c>
       <c r="H8" t="n">
-        <v>-81596439</v>
+        <v>94641510</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-15842819</v>
+        <v>-13813015</v>
       </c>
       <c r="E9" t="n">
-        <v>-15842819</v>
+        <v>-23601689</v>
       </c>
       <c r="F9" t="n">
-        <v>7589057</v>
+        <v>-10159438</v>
       </c>
       <c r="G9" t="n">
-        <v>7589057</v>
+        <v>-12058135</v>
       </c>
       <c r="H9" t="n">
-        <v>-3141643</v>
+        <v>70612627</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-28100187</v>
+        <v>-1013390</v>
       </c>
       <c r="E10" t="n">
-        <v>-28100187</v>
+        <v>592109</v>
       </c>
       <c r="F10" t="n">
-        <v>-102323096</v>
+        <v>12606156</v>
       </c>
       <c r="G10" t="n">
-        <v>-102323096</v>
+        <v>13022540</v>
       </c>
       <c r="H10" t="n">
-        <v>148582238</v>
+        <v>89559555</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-2961794</v>
+        <v>1330590</v>
       </c>
       <c r="E11" t="n">
-        <v>-2961794</v>
+        <v>1174981</v>
       </c>
       <c r="F11" t="n">
-        <v>-21607041</v>
+        <v>-10891945</v>
       </c>
       <c r="G11" t="n">
-        <v>-21607041</v>
+        <v>-10719826</v>
       </c>
       <c r="H11" t="n">
-        <v>45390952</v>
+        <v>-11987610</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-11141148</v>
+        <v>-782310</v>
       </c>
       <c r="E12" t="n">
-        <v>-11141148</v>
+        <v>-22396</v>
       </c>
       <c r="F12" t="n">
-        <v>-24135641</v>
+        <v>4289417</v>
       </c>
       <c r="G12" t="n">
-        <v>-24135641</v>
+        <v>6596116</v>
       </c>
       <c r="H12" t="n">
-        <v>108521747</v>
+        <v>11881155</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-23601689</v>
+        <v>1247491</v>
       </c>
       <c r="E13" t="n">
-        <v>-23601689</v>
+        <v>2137431</v>
       </c>
       <c r="F13" t="n">
-        <v>-12058135</v>
+        <v>-15568</v>
       </c>
       <c r="G13" t="n">
-        <v>-12058135</v>
+        <v>1001763</v>
       </c>
       <c r="H13" t="n">
-        <v>74220121</v>
+        <v>-10207730</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -13,301 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>1174981</v>
+        <v>-9563828</v>
       </c>
       <c r="E14" t="n">
-        <v>1174981</v>
+        <v>8376114</v>
       </c>
       <c r="F14" t="n">
-        <v>-10719826</v>
+        <v>-24485996</v>
       </c>
       <c r="G14" t="n">
-        <v>-10719826</v>
+        <v>-11184678</v>
       </c>
       <c r="H14" t="n">
-        <v>-11796117</v>
+        <v>-94642736</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>205305</v>
+        <v>-2920851</v>
       </c>
       <c r="E15" t="n">
-        <v>205305</v>
+        <v>6854883</v>
       </c>
       <c r="F15" t="n">
-        <v>-4294919</v>
+        <v>-17257727</v>
       </c>
       <c r="G15" t="n">
-        <v>-4294919</v>
+        <v>-10489690</v>
       </c>
       <c r="H15" t="n">
-        <v>-16535978</v>
+        <v>-90437434</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-3702664</v>
+        <v>-2305552</v>
       </c>
       <c r="E16" t="n">
-        <v>-3702664</v>
+        <v>3314976</v>
       </c>
       <c r="F16" t="n">
-        <v>2199194</v>
+        <v>-14503614</v>
       </c>
       <c r="G16" t="n">
-        <v>2199194</v>
+        <v>-10549554</v>
       </c>
       <c r="H16" t="n">
-        <v>335514253</v>
+        <v>-43643908</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-343523</v>
+        <v>-556351</v>
       </c>
       <c r="E17" t="n">
-        <v>-343523</v>
+        <v>2578779</v>
       </c>
       <c r="F17" t="n">
-        <v>3888813</v>
+        <v>367800</v>
       </c>
       <c r="G17" t="n">
-        <v>3888813</v>
+        <v>532413</v>
       </c>
       <c r="H17" t="n">
-        <v>11171604</v>
+        <v>6184571</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>零壹</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>🟢 5d 翻綠</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4583502</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-3702664</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5531590</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2199194</v>
+      </c>
+      <c r="H18" t="n">
+        <v>324492577</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>🔴 5d 翻紅</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-97451</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2539038</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-755287</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-288033</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-761739</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-8823335</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-15842819</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9152518</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7589057</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-4484568</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>廣達</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -466,182 +466,182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📈 20d 巨變(加碼 38,522 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>-15737743</v>
+        <v>833462</v>
       </c>
       <c r="E2" t="n">
-        <v>19645741</v>
+        <v>-15042355</v>
       </c>
       <c r="F2" t="n">
-        <v>-15062067</v>
+        <v>-23353657</v>
       </c>
       <c r="G2" t="n">
-        <v>-53584173</v>
+        <v>-27459555</v>
       </c>
       <c r="H2" t="n">
-        <v>53943968</v>
+        <v>129761814</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-15042355</v>
+        <v>-11241120</v>
       </c>
       <c r="E3" t="n">
-        <v>14909059</v>
+        <v>-8823335</v>
       </c>
       <c r="F3" t="n">
-        <v>-27459555</v>
+        <v>2819593</v>
       </c>
       <c r="G3" t="n">
-        <v>-30513770</v>
+        <v>9152518</v>
       </c>
       <c r="H3" t="n">
-        <v>109347348</v>
+        <v>-12612898</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 16,326 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-16518093</v>
+        <v>-2790792</v>
       </c>
       <c r="E4" t="n">
-        <v>-28100187</v>
+        <v>1352246</v>
       </c>
       <c r="F4" t="n">
-        <v>-85997495</v>
+        <v>7831534</v>
       </c>
       <c r="G4" t="n">
-        <v>-102323096</v>
+        <v>8204270</v>
       </c>
       <c r="H4" t="n">
-        <v>146009046</v>
+        <v>12836115</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,384 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-1176797</v>
+        <v>870179</v>
       </c>
       <c r="E5" t="n">
-        <v>-343523</v>
+        <v>806127</v>
       </c>
       <c r="F5" t="n">
-        <v>5600198</v>
+        <v>-277821</v>
       </c>
       <c r="G5" t="n">
-        <v>3888813</v>
+        <v>9106449</v>
       </c>
       <c r="H5" t="n">
-        <v>10774486</v>
+        <v>26567583</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 8,488 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-2719624</v>
+        <v>-3476863</v>
       </c>
       <c r="E6" t="n">
-        <v>-2168260</v>
+        <v>-13813015</v>
       </c>
       <c r="F6" t="n">
-        <v>-13863030</v>
+        <v>-1671909</v>
       </c>
       <c r="G6" t="n">
-        <v>-14666067</v>
+        <v>-10159438</v>
       </c>
       <c r="H6" t="n">
-        <v>5668086</v>
+        <v>79513319</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,30 +653,30 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-3050749</v>
+        <v>-4404756</v>
       </c>
       <c r="E7" t="n">
-        <v>-2961794</v>
+        <v>-2719624</v>
       </c>
       <c r="F7" t="n">
-        <v>-28959290</v>
+        <v>-15115139</v>
       </c>
       <c r="G7" t="n">
-        <v>-21607041</v>
+        <v>-13863030</v>
       </c>
       <c r="H7" t="n">
-        <v>40968871</v>
+        <v>5097191</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,30 +688,30 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-14889147</v>
+        <v>-20464707</v>
       </c>
       <c r="E8" t="n">
-        <v>-11141148</v>
+        <v>-16518093</v>
       </c>
       <c r="F8" t="n">
-        <v>-24757674</v>
+        <v>-83192738</v>
       </c>
       <c r="G8" t="n">
-        <v>-24135641</v>
+        <v>-85997495</v>
       </c>
       <c r="H8" t="n">
-        <v>94641510</v>
+        <v>144441571</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,303 +723,303 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-13813015</v>
+        <v>-8747541</v>
       </c>
       <c r="E9" t="n">
-        <v>-23601689</v>
+        <v>-3050749</v>
       </c>
       <c r="F9" t="n">
-        <v>-10159438</v>
+        <v>-28521936</v>
       </c>
       <c r="G9" t="n">
-        <v>-12058135</v>
+        <v>-28959290</v>
       </c>
       <c r="H9" t="n">
-        <v>70612627</v>
+        <v>45324938</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1013390</v>
+        <v>-15933518</v>
       </c>
       <c r="E10" t="n">
-        <v>592109</v>
+        <v>-14889147</v>
       </c>
       <c r="F10" t="n">
-        <v>12606156</v>
+        <v>-31911406</v>
       </c>
       <c r="G10" t="n">
-        <v>13022540</v>
+        <v>-24757674</v>
       </c>
       <c r="H10" t="n">
-        <v>89559555</v>
+        <v>84477100</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1330590</v>
+        <v>-452608</v>
       </c>
       <c r="E11" t="n">
-        <v>1174981</v>
+        <v>-1013390</v>
       </c>
       <c r="F11" t="n">
-        <v>-10891945</v>
+        <v>12366962</v>
       </c>
       <c r="G11" t="n">
-        <v>-10719826</v>
+        <v>12606156</v>
       </c>
       <c r="H11" t="n">
-        <v>-11987610</v>
+        <v>87631282</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-782310</v>
+        <v>541905</v>
       </c>
       <c r="E12" t="n">
-        <v>-22396</v>
+        <v>1330590</v>
       </c>
       <c r="F12" t="n">
-        <v>4289417</v>
+        <v>-11143936</v>
       </c>
       <c r="G12" t="n">
-        <v>6596116</v>
+        <v>-10891945</v>
       </c>
       <c r="H12" t="n">
-        <v>11881155</v>
+        <v>-12572615</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1247491</v>
+        <v>-1064182</v>
       </c>
       <c r="E13" t="n">
-        <v>2137431</v>
+        <v>1549655</v>
       </c>
       <c r="F13" t="n">
-        <v>-15568</v>
+        <v>9411377</v>
       </c>
       <c r="G13" t="n">
-        <v>1001763</v>
+        <v>9881382</v>
       </c>
       <c r="H13" t="n">
-        <v>-10207730</v>
+        <v>-2650697</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -13,301 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-9563828</v>
+        <v>-1481909</v>
       </c>
       <c r="E14" t="n">
-        <v>8376114</v>
+        <v>-782310</v>
       </c>
       <c r="F14" t="n">
-        <v>-24485996</v>
+        <v>1032347</v>
       </c>
       <c r="G14" t="n">
-        <v>-11184678</v>
+        <v>4289417</v>
       </c>
       <c r="H14" t="n">
-        <v>-94642736</v>
+        <v>10469769</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-2920851</v>
+        <v>362223</v>
       </c>
       <c r="E15" t="n">
-        <v>6854883</v>
+        <v>-637282</v>
       </c>
       <c r="F15" t="n">
-        <v>-17257727</v>
+        <v>-4222703</v>
       </c>
       <c r="G15" t="n">
-        <v>-10489690</v>
+        <v>-4951283</v>
       </c>
       <c r="H15" t="n">
-        <v>-90437434</v>
+        <v>-26377645</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 24,183 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-2305552</v>
+        <v>45185704</v>
       </c>
       <c r="E16" t="n">
-        <v>3314976</v>
+        <v>-15737743</v>
       </c>
       <c r="F16" t="n">
-        <v>-14503614</v>
+        <v>9121095</v>
       </c>
       <c r="G16" t="n">
-        <v>-10549554</v>
+        <v>-15062067</v>
       </c>
       <c r="H16" t="n">
-        <v>-43643908</v>
+        <v>120031551</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-556351</v>
+        <v>-1026252</v>
       </c>
       <c r="E17" t="n">
-        <v>2578779</v>
+        <v>-1176797</v>
       </c>
       <c r="F17" t="n">
-        <v>367800</v>
+        <v>5192797</v>
       </c>
       <c r="G17" t="n">
-        <v>532413</v>
+        <v>5600198</v>
       </c>
       <c r="H17" t="n">
-        <v>6184571</v>
+        <v>8675461</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
@@ -1031,26 +1031,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>📈 20d 巨變(加碼 11,567 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
+        <v>15028660</v>
+      </c>
+      <c r="E18" t="n">
         <v>4583502</v>
       </c>
-      <c r="E18" t="n">
-        <v>-3702664</v>
-      </c>
       <c r="F18" t="n">
+        <v>17098670</v>
+      </c>
+      <c r="G18" t="n">
         <v>5531590</v>
       </c>
-      <c r="G18" t="n">
-        <v>2199194</v>
-      </c>
       <c r="H18" t="n">
-        <v>324492577</v>
+        <v>320056959</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1061,70 +1061,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>📈 20d 巨變(加碼 13,364 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-97451</v>
+        <v>-10823713</v>
       </c>
       <c r="E19" t="n">
-        <v>2539038</v>
+        <v>-9563828</v>
       </c>
       <c r="F19" t="n">
-        <v>-755287</v>
+        <v>-11122236</v>
       </c>
       <c r="G19" t="n">
-        <v>-288033</v>
+        <v>-24485996</v>
       </c>
       <c r="H19" t="n">
-        <v>-761739</v>
+        <v>-92331351</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📈 20d 巨變(加碼 11,904 千)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-8823335</v>
+        <v>16635189</v>
       </c>
       <c r="E20" t="n">
-        <v>-15842819</v>
+        <v>18793616</v>
       </c>
       <c r="F20" t="n">
-        <v>9152518</v>
+        <v>59819944</v>
       </c>
       <c r="G20" t="n">
-        <v>7589057</v>
+        <v>47916434</v>
       </c>
       <c r="H20" t="n">
-        <v>-4484568</v>
+        <v>37158513</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,175 +466,175 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 28,041 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>833462</v>
+        <v>39415097</v>
       </c>
       <c r="E2" t="n">
-        <v>-15042355</v>
+        <v>-20464707</v>
       </c>
       <c r="F2" t="n">
-        <v>-23353657</v>
+        <v>-55151855</v>
       </c>
       <c r="G2" t="n">
-        <v>-27459555</v>
+        <v>-83192738</v>
       </c>
       <c r="H2" t="n">
-        <v>129761814</v>
+        <v>173771945</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 13,370 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-11241120</v>
+        <v>4698799</v>
       </c>
       <c r="E3" t="n">
-        <v>-8823335</v>
+        <v>-10823713</v>
       </c>
       <c r="F3" t="n">
-        <v>2819593</v>
+        <v>2247918</v>
       </c>
       <c r="G3" t="n">
-        <v>9152518</v>
+        <v>-11122236</v>
       </c>
       <c r="H3" t="n">
-        <v>-12612898</v>
+        <v>-68937599</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-2790792</v>
+        <v>2512473</v>
       </c>
       <c r="E4" t="n">
-        <v>1352246</v>
+        <v>-4907761</v>
       </c>
       <c r="F4" t="n">
-        <v>7831534</v>
+        <v>-14641026</v>
       </c>
       <c r="G4" t="n">
-        <v>8204270</v>
+        <v>-12000893</v>
       </c>
       <c r="H4" t="n">
-        <v>12836115</v>
+        <v>-42460146</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,384 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -8,382 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>870179</v>
+        <v>-5196198</v>
       </c>
       <c r="E5" t="n">
-        <v>806127</v>
+        <v>-3476863</v>
       </c>
       <c r="F5" t="n">
-        <v>-277821</v>
+        <v>-10053901</v>
       </c>
       <c r="G5" t="n">
-        <v>9106449</v>
+        <v>-1671909</v>
       </c>
       <c r="H5" t="n">
-        <v>26567583</v>
+        <v>84605454</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 8,488 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-3476863</v>
+        <v>702668</v>
       </c>
       <c r="E6" t="n">
-        <v>-13813015</v>
+        <v>870179</v>
       </c>
       <c r="F6" t="n">
-        <v>-1671909</v>
+        <v>-779564</v>
       </c>
       <c r="G6" t="n">
-        <v>-10159438</v>
+        <v>-277821</v>
       </c>
       <c r="H6" t="n">
-        <v>79513319</v>
+        <v>27019701</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
@@ -653,19 +653,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
+        <v>-3998099</v>
+      </c>
+      <c r="E7" t="n">
         <v>-4404756</v>
       </c>
-      <c r="E7" t="n">
-        <v>-2719624</v>
-      </c>
       <c r="F7" t="n">
+        <v>-13559737</v>
+      </c>
+      <c r="G7" t="n">
         <v>-15115139</v>
       </c>
-      <c r="G7" t="n">
-        <v>-13863030</v>
-      </c>
       <c r="H7" t="n">
-        <v>5097191</v>
+        <v>5143023</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,30 +688,30 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-20464707</v>
+        <v>-7967959</v>
       </c>
       <c r="E8" t="n">
-        <v>-16518093</v>
+        <v>-8747541</v>
       </c>
       <c r="F8" t="n">
-        <v>-83192738</v>
+        <v>-24354710</v>
       </c>
       <c r="G8" t="n">
-        <v>-85997495</v>
+        <v>-28521936</v>
       </c>
       <c r="H8" t="n">
-        <v>144441571</v>
+        <v>46323985</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,58 +723,58 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-8747541</v>
+        <v>-17228299</v>
       </c>
       <c r="E9" t="n">
-        <v>-3050749</v>
+        <v>-15933518</v>
       </c>
       <c r="F9" t="n">
-        <v>-28521936</v>
+        <v>-36108997</v>
       </c>
       <c r="G9" t="n">
-        <v>-28959290</v>
+        <v>-31911406</v>
       </c>
       <c r="H9" t="n">
-        <v>45324938</v>
+        <v>81603162</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-15933518</v>
+        <v>-4904480</v>
       </c>
       <c r="E10" t="n">
-        <v>-14889147</v>
+        <v>-2790792</v>
       </c>
       <c r="F10" t="n">
-        <v>-31911406</v>
+        <v>7599125</v>
       </c>
       <c r="G10" t="n">
-        <v>-24757674</v>
+        <v>7831534</v>
       </c>
       <c r="H10" t="n">
-        <v>84477100</v>
+        <v>12264231</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
+        <v>-149956</v>
+      </c>
+      <c r="E11" t="n">
         <v>-452608</v>
       </c>
-      <c r="E11" t="n">
-        <v>-1013390</v>
-      </c>
       <c r="F11" t="n">
+        <v>12114833</v>
+      </c>
+      <c r="G11" t="n">
         <v>12366962</v>
       </c>
-      <c r="G11" t="n">
-        <v>12606156</v>
-      </c>
       <c r="H11" t="n">
-        <v>87631282</v>
+        <v>87786062</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -816,77 +816,77 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>541905</v>
+        <v>-3540487</v>
       </c>
       <c r="E12" t="n">
-        <v>1330590</v>
+        <v>1554938</v>
       </c>
       <c r="F12" t="n">
-        <v>-11143936</v>
+        <v>6419649</v>
       </c>
       <c r="G12" t="n">
-        <v>-10891945</v>
+        <v>8749268</v>
       </c>
       <c r="H12" t="n">
-        <v>-12572615</v>
+        <v>-1866986</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-1064182</v>
+        <v>168527</v>
       </c>
       <c r="E13" t="n">
-        <v>1549655</v>
+        <v>362223</v>
       </c>
       <c r="F13" t="n">
-        <v>9411377</v>
+        <v>-4734152</v>
       </c>
       <c r="G13" t="n">
-        <v>9881382</v>
+        <v>-4222703</v>
       </c>
       <c r="H13" t="n">
-        <v>-2650697</v>
+        <v>-26474756</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,58 +898,58 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-1481909</v>
+        <v>194719</v>
       </c>
       <c r="E14" t="n">
-        <v>-782310</v>
+        <v>-147407</v>
       </c>
       <c r="F14" t="n">
-        <v>1032347</v>
+        <v>-1324540</v>
       </c>
       <c r="G14" t="n">
-        <v>4289417</v>
+        <v>-1210962</v>
       </c>
       <c r="H14" t="n">
-        <v>10469769</v>
+        <v>-16188573</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>📈 20d 巨變(加碼 39,743 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>362223</v>
+        <v>24279611</v>
       </c>
       <c r="E15" t="n">
-        <v>-637282</v>
+        <v>833462</v>
       </c>
       <c r="F15" t="n">
-        <v>-4222703</v>
+        <v>16389116</v>
       </c>
       <c r="G15" t="n">
-        <v>-4951283</v>
+        <v>-23353657</v>
       </c>
       <c r="H15" t="n">
-        <v>-26377645</v>
+        <v>130763193</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
@@ -961,170 +961,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 24,183 千)</t>
+          <t>📈 20d 巨變(加碼 73,020 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>54190903</v>
+      </c>
+      <c r="E16" t="n">
         <v>45185704</v>
       </c>
-      <c r="E16" t="n">
-        <v>-15737743</v>
-      </c>
       <c r="F16" t="n">
+        <v>82141541</v>
+      </c>
+      <c r="G16" t="n">
         <v>9121095</v>
       </c>
-      <c r="G16" t="n">
-        <v>-15062067</v>
-      </c>
       <c r="H16" t="n">
-        <v>120031551</v>
+        <v>136820438</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>華邦電</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2472</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-1026252</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-1176797</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5192797</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5600198</v>
-      </c>
-      <c r="H17" t="n">
-        <v>8675461</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>立隆電</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 11,567 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>15028660</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4583502</v>
-      </c>
-      <c r="F18" t="n">
-        <v>17098670</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5531590</v>
-      </c>
-      <c r="H18" t="n">
-        <v>320056959</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 13,364 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-10823713</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-9563828</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-11122236</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-24485996</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-92331351</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 11,904 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16635189</v>
-      </c>
-      <c r="E20" t="n">
-        <v>18793616</v>
-      </c>
-      <c r="F20" t="n">
-        <v>59819944</v>
-      </c>
-      <c r="G20" t="n">
-        <v>47916434</v>
-      </c>
-      <c r="H20" t="n">
-        <v>37158513</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 28,041 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -28,235 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
+        <v>22267600</v>
+      </c>
+      <c r="E2" t="n">
         <v>39415097</v>
       </c>
-      <c r="E2" t="n">
-        <v>-20464707</v>
-      </c>
       <c r="F2" t="n">
+        <v>-83386572</v>
+      </c>
+      <c r="G2" t="n">
         <v>-55151855</v>
       </c>
-      <c r="G2" t="n">
-        <v>-83192738</v>
-      </c>
       <c r="H2" t="n">
-        <v>173771945</v>
+        <v>152603134</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,105 +501,105 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 13,370 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>4698799</v>
+        <v>-6037984</v>
       </c>
       <c r="E3" t="n">
-        <v>-10823713</v>
+        <v>4753667</v>
       </c>
       <c r="F3" t="n">
-        <v>2247918</v>
+        <v>13355396</v>
       </c>
       <c r="G3" t="n">
-        <v>-11122236</v>
+        <v>11117925</v>
       </c>
       <c r="H3" t="n">
-        <v>-68937599</v>
+        <v>316819428</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 13,932 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2512473</v>
+        <v>7118515</v>
       </c>
       <c r="E4" t="n">
-        <v>-4907761</v>
+        <v>4698799</v>
       </c>
       <c r="F4" t="n">
-        <v>-14641026</v>
+        <v>16179727</v>
       </c>
       <c r="G4" t="n">
-        <v>-12000893</v>
+        <v>2247918</v>
       </c>
       <c r="H4" t="n">
-        <v>-42460146</v>
+        <v>-71724109</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -8,382 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,078 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-5196198</v>
+        <v>-19373067</v>
       </c>
       <c r="E5" t="n">
-        <v>-3476863</v>
+        <v>-17228299</v>
       </c>
       <c r="F5" t="n">
-        <v>-10053901</v>
+        <v>-45187258</v>
       </c>
       <c r="G5" t="n">
-        <v>-1671909</v>
+        <v>-36108997</v>
       </c>
       <c r="H5" t="n">
-        <v>84605454</v>
+        <v>75603707</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
@@ -618,19 +618,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
+        <v>744092</v>
+      </c>
+      <c r="E6" t="n">
         <v>702668</v>
       </c>
-      <c r="E6" t="n">
-        <v>870179</v>
-      </c>
       <c r="F6" t="n">
+        <v>-251248</v>
+      </c>
+      <c r="G6" t="n">
         <v>-779564</v>
       </c>
-      <c r="G6" t="n">
-        <v>-277821</v>
-      </c>
       <c r="H6" t="n">
-        <v>27019701</v>
+        <v>27104270</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
+        <v>-4884032</v>
+      </c>
+      <c r="E7" t="n">
         <v>-3998099</v>
       </c>
-      <c r="E7" t="n">
-        <v>-4404756</v>
-      </c>
       <c r="F7" t="n">
+        <v>-15630684</v>
+      </c>
+      <c r="G7" t="n">
         <v>-13559737</v>
       </c>
-      <c r="G7" t="n">
-        <v>-15115139</v>
-      </c>
       <c r="H7" t="n">
-        <v>5143023</v>
+        <v>3873068</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
+        <v>-8243638</v>
+      </c>
+      <c r="E8" t="n">
         <v>-7967959</v>
       </c>
-      <c r="E8" t="n">
-        <v>-8747541</v>
-      </c>
       <c r="F8" t="n">
+        <v>-29665766</v>
+      </c>
+      <c r="G8" t="n">
         <v>-24354710</v>
       </c>
-      <c r="G8" t="n">
-        <v>-28521936</v>
-      </c>
       <c r="H8" t="n">
-        <v>46323985</v>
+        <v>44085887</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,23 +723,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-17228299</v>
+        <v>-26203536</v>
       </c>
       <c r="E9" t="n">
-        <v>-15933518</v>
+        <v>-5196198</v>
       </c>
       <c r="F9" t="n">
-        <v>-36108997</v>
+        <v>-16781290</v>
       </c>
       <c r="G9" t="n">
-        <v>-31911406</v>
+        <v>-10053901</v>
       </c>
       <c r="H9" t="n">
-        <v>81603162</v>
+        <v>69458870</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
+        <v>-6872572</v>
+      </c>
+      <c r="E10" t="n">
         <v>-4904480</v>
       </c>
-      <c r="E10" t="n">
-        <v>-2790792</v>
-      </c>
       <c r="F10" t="n">
+        <v>7349209</v>
+      </c>
+      <c r="G10" t="n">
         <v>7599125</v>
       </c>
-      <c r="G10" t="n">
-        <v>7831534</v>
-      </c>
       <c r="H10" t="n">
-        <v>12264231</v>
+        <v>10792556</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -781,77 +781,77 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-149956</v>
+        <v>615903</v>
       </c>
       <c r="E11" t="n">
-        <v>-452608</v>
+        <v>168527</v>
       </c>
       <c r="F11" t="n">
-        <v>12114833</v>
+        <v>-4034439</v>
       </c>
       <c r="G11" t="n">
-        <v>12366962</v>
+        <v>-4734152</v>
       </c>
       <c r="H11" t="n">
-        <v>87786062</v>
+        <v>-26045347</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-3540487</v>
+        <v>915891</v>
       </c>
       <c r="E12" t="n">
-        <v>1554938</v>
+        <v>-85616</v>
       </c>
       <c r="F12" t="n">
-        <v>6419649</v>
+        <v>-4891473</v>
       </c>
       <c r="G12" t="n">
-        <v>8749268</v>
+        <v>-8212150</v>
       </c>
       <c r="H12" t="n">
-        <v>-1866986</v>
+        <v>-21842494</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,126 +863,161 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>168527</v>
+        <v>186058</v>
       </c>
       <c r="E13" t="n">
-        <v>362223</v>
+        <v>194719</v>
       </c>
       <c r="F13" t="n">
-        <v>-4734152</v>
+        <v>-1728660</v>
       </c>
       <c r="G13" t="n">
-        <v>-4222703</v>
+        <v>-1324540</v>
       </c>
       <c r="H13" t="n">
-        <v>-26474756</v>
+        <v>-16356379</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>194719</v>
+        <v>-10524864</v>
       </c>
       <c r="E14" t="n">
-        <v>-147407</v>
+        <v>2512473</v>
       </c>
       <c r="F14" t="n">
-        <v>-1324540</v>
+        <v>-8568017</v>
       </c>
       <c r="G14" t="n">
-        <v>-1210962</v>
+        <v>-14641026</v>
       </c>
       <c r="H14" t="n">
-        <v>-16188573</v>
+        <v>-48374120</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 39,743 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>24279611</v>
+        <v>-1330791</v>
       </c>
       <c r="E15" t="n">
-        <v>833462</v>
+        <v>264563</v>
       </c>
       <c r="F15" t="n">
-        <v>16389116</v>
+        <v>7704927</v>
       </c>
       <c r="G15" t="n">
-        <v>-23353657</v>
+        <v>8876076</v>
       </c>
       <c r="H15" t="n">
-        <v>130763193</v>
+        <v>-3772797</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1474045</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-3540487</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7823539</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6419649</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-187750</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>全友</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2344</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 73,020 千)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -12,758 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
+        <v>46202315</v>
+      </c>
+      <c r="E17" t="n">
         <v>54190903</v>
       </c>
-      <c r="E16" t="n">
-        <v>45185704</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="F17" t="n">
+        <v>69383598</v>
+      </c>
+      <c r="G17" t="n">
         <v>82141541</v>
       </c>
-      <c r="G16" t="n">
-        <v>9121095</v>
-      </c>
-      <c r="H16" t="n">
-        <v>136820438</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H17" t="n">
+        <v>138956009</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -466,525 +466,525 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -28,235 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 13,675 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>22267600</v>
+        <v>5980502</v>
       </c>
       <c r="E2" t="n">
-        <v>39415097</v>
+        <v>-8243638</v>
       </c>
       <c r="F2" t="n">
-        <v>-83386572</v>
+        <v>-15990706</v>
       </c>
       <c r="G2" t="n">
-        <v>-55151855</v>
+        <v>-29665766</v>
       </c>
       <c r="H2" t="n">
-        <v>152603134</v>
+        <v>43777148</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-6037984</v>
+        <v>5977639</v>
       </c>
       <c r="E3" t="n">
-        <v>4753667</v>
+        <v>-10524864</v>
       </c>
       <c r="F3" t="n">
-        <v>13355396</v>
+        <v>-1394058</v>
       </c>
       <c r="G3" t="n">
-        <v>11117925</v>
+        <v>-8568017</v>
       </c>
       <c r="H3" t="n">
-        <v>316819428</v>
+        <v>-35426423</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 13,932 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7118515</v>
+        <v>6606027</v>
       </c>
       <c r="E4" t="n">
-        <v>4698799</v>
+        <v>-5119278</v>
       </c>
       <c r="F4" t="n">
-        <v>16179727</v>
+        <v>-4156531</v>
       </c>
       <c r="G4" t="n">
-        <v>2247918</v>
+        <v>-9249124</v>
       </c>
       <c r="H4" t="n">
-        <v>-71724109</v>
+        <v>-29064793</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,078 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>-19373067</v>
+        <v>27642933</v>
       </c>
       <c r="E5" t="n">
-        <v>-17228299</v>
+        <v>22267600</v>
       </c>
       <c r="F5" t="n">
-        <v>-45187258</v>
+        <v>-88746614</v>
       </c>
       <c r="G5" t="n">
-        <v>-36108997</v>
+        <v>-83386572</v>
       </c>
       <c r="H5" t="n">
-        <v>75603707</v>
+        <v>51417920</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -26,559 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>744092</v>
+        <v>7828725</v>
       </c>
       <c r="E6" t="n">
-        <v>702668</v>
+        <v>7118515</v>
       </c>
       <c r="F6" t="n">
-        <v>-251248</v>
+        <v>-10379320</v>
       </c>
       <c r="G6" t="n">
-        <v>-779564</v>
+        <v>16179727</v>
       </c>
       <c r="H6" t="n">
-        <v>27104270</v>
+        <v>-78620875</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -20,401 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-4884032</v>
+        <v>-17286836</v>
       </c>
       <c r="E7" t="n">
-        <v>-3998099</v>
+        <v>-19373067</v>
       </c>
       <c r="F7" t="n">
-        <v>-15630684</v>
+        <v>-65588464</v>
       </c>
       <c r="G7" t="n">
-        <v>-13559737</v>
+        <v>-45187258</v>
       </c>
       <c r="H7" t="n">
-        <v>3873068</v>
+        <v>30346507</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-8243638</v>
+        <v>1066416</v>
       </c>
       <c r="E8" t="n">
-        <v>-7967959</v>
+        <v>615903</v>
       </c>
       <c r="F8" t="n">
-        <v>-29665766</v>
+        <v>-4502910</v>
       </c>
       <c r="G8" t="n">
-        <v>-24354710</v>
+        <v>-4034439</v>
       </c>
       <c r="H8" t="n">
-        <v>44085887</v>
+        <v>-23744753</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-26203536</v>
+        <v>7837351</v>
       </c>
       <c r="E9" t="n">
-        <v>-5196198</v>
+        <v>-6037984</v>
       </c>
       <c r="F9" t="n">
-        <v>-16781290</v>
+        <v>5572399</v>
       </c>
       <c r="G9" t="n">
-        <v>-10053901</v>
+        <v>13355396</v>
       </c>
       <c r="H9" t="n">
-        <v>69458870</v>
+        <v>265535726</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-6872572</v>
+        <v>-1026071</v>
       </c>
       <c r="E10" t="n">
-        <v>-4904480</v>
+        <v>-1330791</v>
       </c>
       <c r="F10" t="n">
-        <v>7349209</v>
+        <v>6039260</v>
       </c>
       <c r="G10" t="n">
-        <v>7599125</v>
+        <v>7704927</v>
       </c>
       <c r="H10" t="n">
-        <v>10792556</v>
+        <v>-4840695</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>615903</v>
+        <v>-5604784</v>
       </c>
       <c r="E11" t="n">
-        <v>168527</v>
+        <v>-1474045</v>
       </c>
       <c r="F11" t="n">
-        <v>-4034439</v>
+        <v>6963905</v>
       </c>
       <c r="G11" t="n">
-        <v>-4734152</v>
+        <v>7823539</v>
       </c>
       <c r="H11" t="n">
-        <v>-26045347</v>
+        <v>-1599304</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>915891</v>
+        <v>-5644501</v>
       </c>
       <c r="E12" t="n">
-        <v>-85616</v>
+        <v>-6872572</v>
       </c>
       <c r="F12" t="n">
-        <v>-4891473</v>
+        <v>3027543</v>
       </c>
       <c r="G12" t="n">
-        <v>-8212150</v>
+        <v>7349209</v>
       </c>
       <c r="H12" t="n">
-        <v>-21842494</v>
+        <v>6924568</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>📉 20d 巨變(減碼 -11,870 千)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>186058</v>
+        <v>3248723</v>
       </c>
       <c r="E13" t="n">
-        <v>194719</v>
+        <v>5487491</v>
       </c>
       <c r="F13" t="n">
-        <v>-1728660</v>
+        <v>30034664</v>
       </c>
       <c r="G13" t="n">
-        <v>-1324540</v>
+        <v>41904652</v>
       </c>
       <c r="H13" t="n">
-        <v>-16356379</v>
+        <v>135803515</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>📈 20d 巨變(加碼 37,844 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10524864</v>
+        <v>23799650</v>
       </c>
       <c r="E14" t="n">
-        <v>2512473</v>
+        <v>2254390</v>
       </c>
       <c r="F14" t="n">
-        <v>-8568017</v>
+        <v>60575199</v>
       </c>
       <c r="G14" t="n">
-        <v>-14641026</v>
+        <v>22731641</v>
       </c>
       <c r="H14" t="n">
-        <v>-48374120</v>
+        <v>143341552</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📉 20d 巨變(減碼 -17,381 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1330791</v>
+        <v>-11881299</v>
       </c>
       <c r="E15" t="n">
-        <v>264563</v>
+        <v>-13871695</v>
       </c>
       <c r="F15" t="n">
-        <v>7704927</v>
+        <v>-23332024</v>
       </c>
       <c r="G15" t="n">
-        <v>8876076</v>
+        <v>-5951370</v>
       </c>
       <c r="H15" t="n">
-        <v>-3772797</v>
+        <v>-28468405</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📉 20d 巨變(減碼 -30,995 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1474045</v>
+        <v>-12332291</v>
       </c>
       <c r="E16" t="n">
-        <v>-3540487</v>
+        <v>-26203536</v>
       </c>
       <c r="F16" t="n">
-        <v>7823539</v>
+        <v>-47776682</v>
       </c>
       <c r="G16" t="n">
-        <v>6419649</v>
+        <v>-16781290</v>
       </c>
       <c r="H16" t="n">
-        <v>-187750</v>
+        <v>-1582093</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
@@ -996,26 +996,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12,758 千)</t>
+          <t>📈 20d 巨變(加碼 50,723 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
+        <v>85976382</v>
+      </c>
+      <c r="E17" t="n">
         <v>46202315</v>
       </c>
-      <c r="E17" t="n">
-        <v>54190903</v>
-      </c>
       <c r="F17" t="n">
+        <v>120106560</v>
+      </c>
+      <c r="G17" t="n">
         <v>69383598</v>
       </c>
-      <c r="G17" t="n">
-        <v>82141541</v>
-      </c>
       <c r="H17" t="n">
-        <v>138956009</v>
+        <v>163908492</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 13,675 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 11,043 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
+        <v>11341415</v>
+      </c>
+      <c r="E2" t="n">
         <v>5980502</v>
       </c>
-      <c r="E2" t="n">
-        <v>-8243638</v>
-      </c>
       <c r="F2" t="n">
+        <v>-4947331</v>
+      </c>
+      <c r="G2" t="n">
         <v>-15990706</v>
       </c>
-      <c r="G2" t="n">
-        <v>-29665766</v>
-      </c>
       <c r="H2" t="n">
-        <v>43777148</v>
+        <v>46409522</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,523 +501,558 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>5977639</v>
+        <v>-3986052</v>
       </c>
       <c r="E3" t="n">
-        <v>-10524864</v>
+        <v>7837351</v>
       </c>
       <c r="F3" t="n">
-        <v>-1394058</v>
+        <v>9804512</v>
       </c>
       <c r="G3" t="n">
-        <v>-8568017</v>
+        <v>5572399</v>
       </c>
       <c r="H3" t="n">
-        <v>-35426423</v>
+        <v>249672320</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6606027</v>
+        <v>20264031</v>
       </c>
       <c r="E4" t="n">
-        <v>-5119278</v>
+        <v>27642933</v>
       </c>
       <c r="F4" t="n">
-        <v>-4156531</v>
+        <v>-87353388</v>
       </c>
       <c r="G4" t="n">
-        <v>-9249124</v>
+        <v>-88746614</v>
       </c>
       <c r="H4" t="n">
-        <v>-29064793</v>
+        <v>9757141</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -17,299 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>27642933</v>
+        <v>4111694</v>
       </c>
       <c r="E5" t="n">
-        <v>22267600</v>
+        <v>5977639</v>
       </c>
       <c r="F5" t="n">
-        <v>-88746614</v>
+        <v>-18692723</v>
       </c>
       <c r="G5" t="n">
-        <v>-83386572</v>
+        <v>-1394058</v>
       </c>
       <c r="H5" t="n">
-        <v>51417920</v>
+        <v>-26953168</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -26,559 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>7828725</v>
+        <v>4273686</v>
       </c>
       <c r="E6" t="n">
-        <v>7118515</v>
+        <v>6606027</v>
       </c>
       <c r="F6" t="n">
-        <v>-10379320</v>
+        <v>-6410766</v>
       </c>
       <c r="G6" t="n">
-        <v>16179727</v>
+        <v>-4156531</v>
       </c>
       <c r="H6" t="n">
-        <v>-78620875</v>
+        <v>-29717399</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -20,401 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-17286836</v>
+        <v>1108436</v>
       </c>
       <c r="E7" t="n">
-        <v>-19373067</v>
+        <v>307351</v>
       </c>
       <c r="F7" t="n">
-        <v>-65588464</v>
+        <v>-678624</v>
       </c>
       <c r="G7" t="n">
-        <v>-45187258</v>
+        <v>-2331457</v>
       </c>
       <c r="H7" t="n">
-        <v>30346507</v>
+        <v>10978898</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1066416</v>
+        <v>9460411</v>
       </c>
       <c r="E8" t="n">
-        <v>615903</v>
+        <v>7828725</v>
       </c>
       <c r="F8" t="n">
-        <v>-4502910</v>
+        <v>-15300182</v>
       </c>
       <c r="G8" t="n">
-        <v>-4034439</v>
+        <v>-10379320</v>
       </c>
       <c r="H8" t="n">
-        <v>-23744753</v>
+        <v>-78572612</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>7837351</v>
+        <v>-19215588</v>
       </c>
       <c r="E9" t="n">
-        <v>-6037984</v>
+        <v>-17286836</v>
       </c>
       <c r="F9" t="n">
-        <v>5572399</v>
+        <v>-58295386</v>
       </c>
       <c r="G9" t="n">
-        <v>13355396</v>
+        <v>-65588464</v>
       </c>
       <c r="H9" t="n">
-        <v>265535726</v>
+        <v>22619606</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1026071</v>
+        <v>2078384</v>
       </c>
       <c r="E10" t="n">
-        <v>-1330791</v>
+        <v>-125379</v>
       </c>
       <c r="F10" t="n">
-        <v>6039260</v>
+        <v>-960047</v>
       </c>
       <c r="G10" t="n">
-        <v>7704927</v>
+        <v>-3354630</v>
       </c>
       <c r="H10" t="n">
-        <v>-4840695</v>
+        <v>-20435321</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-5604784</v>
+        <v>848650</v>
       </c>
       <c r="E11" t="n">
-        <v>-1474045</v>
+        <v>-362051</v>
       </c>
       <c r="F11" t="n">
-        <v>6963905</v>
+        <v>-1134216</v>
       </c>
       <c r="G11" t="n">
-        <v>7823539</v>
+        <v>-2448542</v>
       </c>
       <c r="H11" t="n">
-        <v>-1599304</v>
+        <v>-15982770</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-5644501</v>
+        <v>1306524</v>
       </c>
       <c r="E12" t="n">
-        <v>-6872572</v>
+        <v>1066416</v>
       </c>
       <c r="F12" t="n">
-        <v>3027543</v>
+        <v>-2708282</v>
       </c>
       <c r="G12" t="n">
-        <v>7349209</v>
+        <v>-4502910</v>
       </c>
       <c r="H12" t="n">
-        <v>6924568</v>
+        <v>-22107125</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11,870 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3248723</v>
+        <v>-1337903</v>
       </c>
       <c r="E13" t="n">
-        <v>5487491</v>
+        <v>1392398</v>
       </c>
       <c r="F13" t="n">
-        <v>30034664</v>
+        <v>-2725104</v>
       </c>
       <c r="G13" t="n">
-        <v>41904652</v>
+        <v>-1205682</v>
       </c>
       <c r="H13" t="n">
-        <v>135803515</v>
+        <v>815242</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 37,844 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>23799650</v>
+        <v>-3068694</v>
       </c>
       <c r="E14" t="n">
-        <v>2254390</v>
+        <v>-5604784</v>
       </c>
       <c r="F14" t="n">
-        <v>60575199</v>
+        <v>7680313</v>
       </c>
       <c r="G14" t="n">
-        <v>22731641</v>
+        <v>6963905</v>
       </c>
       <c r="H14" t="n">
-        <v>143341552</v>
+        <v>2581806</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -17,381 千)</t>
+          <t>📉 20d 巨變(減碼 -19,766 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-11881299</v>
+        <v>6956837</v>
       </c>
       <c r="E15" t="n">
-        <v>-13871695</v>
+        <v>11331429</v>
       </c>
       <c r="F15" t="n">
-        <v>-23332024</v>
+        <v>43564180</v>
       </c>
       <c r="G15" t="n">
-        <v>-5951370</v>
+        <v>63329795</v>
       </c>
       <c r="H15" t="n">
-        <v>-28468405</v>
+        <v>50201356</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -30,995 千)</t>
+          <t>📉 20d 巨變(減碼 -21,158 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-12332291</v>
+        <v>4581923</v>
       </c>
       <c r="E16" t="n">
-        <v>-26203536</v>
+        <v>23799650</v>
       </c>
       <c r="F16" t="n">
-        <v>-47776682</v>
+        <v>39417392</v>
       </c>
       <c r="G16" t="n">
-        <v>-16781290</v>
+        <v>60575199</v>
       </c>
       <c r="H16" t="n">
-        <v>-1582093</v>
+        <v>149223154</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 50,723 千)</t>
+          <t>📉 20d 巨變(減碼 -9,133 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
+        <v>-28707300</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-12332291</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-56909445</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-47776682</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-7809713</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -26,856 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>68795115</v>
+      </c>
+      <c r="E18" t="n">
         <v>85976382</v>
       </c>
-      <c r="E17" t="n">
-        <v>46202315</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
+        <v>93250126</v>
+      </c>
+      <c r="G18" t="n">
         <v>120106560</v>
       </c>
-      <c r="G17" t="n">
-        <v>69383598</v>
-      </c>
-      <c r="H17" t="n">
-        <v>163908492</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H18" t="n">
+        <v>182108367</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,77 +466,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 11,043 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 61,568 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>11341415</v>
+        <v>6442421</v>
       </c>
       <c r="E2" t="n">
-        <v>5980502</v>
+        <v>20264031</v>
       </c>
       <c r="F2" t="n">
-        <v>-4947331</v>
+        <v>-25785294</v>
       </c>
       <c r="G2" t="n">
-        <v>-15990706</v>
+        <v>-87353388</v>
       </c>
       <c r="H2" t="n">
-        <v>46409522</v>
+        <v>25265905</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -106,818 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-3986052</v>
+        <v>37785539</v>
       </c>
       <c r="E3" t="n">
-        <v>7837351</v>
+        <v>68795115</v>
       </c>
       <c r="F3" t="n">
-        <v>9804512</v>
+        <v>-13567682</v>
       </c>
       <c r="G3" t="n">
-        <v>5572399</v>
+        <v>93250126</v>
       </c>
       <c r="H3" t="n">
-        <v>249672320</v>
+        <v>167887678</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,58 +548,58 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>20264031</v>
+        <v>7998501</v>
       </c>
       <c r="E4" t="n">
-        <v>27642933</v>
+        <v>11341415</v>
       </c>
       <c r="F4" t="n">
-        <v>-87353388</v>
+        <v>-4356547</v>
       </c>
       <c r="G4" t="n">
-        <v>-88746614</v>
+        <v>-4947331</v>
       </c>
       <c r="H4" t="n">
-        <v>9757141</v>
+        <v>44065655</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -17,299 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 15,441 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>4111694</v>
+        <v>-19078578</v>
       </c>
       <c r="E5" t="n">
-        <v>5977639</v>
+        <v>-19215588</v>
       </c>
       <c r="F5" t="n">
-        <v>-18692723</v>
+        <v>-42854543</v>
       </c>
       <c r="G5" t="n">
-        <v>-1394058</v>
+        <v>-58295386</v>
       </c>
       <c r="H5" t="n">
-        <v>-26953168</v>
+        <v>19882678</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
@@ -618,19 +618,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
+        <v>3831589</v>
+      </c>
+      <c r="E6" t="n">
         <v>4273686</v>
       </c>
-      <c r="E6" t="n">
-        <v>6606027</v>
-      </c>
       <c r="F6" t="n">
+        <v>-6839383</v>
+      </c>
+      <c r="G6" t="n">
         <v>-6410766</v>
       </c>
-      <c r="G6" t="n">
-        <v>-4156531</v>
-      </c>
       <c r="H6" t="n">
-        <v>-29717399</v>
+        <v>-30885454</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
+        <v>1555506</v>
+      </c>
+      <c r="E7" t="n">
         <v>1108436</v>
       </c>
-      <c r="E7" t="n">
-        <v>307351</v>
-      </c>
       <c r="F7" t="n">
+        <v>-184755</v>
+      </c>
+      <c r="G7" t="n">
         <v>-678624</v>
       </c>
-      <c r="G7" t="n">
-        <v>-2331457</v>
-      </c>
       <c r="H7" t="n">
-        <v>10978898</v>
+        <v>11705583</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,58 +688,58 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>9460411</v>
+        <v>218117</v>
       </c>
       <c r="E8" t="n">
-        <v>7828725</v>
+        <v>-302920</v>
       </c>
       <c r="F8" t="n">
-        <v>-15300182</v>
+        <v>-13215601</v>
       </c>
       <c r="G8" t="n">
-        <v>-10379320</v>
+        <v>-12137715</v>
       </c>
       <c r="H8" t="n">
-        <v>-78572612</v>
+        <v>-14450149</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-19215588</v>
+        <v>-357986</v>
       </c>
       <c r="E9" t="n">
-        <v>-17286836</v>
+        <v>286602</v>
       </c>
       <c r="F9" t="n">
-        <v>-58295386</v>
+        <v>11970221</v>
       </c>
       <c r="G9" t="n">
-        <v>-65588464</v>
+        <v>11469891</v>
       </c>
       <c r="H9" t="n">
-        <v>22619606</v>
+        <v>5508204</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
@@ -751,26 +751,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
+        <v>3439821</v>
+      </c>
+      <c r="E10" t="n">
         <v>2078384</v>
       </c>
-      <c r="E10" t="n">
-        <v>-125379</v>
-      </c>
       <c r="F10" t="n">
+        <v>1696224</v>
+      </c>
+      <c r="G10" t="n">
         <v>-960047</v>
       </c>
-      <c r="G10" t="n">
-        <v>-3354630</v>
-      </c>
       <c r="H10" t="n">
-        <v>-20435321</v>
+        <v>-18324050</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -793,19 +793,19 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
+        <v>1239125</v>
+      </c>
+      <c r="E11" t="n">
         <v>848650</v>
       </c>
-      <c r="E11" t="n">
-        <v>-362051</v>
-      </c>
       <c r="F11" t="n">
+        <v>-859183</v>
+      </c>
+      <c r="G11" t="n">
         <v>-1134216</v>
       </c>
-      <c r="G11" t="n">
-        <v>-2448542</v>
-      </c>
       <c r="H11" t="n">
-        <v>-15982770</v>
+        <v>-15668120</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -816,245 +816,280 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -17,800 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1306524</v>
+        <v>-11282023</v>
       </c>
       <c r="E12" t="n">
-        <v>1066416</v>
+        <v>4111694</v>
       </c>
       <c r="F12" t="n">
-        <v>-2708282</v>
+        <v>-36492446</v>
       </c>
       <c r="G12" t="n">
-        <v>-4502910</v>
+        <v>-18692723</v>
       </c>
       <c r="H12" t="n">
-        <v>-22107125</v>
+        <v>-39256155</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-1337903</v>
+        <v>-3433420</v>
       </c>
       <c r="E13" t="n">
-        <v>1392398</v>
+        <v>-3986052</v>
       </c>
       <c r="F13" t="n">
-        <v>-2725104</v>
+        <v>2565175</v>
       </c>
       <c r="G13" t="n">
-        <v>-1205682</v>
+        <v>9804512</v>
       </c>
       <c r="H13" t="n">
-        <v>815242</v>
+        <v>246571397</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-3068694</v>
+        <v>1497319</v>
       </c>
       <c r="E14" t="n">
-        <v>-5604784</v>
+        <v>1306524</v>
       </c>
       <c r="F14" t="n">
-        <v>7680313</v>
+        <v>-2081489</v>
       </c>
       <c r="G14" t="n">
-        <v>6963905</v>
+        <v>-2708282</v>
       </c>
       <c r="H14" t="n">
-        <v>2581806</v>
+        <v>-22013441</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -19,766 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>6956837</v>
+        <v>-1688899</v>
       </c>
       <c r="E15" t="n">
-        <v>11331429</v>
+        <v>-2622495</v>
       </c>
       <c r="F15" t="n">
-        <v>43564180</v>
+        <v>5505913</v>
       </c>
       <c r="G15" t="n">
-        <v>63329795</v>
+        <v>4145705</v>
       </c>
       <c r="H15" t="n">
-        <v>50201356</v>
+        <v>-5855735</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -21,158 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>4581923</v>
+        <v>-19690141</v>
       </c>
       <c r="E16" t="n">
-        <v>23799650</v>
+        <v>9460411</v>
       </c>
       <c r="F16" t="n">
-        <v>39417392</v>
+        <v>-19887678</v>
       </c>
       <c r="G16" t="n">
-        <v>60575199</v>
+        <v>-15300182</v>
       </c>
       <c r="H16" t="n">
-        <v>149223154</v>
+        <v>-84329412</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9,133 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-28707300</v>
+        <v>3845732</v>
       </c>
       <c r="E17" t="n">
-        <v>-12332291</v>
+        <v>-3068694</v>
       </c>
       <c r="F17" t="n">
-        <v>-56909445</v>
+        <v>13243510</v>
       </c>
       <c r="G17" t="n">
-        <v>-47776682</v>
+        <v>7680313</v>
       </c>
       <c r="H17" t="n">
-        <v>-7809713</v>
+        <v>6279781</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -26,856 千)</t>
+          <t>📉 20d 巨變(減碼 -12,506 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>68795115</v>
+        <v>25353814</v>
       </c>
       <c r="E18" t="n">
-        <v>85976382</v>
+        <v>4581923</v>
       </c>
       <c r="F18" t="n">
-        <v>93250126</v>
+        <v>26911153</v>
       </c>
       <c r="G18" t="n">
-        <v>120106560</v>
+        <v>39417392</v>
       </c>
       <c r="H18" t="n">
-        <v>182108367</v>
+        <v>170996424</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -12,316 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-59404559</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-28707300</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-69224992</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-56909445</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-33414837</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>鴻海</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 61,568 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>6442421</v>
       </c>
       <c r="E2" t="n">
-        <v>20264031</v>
+        <v>6442421</v>
       </c>
       <c r="F2" t="n">
         <v>-25785294</v>
       </c>
       <c r="G2" t="n">
-        <v>-87353388</v>
+        <v>-25785294</v>
       </c>
       <c r="H2" t="n">
         <v>25265905</v>
@@ -501,42 +501,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -106,818 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>37785539</v>
+        <v>7998501</v>
       </c>
       <c r="E3" t="n">
-        <v>68795115</v>
+        <v>7998501</v>
       </c>
       <c r="F3" t="n">
-        <v>-13567682</v>
+        <v>-4356547</v>
       </c>
       <c r="G3" t="n">
-        <v>93250126</v>
+        <v>-4356547</v>
       </c>
       <c r="H3" t="n">
-        <v>167887678</v>
+        <v>44065655</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,198 +548,198 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7998501</v>
+        <v>37785539</v>
       </c>
       <c r="E4" t="n">
-        <v>11341415</v>
+        <v>37785539</v>
       </c>
       <c r="F4" t="n">
-        <v>-4356547</v>
+        <v>-13567682</v>
       </c>
       <c r="G4" t="n">
-        <v>-4947331</v>
+        <v>-13567682</v>
       </c>
       <c r="H4" t="n">
-        <v>44065655</v>
+        <v>167887678</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 15,441 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>-19078578</v>
+        <v>3831589</v>
       </c>
       <c r="E5" t="n">
-        <v>-19215588</v>
+        <v>3831589</v>
       </c>
       <c r="F5" t="n">
-        <v>-42854543</v>
+        <v>-6839383</v>
       </c>
       <c r="G5" t="n">
-        <v>-58295386</v>
+        <v>-6839383</v>
       </c>
       <c r="H5" t="n">
-        <v>19882678</v>
+        <v>-30885454</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3831589</v>
+        <v>1555506</v>
       </c>
       <c r="E6" t="n">
-        <v>4273686</v>
+        <v>1555506</v>
       </c>
       <c r="F6" t="n">
-        <v>-6839383</v>
+        <v>-184755</v>
       </c>
       <c r="G6" t="n">
-        <v>-6410766</v>
+        <v>-184755</v>
       </c>
       <c r="H6" t="n">
-        <v>-30885454</v>
+        <v>11705583</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1555506</v>
+        <v>218117</v>
       </c>
       <c r="E7" t="n">
-        <v>1108436</v>
+        <v>218117</v>
       </c>
       <c r="F7" t="n">
-        <v>-184755</v>
+        <v>-13215601</v>
       </c>
       <c r="G7" t="n">
-        <v>-678624</v>
+        <v>-13215601</v>
       </c>
       <c r="H7" t="n">
-        <v>11705583</v>
+        <v>-14450149</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>218117</v>
+        <v>-357986</v>
       </c>
       <c r="E8" t="n">
-        <v>-302920</v>
+        <v>-357986</v>
       </c>
       <c r="F8" t="n">
-        <v>-13215601</v>
+        <v>11970221</v>
       </c>
       <c r="G8" t="n">
-        <v>-12137715</v>
+        <v>11970221</v>
       </c>
       <c r="H8" t="n">
-        <v>-14450149</v>
+        <v>5508204</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-357986</v>
+        <v>-19078578</v>
       </c>
       <c r="E9" t="n">
-        <v>286602</v>
+        <v>-19078578</v>
       </c>
       <c r="F9" t="n">
-        <v>11970221</v>
+        <v>-42854543</v>
       </c>
       <c r="G9" t="n">
-        <v>11469891</v>
+        <v>-42854543</v>
       </c>
       <c r="H9" t="n">
-        <v>5508204</v>
+        <v>19882678</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
@@ -761,13 +761,13 @@
         <v>3439821</v>
       </c>
       <c r="E10" t="n">
-        <v>2078384</v>
+        <v>3439821</v>
       </c>
       <c r="F10" t="n">
         <v>1696224</v>
       </c>
       <c r="G10" t="n">
-        <v>-960047</v>
+        <v>1696224</v>
       </c>
       <c r="H10" t="n">
         <v>-18324050</v>
@@ -796,13 +796,13 @@
         <v>1239125</v>
       </c>
       <c r="E11" t="n">
-        <v>848650</v>
+        <v>1239125</v>
       </c>
       <c r="F11" t="n">
         <v>-859183</v>
       </c>
       <c r="G11" t="n">
-        <v>-1134216</v>
+        <v>-859183</v>
       </c>
       <c r="H11" t="n">
         <v>-15668120</v>
@@ -816,42 +816,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -17,800 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-11282023</v>
+        <v>-3433420</v>
       </c>
       <c r="E12" t="n">
-        <v>4111694</v>
+        <v>-3433420</v>
       </c>
       <c r="F12" t="n">
-        <v>-36492446</v>
+        <v>2565175</v>
       </c>
       <c r="G12" t="n">
-        <v>-18692723</v>
+        <v>2565175</v>
       </c>
       <c r="H12" t="n">
-        <v>-39256155</v>
+        <v>246571397</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,233 +863,58 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-3433420</v>
+        <v>1497319</v>
       </c>
       <c r="E13" t="n">
-        <v>-3986052</v>
+        <v>1497319</v>
       </c>
       <c r="F13" t="n">
-        <v>2565175</v>
+        <v>-2081489</v>
       </c>
       <c r="G13" t="n">
-        <v>9804512</v>
+        <v>-2081489</v>
       </c>
       <c r="H13" t="n">
-        <v>246571397</v>
+        <v>-22013441</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1497319</v>
+        <v>-1688899</v>
       </c>
       <c r="E14" t="n">
-        <v>1306524</v>
+        <v>-1688899</v>
       </c>
       <c r="F14" t="n">
-        <v>-2081489</v>
+        <v>5505913</v>
       </c>
       <c r="G14" t="n">
-        <v>-2708282</v>
+        <v>5505913</v>
       </c>
       <c r="H14" t="n">
-        <v>-22013441</v>
+        <v>-5855735</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-1688899</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-2622495</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5505913</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4145705</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-5855735</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
           <t>台燿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>🔴 5d 翻紅</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-19690141</v>
-      </c>
-      <c r="E16" t="n">
-        <v>9460411</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-19887678</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-15300182</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-84329412</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🟢 5d 翻綠</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3845732</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-3068694</v>
-      </c>
-      <c r="F17" t="n">
-        <v>13243510</v>
-      </c>
-      <c r="G17" t="n">
-        <v>7680313</v>
-      </c>
-      <c r="H17" t="n">
-        <v>6279781</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>全友</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -12,506 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>25353814</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4581923</v>
-      </c>
-      <c r="F18" t="n">
-        <v>26911153</v>
-      </c>
-      <c r="G18" t="n">
-        <v>39417392</v>
-      </c>
-      <c r="H18" t="n">
-        <v>170996424</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -12,316 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-59404559</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-28707300</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-69224992</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-56909445</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-33414837</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>鴻海</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,77 +466,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -8,117 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>6442421</v>
+        <v>3775802</v>
       </c>
       <c r="E2" t="n">
-        <v>6442421</v>
+        <v>7998501</v>
       </c>
       <c r="F2" t="n">
-        <v>-25785294</v>
+        <v>-12473318</v>
       </c>
       <c r="G2" t="n">
-        <v>-25785294</v>
+        <v>-4356547</v>
       </c>
       <c r="H2" t="n">
-        <v>25265905</v>
+        <v>51709260</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7998501</v>
+        <v>4968892</v>
       </c>
       <c r="E3" t="n">
-        <v>7998501</v>
+        <v>-588540</v>
       </c>
       <c r="F3" t="n">
-        <v>-4356547</v>
+        <v>-6051164</v>
       </c>
       <c r="G3" t="n">
-        <v>-4356547</v>
+        <v>-8780799</v>
       </c>
       <c r="H3" t="n">
-        <v>44065655</v>
+        <v>-72056047</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,93 +548,93 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>37785539</v>
+        <v>31469613</v>
       </c>
       <c r="E4" t="n">
-        <v>37785539</v>
+        <v>6442421</v>
       </c>
       <c r="F4" t="n">
-        <v>-13567682</v>
+        <v>-28314912</v>
       </c>
       <c r="G4" t="n">
-        <v>-13567682</v>
+        <v>-25785294</v>
       </c>
       <c r="H4" t="n">
-        <v>167887678</v>
+        <v>19629133</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -11,182 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>3831589</v>
+        <v>-17609989</v>
       </c>
       <c r="E5" t="n">
-        <v>3831589</v>
+        <v>-19078578</v>
       </c>
       <c r="F5" t="n">
-        <v>-6839383</v>
+        <v>-54036751</v>
       </c>
       <c r="G5" t="n">
-        <v>-6839383</v>
+        <v>-42854543</v>
       </c>
       <c r="H5" t="n">
-        <v>-30885454</v>
+        <v>6861128</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1555506</v>
+        <v>3508430</v>
       </c>
       <c r="E6" t="n">
-        <v>1555506</v>
+        <v>3831589</v>
       </c>
       <c r="F6" t="n">
-        <v>-184755</v>
+        <v>-9601501</v>
       </c>
       <c r="G6" t="n">
-        <v>-184755</v>
+        <v>-6839383</v>
       </c>
       <c r="H6" t="n">
-        <v>11705583</v>
+        <v>-27341609</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
@@ -653,19 +653,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>218117</v>
+        <v>331846</v>
       </c>
       <c r="E7" t="n">
         <v>218117</v>
       </c>
       <c r="F7" t="n">
-        <v>-13215601</v>
+        <v>-12006654</v>
       </c>
       <c r="G7" t="n">
         <v>-13215601</v>
       </c>
       <c r="H7" t="n">
-        <v>-14450149</v>
+        <v>-14216878</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-357986</v>
+        <v>-528248</v>
       </c>
       <c r="E8" t="n">
         <v>-357986</v>
       </c>
       <c r="F8" t="n">
-        <v>11970221</v>
+        <v>10155677</v>
       </c>
       <c r="G8" t="n">
         <v>11970221</v>
       </c>
       <c r="H8" t="n">
-        <v>5508204</v>
+        <v>4611068</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -711,77 +711,77 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-19078578</v>
+        <v>5208206</v>
       </c>
       <c r="E9" t="n">
-        <v>-19078578</v>
+        <v>3439821</v>
       </c>
       <c r="F9" t="n">
-        <v>-42854543</v>
+        <v>3392393</v>
       </c>
       <c r="G9" t="n">
-        <v>-42854543</v>
+        <v>1696224</v>
       </c>
       <c r="H9" t="n">
-        <v>19882678</v>
+        <v>-17109280</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3439821</v>
+        <v>1670286</v>
       </c>
       <c r="E10" t="n">
-        <v>3439821</v>
+        <v>1239125</v>
       </c>
       <c r="F10" t="n">
-        <v>1696224</v>
+        <v>-1943341</v>
       </c>
       <c r="G10" t="n">
-        <v>1696224</v>
+        <v>-859183</v>
       </c>
       <c r="H10" t="n">
-        <v>-18324050</v>
+        <v>-17441615</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,30 +793,30 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1239125</v>
+        <v>732886</v>
       </c>
       <c r="E11" t="n">
-        <v>1239125</v>
+        <v>1497319</v>
       </c>
       <c r="F11" t="n">
-        <v>-859183</v>
+        <v>-2713827</v>
       </c>
       <c r="G11" t="n">
-        <v>-859183</v>
+        <v>-2081489</v>
       </c>
       <c r="H11" t="n">
-        <v>-15668120</v>
+        <v>-21339165</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,93 +828,163 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-3433420</v>
+        <v>-10512512</v>
       </c>
       <c r="E12" t="n">
-        <v>-3433420</v>
+        <v>-9877247</v>
       </c>
       <c r="F12" t="n">
-        <v>2565175</v>
+        <v>-7296532</v>
       </c>
       <c r="G12" t="n">
-        <v>2565175</v>
+        <v>-5947191</v>
       </c>
       <c r="H12" t="n">
-        <v>246571397</v>
+        <v>2442641</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>1497319</v>
+        <v>2488155</v>
       </c>
       <c r="E13" t="n">
-        <v>1497319</v>
+        <v>-3433420</v>
       </c>
       <c r="F13" t="n">
-        <v>-2081489</v>
+        <v>5543464</v>
       </c>
       <c r="G13" t="n">
-        <v>-2081489</v>
+        <v>2565175</v>
       </c>
       <c r="H13" t="n">
-        <v>-22013441</v>
+        <v>186760465</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📉 20d 巨變(減碼 -14,414 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1688899</v>
+        <v>-8579176</v>
       </c>
       <c r="E14" t="n">
-        <v>-1688899</v>
+        <v>-10972221</v>
       </c>
       <c r="F14" t="n">
-        <v>5505913</v>
+        <v>-30027287</v>
       </c>
       <c r="G14" t="n">
-        <v>5505913</v>
+        <v>-15613490</v>
       </c>
       <c r="H14" t="n">
-        <v>-5855735</v>
+        <v>-34626697</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>廣達</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -28,482 千)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-69606377</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-59404559</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-97706730</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-69224992</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-37883737</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 54,657 千)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>32316254</v>
+      </c>
+      <c r="E16" t="n">
+        <v>37785539</v>
+      </c>
+      <c r="F16" t="n">
+        <v>41088991</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-13567682</v>
+      </c>
+      <c r="H16" t="n">
+        <v>208515523</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,322 +466,322 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -8,117 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -38,936 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>3775802</v>
+        <v>-29172135</v>
       </c>
       <c r="E2" t="n">
-        <v>7998501</v>
+        <v>15334765</v>
       </c>
       <c r="F2" t="n">
-        <v>-12473318</v>
+        <v>-10473378</v>
       </c>
       <c r="G2" t="n">
-        <v>-4356547</v>
+        <v>28462453</v>
       </c>
       <c r="H2" t="n">
-        <v>51709260</v>
+        <v>137295342</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -9,035 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>4968892</v>
+        <v>-766526</v>
       </c>
       <c r="E3" t="n">
-        <v>-588540</v>
+        <v>6579238</v>
       </c>
       <c r="F3" t="n">
-        <v>-6051164</v>
+        <v>26786043</v>
       </c>
       <c r="G3" t="n">
-        <v>-8780799</v>
+        <v>35821213</v>
       </c>
       <c r="H3" t="n">
-        <v>-72056047</v>
+        <v>60872044</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -31,433 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>31469613</v>
+        <v>-26758425</v>
       </c>
       <c r="E4" t="n">
-        <v>6442421</v>
+        <v>32316254</v>
       </c>
       <c r="F4" t="n">
-        <v>-28314912</v>
+        <v>9656054</v>
       </c>
       <c r="G4" t="n">
-        <v>-25785294</v>
+        <v>41088991</v>
       </c>
       <c r="H4" t="n">
-        <v>19629133</v>
+        <v>135173194</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -11,182 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>-17609989</v>
+        <v>-11701578</v>
       </c>
       <c r="E5" t="n">
-        <v>-19078578</v>
+        <v>3775802</v>
       </c>
       <c r="F5" t="n">
-        <v>-54036751</v>
+        <v>-15397955</v>
       </c>
       <c r="G5" t="n">
-        <v>-42854543</v>
+        <v>-12473318</v>
       </c>
       <c r="H5" t="n">
-        <v>6861128</v>
+        <v>49953152</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3508430</v>
+        <v>-144420</v>
       </c>
       <c r="E6" t="n">
-        <v>3831589</v>
+        <v>732886</v>
       </c>
       <c r="F6" t="n">
-        <v>-9601501</v>
+        <v>123226</v>
       </c>
       <c r="G6" t="n">
-        <v>-6839383</v>
+        <v>-2713827</v>
       </c>
       <c r="H6" t="n">
-        <v>-27341609</v>
+        <v>-20589505</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>331846</v>
+        <v>-15126714</v>
       </c>
       <c r="E7" t="n">
-        <v>218117</v>
+        <v>-17609989</v>
       </c>
       <c r="F7" t="n">
-        <v>-12006654</v>
+        <v>-49400990</v>
       </c>
       <c r="G7" t="n">
-        <v>-13215601</v>
+        <v>-54036751</v>
       </c>
       <c r="H7" t="n">
-        <v>-14216878</v>
+        <v>7850756</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-528248</v>
+        <v>5365002</v>
       </c>
       <c r="E8" t="n">
-        <v>-357986</v>
+        <v>5208206</v>
       </c>
       <c r="F8" t="n">
-        <v>10155677</v>
+        <v>3701869</v>
       </c>
       <c r="G8" t="n">
-        <v>11970221</v>
+        <v>3392393</v>
       </c>
       <c r="H8" t="n">
-        <v>4611068</v>
+        <v>-18530338</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5208206</v>
+        <v>-14819252</v>
       </c>
       <c r="E9" t="n">
-        <v>3439821</v>
+        <v>-10512512</v>
       </c>
       <c r="F9" t="n">
-        <v>3392393</v>
+        <v>-12022902</v>
       </c>
       <c r="G9" t="n">
-        <v>1696224</v>
+        <v>-7296532</v>
       </c>
       <c r="H9" t="n">
-        <v>-17109280</v>
+        <v>2019087</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1670286</v>
+        <v>-4529923</v>
       </c>
       <c r="E10" t="n">
-        <v>1239125</v>
+        <v>624648</v>
       </c>
       <c r="F10" t="n">
-        <v>-1943341</v>
+        <v>5517709</v>
       </c>
       <c r="G10" t="n">
-        <v>-859183</v>
+        <v>11358225</v>
       </c>
       <c r="H10" t="n">
-        <v>-17441615</v>
+        <v>-948435</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,30 +793,30 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>732886</v>
+        <v>568407</v>
       </c>
       <c r="E11" t="n">
-        <v>1497319</v>
+        <v>1670286</v>
       </c>
       <c r="F11" t="n">
-        <v>-2713827</v>
+        <v>-2125945</v>
       </c>
       <c r="G11" t="n">
-        <v>-2081489</v>
+        <v>-1943341</v>
       </c>
       <c r="H11" t="n">
-        <v>-21339165</v>
+        <v>-17862941</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,163 +828,373 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-10512512</v>
+        <v>4713983</v>
       </c>
       <c r="E12" t="n">
-        <v>-9877247</v>
+        <v>4968892</v>
       </c>
       <c r="F12" t="n">
-        <v>-7296532</v>
+        <v>-4623456</v>
       </c>
       <c r="G12" t="n">
-        <v>-5947191</v>
+        <v>-6051164</v>
       </c>
       <c r="H12" t="n">
-        <v>2442641</v>
+        <v>-71698279</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2488155</v>
+        <v>100727</v>
       </c>
       <c r="E13" t="n">
-        <v>-3433420</v>
+        <v>-104545</v>
       </c>
       <c r="F13" t="n">
-        <v>5543464</v>
+        <v>-2670523</v>
       </c>
       <c r="G13" t="n">
-        <v>2565175</v>
+        <v>-3543774</v>
       </c>
       <c r="H13" t="n">
-        <v>186760465</v>
+        <v>-19368993</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -14,414 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-8579176</v>
+        <v>-10283850</v>
       </c>
       <c r="E14" t="n">
-        <v>-10972221</v>
+        <v>3508430</v>
       </c>
       <c r="F14" t="n">
-        <v>-30027287</v>
+        <v>-6722903</v>
       </c>
       <c r="G14" t="n">
-        <v>-15613490</v>
+        <v>-9601501</v>
       </c>
       <c r="H14" t="n">
-        <v>-34626697</v>
+        <v>-31972524</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -28,482 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-69606377</v>
+        <v>-1802766</v>
       </c>
       <c r="E15" t="n">
-        <v>-59404559</v>
+        <v>557832</v>
       </c>
       <c r="F15" t="n">
-        <v>-97706730</v>
+        <v>-2867511</v>
       </c>
       <c r="G15" t="n">
-        <v>-69224992</v>
+        <v>-567899</v>
       </c>
       <c r="H15" t="n">
-        <v>-37883737</v>
+        <v>-5181501</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 54,657 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-770218</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-528248</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9517587</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10155677</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4900075</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>瑞昱</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-382264</v>
+      </c>
+      <c r="E17" t="n">
+        <v>641308</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6001847</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6231616</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7888572</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -23,697 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="n">
-        <v>32316254</v>
-      </c>
-      <c r="E16" t="n">
-        <v>37785539</v>
-      </c>
-      <c r="F16" t="n">
-        <v>41088991</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-13567682</v>
-      </c>
-      <c r="H16" t="n">
-        <v>208515523</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>華邦電</t>
+      <c r="D18" t="n">
+        <v>-50202619</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-14790875</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-67053350</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-43356410</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-41830769</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 22,432 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>22382615</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2488155</v>
+      </c>
+      <c r="F19" t="n">
+        <v>27975033</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5543464</v>
+      </c>
+      <c r="H19" t="n">
+        <v>174945889</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -8,598 千)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-16900058</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-18720136</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-26916216</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-18318375</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-106118141</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 30,810 千)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3646773</v>
+      </c>
+      <c r="E21" t="n">
+        <v>31469613</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2494594</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-28314912</v>
+      </c>
+      <c r="H21" t="n">
+        <v>16703533</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -16,183 千)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-102256708</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-69606377</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-113889733</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-97706730</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-23853709</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>鴻海</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -38,936 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,865 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
+        <v>-52952989</v>
+      </c>
+      <c r="E2" t="n">
         <v>-29172135</v>
       </c>
-      <c r="E2" t="n">
-        <v>15334765</v>
-      </c>
       <c r="F2" t="n">
+        <v>-20338464</v>
+      </c>
+      <c r="G2" t="n">
         <v>-10473378</v>
       </c>
-      <c r="G2" t="n">
-        <v>28462453</v>
-      </c>
       <c r="H2" t="n">
-        <v>137295342</v>
+        <v>116810923</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -506,26 +506,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -9,035 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 8,550 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
+        <v>-1968208</v>
+      </c>
+      <c r="E3" t="n">
         <v>-766526</v>
       </c>
-      <c r="E3" t="n">
-        <v>6579238</v>
-      </c>
       <c r="F3" t="n">
+        <v>35336071</v>
+      </c>
+      <c r="G3" t="n">
         <v>26786043</v>
       </c>
-      <c r="G3" t="n">
-        <v>35821213</v>
-      </c>
       <c r="H3" t="n">
-        <v>60872044</v>
+        <v>65018655</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -541,26 +541,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -31,433 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 42,005 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
+        <v>-23218065</v>
+      </c>
+      <c r="E4" t="n">
         <v>-26758425</v>
       </c>
-      <c r="E4" t="n">
-        <v>32316254</v>
-      </c>
       <c r="F4" t="n">
+        <v>51661375</v>
+      </c>
+      <c r="G4" t="n">
         <v>9656054</v>
       </c>
-      <c r="G4" t="n">
-        <v>41088991</v>
-      </c>
       <c r="H4" t="n">
-        <v>135173194</v>
+        <v>152622496</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -571,77 +571,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>-11701578</v>
+        <v>4625962</v>
       </c>
       <c r="E5" t="n">
-        <v>3775802</v>
+        <v>4713983</v>
       </c>
       <c r="F5" t="n">
-        <v>-15397955</v>
+        <v>-6309045</v>
       </c>
       <c r="G5" t="n">
-        <v>-12473318</v>
+        <v>-4623456</v>
       </c>
       <c r="H5" t="n">
-        <v>49953152</v>
+        <v>-71591083</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-144420</v>
+        <v>57037</v>
       </c>
       <c r="E6" t="n">
-        <v>732886</v>
+        <v>-140174</v>
       </c>
       <c r="F6" t="n">
-        <v>123226</v>
+        <v>-11463808</v>
       </c>
       <c r="G6" t="n">
-        <v>-2713827</v>
+        <v>-11797696</v>
       </c>
       <c r="H6" t="n">
-        <v>-20589505</v>
+        <v>-13535738</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,30 +653,30 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-15126714</v>
+        <v>-9252854</v>
       </c>
       <c r="E7" t="n">
-        <v>-17609989</v>
+        <v>-11701578</v>
       </c>
       <c r="F7" t="n">
-        <v>-49400990</v>
+        <v>-12829971</v>
       </c>
       <c r="G7" t="n">
-        <v>-54036751</v>
+        <v>-15397955</v>
       </c>
       <c r="H7" t="n">
-        <v>7850756</v>
+        <v>47635283</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,30 +688,30 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>5365002</v>
+        <v>354088</v>
       </c>
       <c r="E8" t="n">
-        <v>5208206</v>
+        <v>-144420</v>
       </c>
       <c r="F8" t="n">
-        <v>3701869</v>
+        <v>1580151</v>
       </c>
       <c r="G8" t="n">
-        <v>3392393</v>
+        <v>123226</v>
       </c>
       <c r="H8" t="n">
-        <v>-18530338</v>
+        <v>-17531911</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,65 +723,65 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-14819252</v>
+        <v>-13674573</v>
       </c>
       <c r="E9" t="n">
-        <v>-10512512</v>
+        <v>-15126714</v>
       </c>
       <c r="F9" t="n">
-        <v>-12022902</v>
+        <v>-49788852</v>
       </c>
       <c r="G9" t="n">
-        <v>-7296532</v>
+        <v>-49400990</v>
       </c>
       <c r="H9" t="n">
-        <v>2019087</v>
+        <v>5737451</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-4529923</v>
+        <v>907468</v>
       </c>
       <c r="E10" t="n">
-        <v>624648</v>
+        <v>5365002</v>
       </c>
       <c r="F10" t="n">
-        <v>5517709</v>
+        <v>86361</v>
       </c>
       <c r="G10" t="n">
-        <v>11358225</v>
+        <v>3701869</v>
       </c>
       <c r="H10" t="n">
-        <v>-948435</v>
+        <v>-22470160</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,30 +793,30 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>568407</v>
+        <v>643027</v>
       </c>
       <c r="E11" t="n">
-        <v>1670286</v>
+        <v>100727</v>
       </c>
       <c r="F11" t="n">
-        <v>-2125945</v>
+        <v>-2369573</v>
       </c>
       <c r="G11" t="n">
-        <v>-1943341</v>
+        <v>-2670523</v>
       </c>
       <c r="H11" t="n">
-        <v>-17862941</v>
+        <v>-19557247</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,30 +828,30 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>4713983</v>
+        <v>96890</v>
       </c>
       <c r="E12" t="n">
-        <v>4968892</v>
+        <v>-352587</v>
       </c>
       <c r="F12" t="n">
-        <v>-4623456</v>
+        <v>-146176</v>
       </c>
       <c r="G12" t="n">
-        <v>-6051164</v>
+        <v>-752007</v>
       </c>
       <c r="H12" t="n">
-        <v>-71698279</v>
+        <v>-19850923</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,338 +863,128 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>100727</v>
+        <v>158183</v>
       </c>
       <c r="E13" t="n">
-        <v>-104545</v>
+        <v>-1196845</v>
       </c>
       <c r="F13" t="n">
-        <v>-2670523</v>
+        <v>-3689558</v>
       </c>
       <c r="G13" t="n">
-        <v>-3543774</v>
+        <v>-5277668</v>
       </c>
       <c r="H13" t="n">
-        <v>-19368993</v>
+        <v>-12808670</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-10283850</v>
+        <v>2637042</v>
       </c>
       <c r="E14" t="n">
-        <v>3508430</v>
+        <v>-956533</v>
       </c>
       <c r="F14" t="n">
-        <v>-6722903</v>
+        <v>2629366</v>
       </c>
       <c r="G14" t="n">
-        <v>-9601501</v>
+        <v>-48555</v>
       </c>
       <c r="H14" t="n">
-        <v>-31972524</v>
+        <v>509025</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-1802766</v>
+        <v>-465853</v>
       </c>
       <c r="E15" t="n">
-        <v>557832</v>
+        <v>-382264</v>
       </c>
       <c r="F15" t="n">
-        <v>-2867511</v>
+        <v>5030582</v>
       </c>
       <c r="G15" t="n">
-        <v>-567899</v>
+        <v>6001847</v>
       </c>
       <c r="H15" t="n">
-        <v>-5181501</v>
+        <v>8202733</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📈 20d 巨變(加碼 11,432 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-770218</v>
+        <v>-10746307</v>
       </c>
       <c r="E16" t="n">
-        <v>-528248</v>
+        <v>-16900058</v>
       </c>
       <c r="F16" t="n">
-        <v>9517587</v>
+        <v>-15484304</v>
       </c>
       <c r="G16" t="n">
-        <v>10155677</v>
+        <v>-26916216</v>
       </c>
       <c r="H16" t="n">
-        <v>4900075</v>
+        <v>-98731487</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>瑞昱</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-382264</v>
-      </c>
-      <c r="E17" t="n">
-        <v>641308</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6001847</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6231616</v>
-      </c>
-      <c r="H17" t="n">
-        <v>7888572</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -23,697 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-50202619</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-14790875</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-67053350</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-43356410</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-41830769</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 22,432 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>22382615</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2488155</v>
-      </c>
-      <c r="F19" t="n">
-        <v>27975033</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5543464</v>
-      </c>
-      <c r="H19" t="n">
-        <v>174945889</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -8,598 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-16900058</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-18720136</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-26916216</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-18318375</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-106118141</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
           <t>國巨*</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 30,810 千)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3646773</v>
-      </c>
-      <c r="E21" t="n">
-        <v>31469613</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2494594</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-28314912</v>
-      </c>
-      <c r="H21" t="n">
-        <v>16703533</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -16,183 千)</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-102256708</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-69606377</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-113889733</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-97706730</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-23853709</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>鴻海</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,70 +466,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,865 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -21,298 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>-52952989</v>
+        <v>-21864838</v>
       </c>
       <c r="E2" t="n">
-        <v>-29172135</v>
+        <v>-1968208</v>
       </c>
       <c r="F2" t="n">
-        <v>-20338464</v>
+        <v>14037771</v>
       </c>
       <c r="G2" t="n">
-        <v>-10473378</v>
+        <v>35336071</v>
       </c>
       <c r="H2" t="n">
-        <v>116810923</v>
+        <v>43712027</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 8,550 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,539 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>-1968208</v>
+        <v>-19021874</v>
       </c>
       <c r="E3" t="n">
-        <v>-766526</v>
+        <v>-9252854</v>
       </c>
       <c r="F3" t="n">
-        <v>35336071</v>
+        <v>-22368683</v>
       </c>
       <c r="G3" t="n">
-        <v>26786043</v>
+        <v>-12829971</v>
       </c>
       <c r="H3" t="n">
-        <v>65018655</v>
+        <v>39187582</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
@@ -541,26 +541,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 42,005 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 23,421 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
+        <v>-62594377</v>
+      </c>
+      <c r="E4" t="n">
         <v>-23218065</v>
       </c>
-      <c r="E4" t="n">
-        <v>-26758425</v>
-      </c>
       <c r="F4" t="n">
+        <v>75081972</v>
+      </c>
+      <c r="G4" t="n">
         <v>51661375</v>
       </c>
-      <c r="G4" t="n">
-        <v>9656054</v>
-      </c>
       <c r="H4" t="n">
-        <v>152622496</v>
+        <v>133776382</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
+        <v>8895436</v>
+      </c>
+      <c r="E5" t="n">
         <v>4625962</v>
       </c>
-      <c r="E5" t="n">
-        <v>4713983</v>
-      </c>
       <c r="F5" t="n">
+        <v>-1901353</v>
+      </c>
+      <c r="G5" t="n">
         <v>-6309045</v>
       </c>
-      <c r="G5" t="n">
-        <v>-4623456</v>
-      </c>
       <c r="H5" t="n">
-        <v>-71591083</v>
+        <v>-66181678</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -606,70 +606,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>57037</v>
+        <v>-60642687</v>
       </c>
       <c r="E6" t="n">
-        <v>-140174</v>
+        <v>-52952989</v>
       </c>
       <c r="F6" t="n">
-        <v>-11463808</v>
+        <v>-26868744</v>
       </c>
       <c r="G6" t="n">
-        <v>-11797696</v>
+        <v>-20338464</v>
       </c>
       <c r="H6" t="n">
-        <v>-13535738</v>
+        <v>101656684</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-9252854</v>
+        <v>455648</v>
       </c>
       <c r="E7" t="n">
-        <v>-11701578</v>
+        <v>57037</v>
       </c>
       <c r="F7" t="n">
-        <v>-12829971</v>
+        <v>-11299586</v>
       </c>
       <c r="G7" t="n">
-        <v>-15397955</v>
+        <v>-11463808</v>
       </c>
       <c r="H7" t="n">
-        <v>47635283</v>
+        <v>-12852427</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
+        <v>722004</v>
+      </c>
+      <c r="E8" t="n">
         <v>354088</v>
       </c>
-      <c r="E8" t="n">
-        <v>-144420</v>
-      </c>
       <c r="F8" t="n">
+        <v>3182454</v>
+      </c>
+      <c r="G8" t="n">
         <v>1580151</v>
       </c>
-      <c r="G8" t="n">
-        <v>123226</v>
-      </c>
       <c r="H8" t="n">
-        <v>-17531911</v>
+        <v>-16579367</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -723,19 +723,19 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
+        <v>-13484582</v>
+      </c>
+      <c r="E9" t="n">
         <v>-13674573</v>
       </c>
-      <c r="E9" t="n">
-        <v>-15126714</v>
-      </c>
       <c r="F9" t="n">
+        <v>-53753858</v>
+      </c>
+      <c r="G9" t="n">
         <v>-49788852</v>
       </c>
-      <c r="G9" t="n">
-        <v>-49400990</v>
-      </c>
       <c r="H9" t="n">
-        <v>5737451</v>
+        <v>1966276</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -746,77 +746,77 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>907468</v>
+        <v>-199805</v>
       </c>
       <c r="E10" t="n">
-        <v>5365002</v>
+        <v>371572</v>
       </c>
       <c r="F10" t="n">
-        <v>86361</v>
+        <v>2717678</v>
       </c>
       <c r="G10" t="n">
-        <v>3701869</v>
+        <v>3408133</v>
       </c>
       <c r="H10" t="n">
-        <v>-22470160</v>
+        <v>27414178</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -29,574 千)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>643027</v>
+        <v>-29490418</v>
       </c>
       <c r="E11" t="n">
-        <v>100727</v>
+        <v>3889133</v>
       </c>
       <c r="F11" t="n">
-        <v>-2369573</v>
+        <v>-33646625</v>
       </c>
       <c r="G11" t="n">
-        <v>-2670523</v>
+        <v>-4072199</v>
       </c>
       <c r="H11" t="n">
-        <v>-19557247</v>
+        <v>-47490824</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,23 +828,23 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>96890</v>
+        <v>647588</v>
       </c>
       <c r="E12" t="n">
-        <v>-352587</v>
+        <v>643027</v>
       </c>
       <c r="F12" t="n">
-        <v>-146176</v>
+        <v>-2338555</v>
       </c>
       <c r="G12" t="n">
-        <v>-752007</v>
+        <v>-2369573</v>
       </c>
       <c r="H12" t="n">
-        <v>-19850923</v>
+        <v>-19547229</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
@@ -863,19 +863,19 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
+        <v>154930</v>
+      </c>
+      <c r="E13" t="n">
         <v>158183</v>
       </c>
-      <c r="E13" t="n">
-        <v>-1196845</v>
-      </c>
       <c r="F13" t="n">
+        <v>-3839730</v>
+      </c>
+      <c r="G13" t="n">
         <v>-3689558</v>
       </c>
-      <c r="G13" t="n">
-        <v>-5277668</v>
-      </c>
       <c r="H13" t="n">
-        <v>-12808670</v>
+        <v>-13296044</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -886,105 +886,210 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2637042</v>
+        <v>-1446634</v>
       </c>
       <c r="E14" t="n">
-        <v>-956533</v>
+        <v>907468</v>
       </c>
       <c r="F14" t="n">
-        <v>2629366</v>
+        <v>-436249</v>
       </c>
       <c r="G14" t="n">
-        <v>-48555</v>
+        <v>86361</v>
       </c>
       <c r="H14" t="n">
-        <v>509025</v>
+        <v>-22980679</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📉 20d 巨變(減碼 -22,920 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-465853</v>
+        <v>-88230643</v>
       </c>
       <c r="E15" t="n">
-        <v>-382264</v>
+        <v>-55282629</v>
       </c>
       <c r="F15" t="n">
-        <v>5030582</v>
+        <v>-88474804</v>
       </c>
       <c r="G15" t="n">
-        <v>6001847</v>
+        <v>-65554461</v>
       </c>
       <c r="H15" t="n">
-        <v>8202733</v>
+        <v>-96474474</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11,432 千)</t>
+          <t>📉 20d 巨變(減碼 -11,139 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>-20928489</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-12164846</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-15525357</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-4386346</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-37934217</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 10,700 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>43747693</v>
+      </c>
+      <c r="E17" t="n">
+        <v>32167728</v>
+      </c>
+      <c r="F17" t="n">
+        <v>40243518</v>
+      </c>
+      <c r="G17" t="n">
+        <v>29543660</v>
+      </c>
+      <c r="H17" t="n">
+        <v>156470418</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -29,701 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-38264554</v>
+      </c>
+      <c r="E18" t="n">
         <v>-10746307</v>
       </c>
-      <c r="E16" t="n">
-        <v>-16900058</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="F18" t="n">
+        <v>-45185774</v>
+      </c>
+      <c r="G18" t="n">
         <v>-15484304</v>
       </c>
-      <c r="G16" t="n">
-        <v>-26916216</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-98731487</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H18" t="n">
+        <v>-124722317</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>國巨*</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -13,458 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-81639975</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-80103660</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-121426686</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-107968416</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-84820314</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>鴻海</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,175 +466,175 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -21,298 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>-21864838</v>
+        <v>856141</v>
       </c>
       <c r="E2" t="n">
-        <v>-1968208</v>
+        <v>-2199065</v>
       </c>
       <c r="F2" t="n">
-        <v>14037771</v>
+        <v>-13519797</v>
       </c>
       <c r="G2" t="n">
-        <v>35336071</v>
+        <v>-16100497</v>
       </c>
       <c r="H2" t="n">
-        <v>43712027</v>
+        <v>-9144703</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,539 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 16,319 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>-19021874</v>
+        <v>-36149622</v>
       </c>
       <c r="E3" t="n">
-        <v>-9252854</v>
+        <v>-62594377</v>
       </c>
       <c r="F3" t="n">
-        <v>-22368683</v>
+        <v>91401322</v>
       </c>
       <c r="G3" t="n">
-        <v>-12829971</v>
+        <v>75081972</v>
       </c>
       <c r="H3" t="n">
-        <v>39187582</v>
+        <v>146000448</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 23,421 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>-62594377</v>
+        <v>12852293</v>
       </c>
       <c r="E4" t="n">
-        <v>-23218065</v>
+        <v>8895436</v>
       </c>
       <c r="F4" t="n">
-        <v>75081972</v>
+        <v>-29703</v>
       </c>
       <c r="G4" t="n">
-        <v>51661375</v>
+        <v>-1901353</v>
       </c>
       <c r="H4" t="n">
-        <v>133776382</v>
+        <v>-63151751</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>8895436</v>
+        <v>-90199039</v>
       </c>
       <c r="E5" t="n">
-        <v>4625962</v>
+        <v>-60642687</v>
       </c>
       <c r="F5" t="n">
-        <v>-1901353</v>
+        <v>-28083449</v>
       </c>
       <c r="G5" t="n">
-        <v>-6309045</v>
+        <v>-26868744</v>
       </c>
       <c r="H5" t="n">
-        <v>-66181678</v>
+        <v>93873602</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-60642687</v>
+        <v>-24445277</v>
       </c>
       <c r="E6" t="n">
-        <v>-52952989</v>
+        <v>-21864838</v>
       </c>
       <c r="F6" t="n">
-        <v>-26868744</v>
+        <v>17604233</v>
       </c>
       <c r="G6" t="n">
-        <v>-20338464</v>
+        <v>14037771</v>
       </c>
       <c r="H6" t="n">
-        <v>101656684</v>
+        <v>42181565</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
@@ -653,19 +653,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
+        <v>381001</v>
+      </c>
+      <c r="E7" t="n">
         <v>455648</v>
       </c>
-      <c r="E7" t="n">
-        <v>57037</v>
-      </c>
       <c r="F7" t="n">
+        <v>-11699662</v>
+      </c>
+      <c r="G7" t="n">
         <v>-11299586</v>
       </c>
-      <c r="G7" t="n">
-        <v>-11463808</v>
-      </c>
       <c r="H7" t="n">
-        <v>-12852427</v>
+        <v>-13098509</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -676,140 +676,140 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>722004</v>
+        <v>-19813379</v>
       </c>
       <c r="E8" t="n">
-        <v>354088</v>
+        <v>-19021874</v>
       </c>
       <c r="F8" t="n">
-        <v>3182454</v>
+        <v>-22302561</v>
       </c>
       <c r="G8" t="n">
-        <v>1580151</v>
+        <v>-22368683</v>
       </c>
       <c r="H8" t="n">
-        <v>-16579367</v>
+        <v>36052210</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-13484582</v>
+        <v>431817</v>
       </c>
       <c r="E9" t="n">
-        <v>-13674573</v>
+        <v>722004</v>
       </c>
       <c r="F9" t="n">
-        <v>-53753858</v>
+        <v>2852082</v>
       </c>
       <c r="G9" t="n">
-        <v>-49788852</v>
+        <v>3182454</v>
       </c>
       <c r="H9" t="n">
-        <v>1966276</v>
+        <v>-16775870</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-199805</v>
+        <v>-7238448</v>
       </c>
       <c r="E10" t="n">
-        <v>371572</v>
+        <v>-13484582</v>
       </c>
       <c r="F10" t="n">
-        <v>2717678</v>
+        <v>-48706278</v>
       </c>
       <c r="G10" t="n">
-        <v>3408133</v>
+        <v>-53753858</v>
       </c>
       <c r="H10" t="n">
-        <v>27414178</v>
+        <v>5475482</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -29,574 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-29490418</v>
+        <v>-160535</v>
       </c>
       <c r="E11" t="n">
-        <v>3889133</v>
+        <v>-199805</v>
       </c>
       <c r="F11" t="n">
-        <v>-33646625</v>
+        <v>3034052</v>
       </c>
       <c r="G11" t="n">
-        <v>-4072199</v>
+        <v>2717678</v>
       </c>
       <c r="H11" t="n">
-        <v>-47490824</v>
+        <v>27775918</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
@@ -828,19 +828,19 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
+        <v>2497412</v>
+      </c>
+      <c r="E12" t="n">
         <v>647588</v>
       </c>
-      <c r="E12" t="n">
-        <v>643027</v>
-      </c>
       <c r="F12" t="n">
+        <v>-289443</v>
+      </c>
+      <c r="G12" t="n">
         <v>-2338555</v>
       </c>
-      <c r="G12" t="n">
-        <v>-2369573</v>
-      </c>
       <c r="H12" t="n">
-        <v>-19547229</v>
+        <v>-17723117</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -851,245 +851,210 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>154930</v>
+        <v>-7413554</v>
       </c>
       <c r="E13" t="n">
-        <v>158183</v>
+        <v>-2449655</v>
       </c>
       <c r="F13" t="n">
-        <v>-3839730</v>
+        <v>3731785</v>
       </c>
       <c r="G13" t="n">
-        <v>-3689558</v>
+        <v>3674907</v>
       </c>
       <c r="H13" t="n">
-        <v>-13296044</v>
+        <v>-482539</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>📉 20d 巨變(減碼 -17,819 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1446634</v>
+        <v>-97973798</v>
       </c>
       <c r="E14" t="n">
-        <v>907468</v>
+        <v>-88230643</v>
       </c>
       <c r="F14" t="n">
-        <v>-436249</v>
+        <v>-106294186</v>
       </c>
       <c r="G14" t="n">
-        <v>86361</v>
+        <v>-88474804</v>
       </c>
       <c r="H14" t="n">
-        <v>-22980679</v>
+        <v>-118520616</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -22,920 千)</t>
+          <t>📈 20d 巨變(加碼 15,267 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-88230643</v>
+        <v>56145489</v>
       </c>
       <c r="E15" t="n">
-        <v>-55282629</v>
+        <v>43747693</v>
       </c>
       <c r="F15" t="n">
-        <v>-88474804</v>
+        <v>55510536</v>
       </c>
       <c r="G15" t="n">
-        <v>-65554461</v>
+        <v>40243518</v>
       </c>
       <c r="H15" t="n">
-        <v>-96474474</v>
+        <v>165767291</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11,139 千)</t>
+          <t>📈 20d 巨變(加碼 11,946 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-20928489</v>
+        <v>-34745439</v>
       </c>
       <c r="E16" t="n">
-        <v>-12164846</v>
+        <v>-29490418</v>
       </c>
       <c r="F16" t="n">
-        <v>-15525357</v>
+        <v>-21700397</v>
       </c>
       <c r="G16" t="n">
-        <v>-4386346</v>
+        <v>-33646625</v>
       </c>
       <c r="H16" t="n">
-        <v>-37934217</v>
+        <v>-37237081</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10,700 千)</t>
+          <t>📈 20d 巨變(加碼 25,064 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>43747693</v>
+        <v>-33364102</v>
       </c>
       <c r="E17" t="n">
-        <v>32167728</v>
+        <v>-81639975</v>
       </c>
       <c r="F17" t="n">
-        <v>40243518</v>
+        <v>-96362689</v>
       </c>
       <c r="G17" t="n">
-        <v>29543660</v>
+        <v>-121426686</v>
       </c>
       <c r="H17" t="n">
-        <v>156470418</v>
+        <v>-62149565</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -29,701 千)</t>
+          <t>📉 20d 巨變(減碼 -14,157 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-38264554</v>
+        <v>21934711</v>
       </c>
       <c r="E18" t="n">
-        <v>-10746307</v>
+        <v>27048514</v>
       </c>
       <c r="F18" t="n">
-        <v>-45185774</v>
+        <v>78580746</v>
       </c>
       <c r="G18" t="n">
-        <v>-15484304</v>
+        <v>92738230</v>
       </c>
       <c r="H18" t="n">
-        <v>-124722317</v>
+        <v>118325274</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -13,458 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-81639975</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-80103660</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-121426686</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-107968416</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-84820314</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>鴻海</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,128 +478,128 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>856141</v>
+        <v>1256389</v>
       </c>
       <c r="E2" t="n">
-        <v>-2199065</v>
+        <v>-955860</v>
       </c>
       <c r="F2" t="n">
-        <v>-13519797</v>
+        <v>-15757253</v>
       </c>
       <c r="G2" t="n">
-        <v>-16100497</v>
+        <v>-16512301</v>
       </c>
       <c r="H2" t="n">
-        <v>-9144703</v>
+        <v>-9676230</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 16,319 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,031 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>-36149622</v>
+        <v>-92873950</v>
       </c>
       <c r="E3" t="n">
-        <v>-62594377</v>
+        <v>-90199039</v>
       </c>
       <c r="F3" t="n">
-        <v>91401322</v>
+        <v>-40114437</v>
       </c>
       <c r="G3" t="n">
-        <v>75081972</v>
+        <v>-28083449</v>
       </c>
       <c r="H3" t="n">
-        <v>146000448</v>
+        <v>43406106</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -29,490 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>12852293</v>
+        <v>-43831776</v>
       </c>
       <c r="E4" t="n">
-        <v>8895436</v>
+        <v>-36149622</v>
       </c>
       <c r="F4" t="n">
-        <v>-29703</v>
+        <v>61911428</v>
       </c>
       <c r="G4" t="n">
-        <v>-1901353</v>
+        <v>91401322</v>
       </c>
       <c r="H4" t="n">
-        <v>-63151751</v>
+        <v>94998783</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>-90199039</v>
+        <v>8031659</v>
       </c>
       <c r="E5" t="n">
-        <v>-60642687</v>
+        <v>12852293</v>
       </c>
       <c r="F5" t="n">
-        <v>-28083449</v>
+        <v>-1037727</v>
       </c>
       <c r="G5" t="n">
-        <v>-26868744</v>
+        <v>-29703</v>
       </c>
       <c r="H5" t="n">
-        <v>93873602</v>
+        <v>-64024388</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
@@ -618,19 +618,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
+        <v>-28230999</v>
+      </c>
+      <c r="E6" t="n">
         <v>-24445277</v>
       </c>
-      <c r="E6" t="n">
-        <v>-21864838</v>
-      </c>
       <c r="F6" t="n">
+        <v>13371136</v>
+      </c>
+      <c r="G6" t="n">
         <v>17604233</v>
       </c>
-      <c r="G6" t="n">
-        <v>14037771</v>
-      </c>
       <c r="H6" t="n">
-        <v>42181565</v>
+        <v>50595734</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -641,420 +641,140 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>381001</v>
+        <v>-415098</v>
       </c>
       <c r="E7" t="n">
-        <v>455648</v>
+        <v>431817</v>
       </c>
       <c r="F7" t="n">
-        <v>-11699662</v>
+        <v>840478</v>
       </c>
       <c r="G7" t="n">
-        <v>-11299586</v>
+        <v>2852082</v>
       </c>
       <c r="H7" t="n">
-        <v>-13098509</v>
+        <v>-15892318</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-19813379</v>
+        <v>2350913</v>
       </c>
       <c r="E8" t="n">
-        <v>-19021874</v>
+        <v>2497412</v>
       </c>
       <c r="F8" t="n">
-        <v>-22302561</v>
+        <v>13058</v>
       </c>
       <c r="G8" t="n">
-        <v>-22368683</v>
+        <v>-289443</v>
       </c>
       <c r="H8" t="n">
-        <v>36052210</v>
+        <v>-18745523</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>431817</v>
+        <v>-47548</v>
       </c>
       <c r="E9" t="n">
-        <v>722004</v>
+        <v>-160535</v>
       </c>
       <c r="F9" t="n">
-        <v>2852082</v>
+        <v>2988653</v>
       </c>
       <c r="G9" t="n">
-        <v>3182454</v>
+        <v>3034052</v>
       </c>
       <c r="H9" t="n">
-        <v>-16775870</v>
+        <v>25660834</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>📉 20d 巨變(減碼 -13,196 千)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7238448</v>
+        <v>-22900019</v>
       </c>
       <c r="E10" t="n">
-        <v>-13484582</v>
+        <v>-33364102</v>
       </c>
       <c r="F10" t="n">
-        <v>-48706278</v>
+        <v>-109558780</v>
       </c>
       <c r="G10" t="n">
-        <v>-53753858</v>
+        <v>-96362689</v>
       </c>
       <c r="H10" t="n">
-        <v>5475482</v>
+        <v>-126278486</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>英業達</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-160535</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-199805</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3034052</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2717678</v>
-      </c>
-      <c r="H11" t="n">
-        <v>27775918</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>建準</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3596</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2497412</v>
-      </c>
-      <c r="E12" t="n">
-        <v>647588</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-289443</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-2338555</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-17723117</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>智易</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-7413554</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-2449655</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3731785</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3674907</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-482539</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>全友</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -17,819 千)</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-97973798</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-88230643</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-106294186</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-88474804</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-118520616</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 15,267 千)</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>56145489</v>
-      </c>
-      <c r="E15" t="n">
-        <v>43747693</v>
-      </c>
-      <c r="F15" t="n">
-        <v>55510536</v>
-      </c>
-      <c r="G15" t="n">
-        <v>40243518</v>
-      </c>
-      <c r="H15" t="n">
-        <v>165767291</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 11,946 千)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-34745439</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-29490418</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-21700397</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-33646625</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-37237081</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 25,064 千)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-33364102</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-81639975</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-96362689</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-121426686</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-62149565</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
           <t>鴻海</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -14,157 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>21934711</v>
-      </c>
-      <c r="E18" t="n">
-        <v>27048514</v>
-      </c>
-      <c r="F18" t="n">
-        <v>78580746</v>
-      </c>
-      <c r="G18" t="n">
-        <v>92738230</v>
-      </c>
-      <c r="H18" t="n">
-        <v>118325274</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>中華電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,315 +466,560 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 23,987 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1256389</v>
+        <v>-5464743</v>
       </c>
       <c r="E2" t="n">
-        <v>-955860</v>
+        <v>-41222492</v>
       </c>
       <c r="F2" t="n">
-        <v>-15757253</v>
+        <v>9354629</v>
       </c>
       <c r="G2" t="n">
-        <v>-16512301</v>
+        <v>-14632154</v>
       </c>
       <c r="H2" t="n">
-        <v>-9676230</v>
+        <v>-64957746</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,031 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 8,288 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-92873950</v>
+        <v>7743099</v>
       </c>
       <c r="E3" t="n">
-        <v>-90199039</v>
+        <v>-2790467</v>
       </c>
       <c r="F3" t="n">
-        <v>-40114437</v>
+        <v>-38438749</v>
       </c>
       <c r="G3" t="n">
-        <v>-28083449</v>
+        <v>-46726690</v>
       </c>
       <c r="H3" t="n">
-        <v>43406106</v>
+        <v>-4614950</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -29,490 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-43831776</v>
+        <v>531729</v>
       </c>
       <c r="E4" t="n">
-        <v>-36149622</v>
+        <v>-22900019</v>
       </c>
       <c r="F4" t="n">
-        <v>61911428</v>
+        <v>-114585274</v>
       </c>
       <c r="G4" t="n">
-        <v>91401322</v>
+        <v>-109558780</v>
       </c>
       <c r="H4" t="n">
-        <v>94998783</v>
+        <v>-144168089</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 10,669 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>8031659</v>
+        <v>-6387125</v>
       </c>
       <c r="E5" t="n">
-        <v>12852293</v>
+        <v>-43831776</v>
       </c>
       <c r="F5" t="n">
-        <v>-1037727</v>
+        <v>72580052</v>
       </c>
       <c r="G5" t="n">
-        <v>-29703</v>
+        <v>61911428</v>
       </c>
       <c r="H5" t="n">
-        <v>-64024388</v>
+        <v>114178970</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-28230999</v>
+        <v>8501543</v>
       </c>
       <c r="E6" t="n">
-        <v>-24445277</v>
+        <v>8031659</v>
       </c>
       <c r="F6" t="n">
-        <v>13371136</v>
+        <v>4226890</v>
       </c>
       <c r="G6" t="n">
-        <v>17604233</v>
+        <v>-1037727</v>
       </c>
       <c r="H6" t="n">
-        <v>50595734</v>
+        <v>-63196736</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-415098</v>
+        <v>-25924016</v>
       </c>
       <c r="E7" t="n">
-        <v>431817</v>
+        <v>-28230999</v>
       </c>
       <c r="F7" t="n">
-        <v>840478</v>
+        <v>8950020</v>
       </c>
       <c r="G7" t="n">
-        <v>2852082</v>
+        <v>13371136</v>
       </c>
       <c r="H7" t="n">
-        <v>-15892318</v>
+        <v>52684777</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2350913</v>
+        <v>-55363074</v>
       </c>
       <c r="E8" t="n">
-        <v>2497412</v>
+        <v>-92873950</v>
       </c>
       <c r="F8" t="n">
-        <v>13058</v>
+        <v>-44358062</v>
       </c>
       <c r="G8" t="n">
-        <v>-289443</v>
+        <v>-40114437</v>
       </c>
       <c r="H8" t="n">
-        <v>-18745523</v>
+        <v>30287297</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-47548</v>
+        <v>-2977067</v>
       </c>
       <c r="E9" t="n">
-        <v>-160535</v>
+        <v>-3817669</v>
       </c>
       <c r="F9" t="n">
-        <v>2988653</v>
+        <v>-35286937</v>
       </c>
       <c r="G9" t="n">
-        <v>3034052</v>
+        <v>-33668209</v>
       </c>
       <c r="H9" t="n">
-        <v>25660834</v>
+        <v>1552475</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -13,196 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2423705</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1256389</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-12315885</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-15757253</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-12061081</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3596</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2583991</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2350913</v>
+      </c>
+      <c r="F11" t="n">
+        <v>471418</v>
+      </c>
+      <c r="G11" t="n">
+        <v>13058</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-17800285</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>智易</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>959285</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-4923994</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-7061039</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-6466594</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-9012959</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-545668</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-47548</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2409304</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2988653</v>
+      </c>
+      <c r="H13" t="n">
+        <v>19798366</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>107738</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-59129</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-683438</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-505714</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-20701575</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>長榮航太</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>🔴 5d 翻紅</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-682050</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1343015</v>
+      </c>
+      <c r="F15" t="n">
+        <v>445152</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1527392</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-2445129</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>建榮</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -14,159 千)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="n">
-        <v>-22900019</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-33364102</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-109558780</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-96362689</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-126278486</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>鴻海</t>
+      <c r="D16" t="n">
+        <v>-82109081</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-98385683</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-121543329</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-107384517</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-123813271</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -8,757 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>20019852</v>
+      </c>
+      <c r="E17" t="n">
+        <v>22435770</v>
+      </c>
+      <c r="F17" t="n">
+        <v>67309746</v>
+      </c>
+      <c r="G17" t="n">
+        <v>76066385</v>
+      </c>
+      <c r="H17" t="n">
+        <v>123604406</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>中華電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,287 +466,287 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 23,987 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 10,245 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>-5464743</v>
+        <v>1791819</v>
       </c>
       <c r="E2" t="n">
-        <v>-41222492</v>
+        <v>-2977067</v>
       </c>
       <c r="F2" t="n">
-        <v>9354629</v>
+        <v>-25042316</v>
       </c>
       <c r="G2" t="n">
-        <v>-14632154</v>
+        <v>-35286937</v>
       </c>
       <c r="H2" t="n">
-        <v>-64957746</v>
+        <v>11975012</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 8,288 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 23,418 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>7743099</v>
+        <v>17758390</v>
       </c>
       <c r="E3" t="n">
-        <v>-2790467</v>
+        <v>-5464743</v>
       </c>
       <c r="F3" t="n">
-        <v>-38438749</v>
+        <v>32772363</v>
       </c>
       <c r="G3" t="n">
-        <v>-46726690</v>
+        <v>9354629</v>
       </c>
       <c r="H3" t="n">
-        <v>-4614950</v>
+        <v>-62200576</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -28,418 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>531729</v>
+        <v>-28580499</v>
       </c>
       <c r="E4" t="n">
-        <v>-22900019</v>
+        <v>-55363074</v>
       </c>
       <c r="F4" t="n">
-        <v>-114585274</v>
+        <v>-72776193</v>
       </c>
       <c r="G4" t="n">
-        <v>-109558780</v>
+        <v>-44358062</v>
       </c>
       <c r="H4" t="n">
-        <v>-144168089</v>
+        <v>31954602</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 10,669 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 36,870 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-6387125</v>
+        <v>28533602</v>
       </c>
       <c r="E5" t="n">
-        <v>-43831776</v>
+        <v>531729</v>
       </c>
       <c r="F5" t="n">
-        <v>72580052</v>
+        <v>-77715364</v>
       </c>
       <c r="G5" t="n">
-        <v>61911428</v>
+        <v>-114585274</v>
       </c>
       <c r="H5" t="n">
-        <v>114178970</v>
+        <v>-108667680</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -31,048 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>8501543</v>
+        <v>-5488548</v>
       </c>
       <c r="E6" t="n">
-        <v>8031659</v>
+        <v>-6387125</v>
       </c>
       <c r="F6" t="n">
-        <v>4226890</v>
+        <v>41532026</v>
       </c>
       <c r="G6" t="n">
-        <v>-1037727</v>
+        <v>72580052</v>
       </c>
       <c r="H6" t="n">
-        <v>-63196736</v>
+        <v>169236631</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-25924016</v>
+        <v>9976527</v>
       </c>
       <c r="E7" t="n">
-        <v>-28230999</v>
+        <v>8501543</v>
       </c>
       <c r="F7" t="n">
-        <v>8950020</v>
+        <v>7167691</v>
       </c>
       <c r="G7" t="n">
-        <v>13371136</v>
+        <v>4226890</v>
       </c>
       <c r="H7" t="n">
-        <v>52684777</v>
+        <v>-61614556</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-55363074</v>
+        <v>-26356575</v>
       </c>
       <c r="E8" t="n">
-        <v>-92873950</v>
+        <v>-25924016</v>
       </c>
       <c r="F8" t="n">
-        <v>-44358062</v>
+        <v>1800262</v>
       </c>
       <c r="G8" t="n">
-        <v>-40114437</v>
+        <v>8950020</v>
       </c>
       <c r="H8" t="n">
-        <v>30287297</v>
+        <v>55803727</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-2977067</v>
+        <v>2576374</v>
       </c>
       <c r="E9" t="n">
-        <v>-3817669</v>
+        <v>2423705</v>
       </c>
       <c r="F9" t="n">
-        <v>-35286937</v>
+        <v>-10867121</v>
       </c>
       <c r="G9" t="n">
-        <v>-33668209</v>
+        <v>-12315885</v>
       </c>
       <c r="H9" t="n">
-        <v>1552475</v>
+        <v>-12520859</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,23 +758,23 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2423705</v>
+        <v>11942838</v>
       </c>
       <c r="E10" t="n">
-        <v>1256389</v>
+        <v>7743099</v>
       </c>
       <c r="F10" t="n">
-        <v>-12315885</v>
+        <v>-33907718</v>
       </c>
       <c r="G10" t="n">
-        <v>-15757253</v>
+        <v>-38438749</v>
       </c>
       <c r="H10" t="n">
-        <v>-12061081</v>
+        <v>-1874693</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
+        <v>2597040</v>
+      </c>
+      <c r="E11" t="n">
         <v>2583991</v>
       </c>
-      <c r="E11" t="n">
-        <v>2350913</v>
-      </c>
       <c r="F11" t="n">
+        <v>1007467</v>
+      </c>
+      <c r="G11" t="n">
         <v>471418</v>
       </c>
-      <c r="G11" t="n">
-        <v>13058</v>
-      </c>
       <c r="H11" t="n">
-        <v>-17800285</v>
+        <v>-16876139</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -816,77 +816,77 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 📈 20d 巨變(加碼 9,514 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>959285</v>
+        <v>100157</v>
       </c>
       <c r="E12" t="n">
-        <v>-4923994</v>
+        <v>-112223</v>
       </c>
       <c r="F12" t="n">
-        <v>-7061039</v>
+        <v>-2170507</v>
       </c>
       <c r="G12" t="n">
-        <v>-6466594</v>
+        <v>-11684969</v>
       </c>
       <c r="H12" t="n">
-        <v>-9012959</v>
+        <v>-12956379</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-545668</v>
+        <v>281590</v>
       </c>
       <c r="E13" t="n">
-        <v>-47548</v>
+        <v>-1924670</v>
       </c>
       <c r="F13" t="n">
-        <v>2409304</v>
+        <v>-5342086</v>
       </c>
       <c r="G13" t="n">
-        <v>2988653</v>
+        <v>-2960235</v>
       </c>
       <c r="H13" t="n">
-        <v>19798366</v>
+        <v>3056411</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,128 +898,198 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>107738</v>
+        <v>505094</v>
       </c>
       <c r="E14" t="n">
-        <v>-59129</v>
+        <v>-229982</v>
       </c>
       <c r="F14" t="n">
-        <v>-683438</v>
+        <v>-1204547</v>
       </c>
       <c r="G14" t="n">
-        <v>-505714</v>
+        <v>-864816</v>
       </c>
       <c r="H14" t="n">
-        <v>-20701575</v>
+        <v>-14802846</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-682050</v>
+        <v>-730654</v>
       </c>
       <c r="E15" t="n">
-        <v>1343015</v>
+        <v>-545668</v>
       </c>
       <c r="F15" t="n">
-        <v>445152</v>
+        <v>2104859</v>
       </c>
       <c r="G15" t="n">
-        <v>1527392</v>
+        <v>2409304</v>
       </c>
       <c r="H15" t="n">
-        <v>-2445129</v>
+        <v>18181990</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -14,159 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-82109081</v>
+        <v>-1631216</v>
       </c>
       <c r="E16" t="n">
-        <v>-98385683</v>
+        <v>1053781</v>
       </c>
       <c r="F16" t="n">
-        <v>-121543329</v>
+        <v>-451812</v>
       </c>
       <c r="G16" t="n">
-        <v>-107384517</v>
+        <v>165189</v>
       </c>
       <c r="H16" t="n">
-        <v>-123813271</v>
+        <v>-3505916</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8,757 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-6844773</v>
+      </c>
+      <c r="E17" t="n">
+        <v>959285</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-13104223</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-7061039</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-13247513</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -12,193 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="n">
-        <v>20019852</v>
-      </c>
-      <c r="E17" t="n">
-        <v>22435770</v>
-      </c>
-      <c r="F17" t="n">
-        <v>67309746</v>
-      </c>
-      <c r="G17" t="n">
-        <v>76066385</v>
-      </c>
-      <c r="H17" t="n">
-        <v>123604406</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>中華電</t>
+      <c r="D18" t="n">
+        <v>-81510738</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-82109081</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-133736579</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-121543329</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-130608829</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 11,297 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>27041426</v>
+      </c>
+      <c r="E19" t="n">
+        <v>36706974</v>
+      </c>
+      <c r="F19" t="n">
+        <v>71630007</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60333405</v>
+      </c>
+      <c r="H19" t="n">
+        <v>99209660</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>長榮航</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 10,245 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
+        <v>5596562</v>
+      </c>
+      <c r="E2" t="n">
         <v>1791819</v>
       </c>
-      <c r="E2" t="n">
-        <v>-2977067</v>
-      </c>
       <c r="F2" t="n">
+        <v>-23380772</v>
+      </c>
+      <c r="G2" t="n">
         <v>-25042316</v>
       </c>
-      <c r="G2" t="n">
-        <v>-35286937</v>
-      </c>
       <c r="H2" t="n">
-        <v>11975012</v>
+        <v>12381435</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,280 +501,280 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 23,418 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>17758390</v>
+        <v>19824512</v>
       </c>
       <c r="E3" t="n">
-        <v>-5464743</v>
+        <v>11942838</v>
       </c>
       <c r="F3" t="n">
-        <v>32772363</v>
+        <v>-28809176</v>
       </c>
       <c r="G3" t="n">
-        <v>9354629</v>
+        <v>-33907718</v>
       </c>
       <c r="H3" t="n">
-        <v>-62200576</v>
+        <v>2235806</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -28,418 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -10,561 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-28580499</v>
+        <v>-10487691</v>
       </c>
       <c r="E4" t="n">
-        <v>-55363074</v>
+        <v>-26356575</v>
       </c>
       <c r="F4" t="n">
-        <v>-72776193</v>
+        <v>-8760503</v>
       </c>
       <c r="G4" t="n">
-        <v>-44358062</v>
+        <v>1800262</v>
       </c>
       <c r="H4" t="n">
-        <v>31954602</v>
+        <v>50365983</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 36,870 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>28533602</v>
+        <v>6840020</v>
       </c>
       <c r="E5" t="n">
-        <v>531729</v>
+        <v>9976527</v>
       </c>
       <c r="F5" t="n">
-        <v>-77715364</v>
+        <v>9387896</v>
       </c>
       <c r="G5" t="n">
-        <v>-114585274</v>
+        <v>7167691</v>
       </c>
       <c r="H5" t="n">
-        <v>-108667680</v>
+        <v>-59341658</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -31,048 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-5488548</v>
+        <v>691927</v>
       </c>
       <c r="E6" t="n">
-        <v>-6387125</v>
+        <v>-512672</v>
       </c>
       <c r="F6" t="n">
-        <v>41532026</v>
+        <v>-13611431</v>
       </c>
       <c r="G6" t="n">
-        <v>72580052</v>
+        <v>-12903063</v>
       </c>
       <c r="H6" t="n">
-        <v>169236631</v>
+        <v>-15223328</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>9976527</v>
+        <v>-14948793</v>
       </c>
       <c r="E7" t="n">
-        <v>8501543</v>
+        <v>-28580499</v>
       </c>
       <c r="F7" t="n">
-        <v>7167691</v>
+        <v>-70176095</v>
       </c>
       <c r="G7" t="n">
-        <v>4226890</v>
+        <v>-72776193</v>
       </c>
       <c r="H7" t="n">
-        <v>-61614556</v>
+        <v>30432069</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-26356575</v>
+        <v>2438445</v>
       </c>
       <c r="E8" t="n">
-        <v>-25924016</v>
+        <v>2576374</v>
       </c>
       <c r="F8" t="n">
-        <v>1800262</v>
+        <v>-9809566</v>
       </c>
       <c r="G8" t="n">
-        <v>8950020</v>
+        <v>-10867121</v>
       </c>
       <c r="H8" t="n">
-        <v>55803727</v>
+        <v>-12764189</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2576374</v>
+        <v>64886427</v>
       </c>
       <c r="E9" t="n">
-        <v>2423705</v>
+        <v>17758390</v>
       </c>
       <c r="F9" t="n">
-        <v>-10867121</v>
+        <v>35195333</v>
       </c>
       <c r="G9" t="n">
-        <v>-12315885</v>
+        <v>32772363</v>
       </c>
       <c r="H9" t="n">
-        <v>-12520859</v>
+        <v>-57677779</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>11942838</v>
+        <v>-1721666</v>
       </c>
       <c r="E10" t="n">
-        <v>7743099</v>
+        <v>-1177473</v>
       </c>
       <c r="F10" t="n">
-        <v>-33907718</v>
+        <v>669085</v>
       </c>
       <c r="G10" t="n">
-        <v>-38438749</v>
+        <v>-394251</v>
       </c>
       <c r="H10" t="n">
-        <v>-1874693</v>
+        <v>-11669557</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
+        <v>2895022</v>
+      </c>
+      <c r="E11" t="n">
         <v>2597040</v>
       </c>
-      <c r="E11" t="n">
-        <v>2583991</v>
-      </c>
       <c r="F11" t="n">
+        <v>1547177</v>
+      </c>
+      <c r="G11" t="n">
         <v>1007467</v>
       </c>
-      <c r="G11" t="n">
-        <v>471418</v>
-      </c>
       <c r="H11" t="n">
-        <v>-16876139</v>
+        <v>-16568139</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -816,77 +816,77 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 📈 20d 巨變(加碼 9,514 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>100157</v>
+        <v>43551893</v>
       </c>
       <c r="E12" t="n">
-        <v>-112223</v>
+        <v>28533602</v>
       </c>
       <c r="F12" t="n">
-        <v>-2170507</v>
+        <v>-70272245</v>
       </c>
       <c r="G12" t="n">
-        <v>-11684969</v>
+        <v>-77715364</v>
       </c>
       <c r="H12" t="n">
-        <v>-12956379</v>
+        <v>-106928256</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>281590</v>
+        <v>417934</v>
       </c>
       <c r="E13" t="n">
-        <v>-1924670</v>
+        <v>505094</v>
       </c>
       <c r="F13" t="n">
-        <v>-5342086</v>
+        <v>-1843368</v>
       </c>
       <c r="G13" t="n">
-        <v>-2960235</v>
+        <v>-1204547</v>
       </c>
       <c r="H13" t="n">
-        <v>3056411</v>
+        <v>-15163645</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,30 +898,30 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>505094</v>
+        <v>-248166</v>
       </c>
       <c r="E14" t="n">
-        <v>-229982</v>
+        <v>-730654</v>
       </c>
       <c r="F14" t="n">
-        <v>-1204547</v>
+        <v>2137366</v>
       </c>
       <c r="G14" t="n">
-        <v>-864816</v>
+        <v>2104859</v>
       </c>
       <c r="H14" t="n">
-        <v>-14802846</v>
+        <v>18197202</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,93 +933,93 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-730654</v>
+        <v>706234</v>
       </c>
       <c r="E15" t="n">
-        <v>-545668</v>
+        <v>-61279</v>
       </c>
       <c r="F15" t="n">
-        <v>2104859</v>
+        <v>-67579</v>
       </c>
       <c r="G15" t="n">
-        <v>2409304</v>
+        <v>-389938</v>
       </c>
       <c r="H15" t="n">
-        <v>18181990</v>
+        <v>-20159274</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 21,504 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-1631216</v>
+        <v>11649726</v>
       </c>
       <c r="E16" t="n">
-        <v>1053781</v>
+        <v>-5488548</v>
       </c>
       <c r="F16" t="n">
-        <v>-451812</v>
+        <v>63036168</v>
       </c>
       <c r="G16" t="n">
-        <v>165189</v>
+        <v>41532026</v>
       </c>
       <c r="H16" t="n">
-        <v>-3505916</v>
+        <v>167528791</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-6844773</v>
+        <v>336215</v>
       </c>
       <c r="E17" t="n">
-        <v>959285</v>
+        <v>-333272</v>
       </c>
       <c r="F17" t="n">
-        <v>-13104223</v>
+        <v>-5881429</v>
       </c>
       <c r="G17" t="n">
-        <v>-7061039</v>
+        <v>-6068532</v>
       </c>
       <c r="H17" t="n">
-        <v>-13247513</v>
+        <v>-5557712</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
@@ -1031,26 +1031,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12,193 千)</t>
+          <t>📉 20d 巨變(減碼 -15,384 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
+        <v>-60093999</v>
+      </c>
+      <c r="E18" t="n">
         <v>-81510738</v>
       </c>
-      <c r="E18" t="n">
-        <v>-82109081</v>
-      </c>
       <c r="F18" t="n">
+        <v>-149120709</v>
+      </c>
+      <c r="G18" t="n">
         <v>-133736579</v>
       </c>
-      <c r="G18" t="n">
-        <v>-121543329</v>
-      </c>
       <c r="H18" t="n">
-        <v>-130608829</v>
+        <v>-143303455</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1061,35 +1061,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11,297 千)</t>
+          <t>📉 20d 巨變(減碼 -16,911 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>27041426</v>
+        <v>-24880920</v>
       </c>
       <c r="E19" t="n">
-        <v>36706974</v>
+        <v>-35115989</v>
       </c>
       <c r="F19" t="n">
-        <v>71630007</v>
+        <v>-64508776</v>
       </c>
       <c r="G19" t="n">
-        <v>60333405</v>
+        <v>-47597399</v>
       </c>
       <c r="H19" t="n">
-        <v>99209660</v>
+        <v>-125376217</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,13 +481,13 @@
         <v>5596562</v>
       </c>
       <c r="E2" t="n">
-        <v>1791819</v>
+        <v>5596562</v>
       </c>
       <c r="F2" t="n">
         <v>-23380772</v>
       </c>
       <c r="G2" t="n">
-        <v>-25042316</v>
+        <v>-23380772</v>
       </c>
       <c r="H2" t="n">
         <v>12381435</v>
@@ -516,13 +516,13 @@
         <v>19824512</v>
       </c>
       <c r="E3" t="n">
-        <v>11942838</v>
+        <v>19824512</v>
       </c>
       <c r="F3" t="n">
         <v>-28809176</v>
       </c>
       <c r="G3" t="n">
-        <v>-33907718</v>
+        <v>-28809176</v>
       </c>
       <c r="H3" t="n">
         <v>2235806</v>
@@ -536,112 +536,112 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -10,561 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>-10487691</v>
+        <v>6840020</v>
       </c>
       <c r="E4" t="n">
-        <v>-26356575</v>
+        <v>6840020</v>
       </c>
       <c r="F4" t="n">
-        <v>-8760503</v>
+        <v>9387896</v>
       </c>
       <c r="G4" t="n">
-        <v>1800262</v>
+        <v>9387896</v>
       </c>
       <c r="H4" t="n">
-        <v>50365983</v>
+        <v>-59341658</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>6840020</v>
+        <v>691927</v>
       </c>
       <c r="E5" t="n">
-        <v>9976527</v>
+        <v>691927</v>
       </c>
       <c r="F5" t="n">
-        <v>9387896</v>
+        <v>-13611431</v>
       </c>
       <c r="G5" t="n">
-        <v>7167691</v>
+        <v>-13611431</v>
       </c>
       <c r="H5" t="n">
-        <v>-59341658</v>
+        <v>-15223328</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>691927</v>
+        <v>-14948793</v>
       </c>
       <c r="E6" t="n">
-        <v>-512672</v>
+        <v>-14948793</v>
       </c>
       <c r="F6" t="n">
-        <v>-13611431</v>
+        <v>-70176095</v>
       </c>
       <c r="G6" t="n">
-        <v>-12903063</v>
+        <v>-70176095</v>
       </c>
       <c r="H6" t="n">
-        <v>-15223328</v>
+        <v>30432069</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,23 +653,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-14948793</v>
+        <v>-10487691</v>
       </c>
       <c r="E7" t="n">
-        <v>-28580499</v>
+        <v>-10487691</v>
       </c>
       <c r="F7" t="n">
-        <v>-70176095</v>
+        <v>-8760503</v>
       </c>
       <c r="G7" t="n">
-        <v>-72776193</v>
+        <v>-8760503</v>
       </c>
       <c r="H7" t="n">
-        <v>30432069</v>
+        <v>50365983</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
@@ -691,13 +691,13 @@
         <v>2438445</v>
       </c>
       <c r="E8" t="n">
-        <v>2576374</v>
+        <v>2438445</v>
       </c>
       <c r="F8" t="n">
         <v>-9809566</v>
       </c>
       <c r="G8" t="n">
-        <v>-10867121</v>
+        <v>-9809566</v>
       </c>
       <c r="H8" t="n">
         <v>-12764189</v>
@@ -726,13 +726,13 @@
         <v>64886427</v>
       </c>
       <c r="E9" t="n">
-        <v>17758390</v>
+        <v>64886427</v>
       </c>
       <c r="F9" t="n">
         <v>35195333</v>
       </c>
       <c r="G9" t="n">
-        <v>32772363</v>
+        <v>35195333</v>
       </c>
       <c r="H9" t="n">
         <v>-57677779</v>
@@ -761,13 +761,13 @@
         <v>-1721666</v>
       </c>
       <c r="E10" t="n">
-        <v>-1177473</v>
+        <v>-1721666</v>
       </c>
       <c r="F10" t="n">
         <v>669085</v>
       </c>
       <c r="G10" t="n">
-        <v>-394251</v>
+        <v>669085</v>
       </c>
       <c r="H10" t="n">
         <v>-11669557</v>
@@ -796,13 +796,13 @@
         <v>2895022</v>
       </c>
       <c r="E11" t="n">
-        <v>2597040</v>
+        <v>2895022</v>
       </c>
       <c r="F11" t="n">
         <v>1547177</v>
       </c>
       <c r="G11" t="n">
-        <v>1007467</v>
+        <v>1547177</v>
       </c>
       <c r="H11" t="n">
         <v>-16568139</v>
@@ -831,13 +831,13 @@
         <v>43551893</v>
       </c>
       <c r="E12" t="n">
-        <v>28533602</v>
+        <v>43551893</v>
       </c>
       <c r="F12" t="n">
         <v>-70272245</v>
       </c>
       <c r="G12" t="n">
-        <v>-77715364</v>
+        <v>-70272245</v>
       </c>
       <c r="H12" t="n">
         <v>-106928256</v>
@@ -866,13 +866,13 @@
         <v>417934</v>
       </c>
       <c r="E13" t="n">
-        <v>505094</v>
+        <v>417934</v>
       </c>
       <c r="F13" t="n">
         <v>-1843368</v>
       </c>
       <c r="G13" t="n">
-        <v>-1204547</v>
+        <v>-1843368</v>
       </c>
       <c r="H13" t="n">
         <v>-15163645</v>
@@ -901,13 +901,13 @@
         <v>-248166</v>
       </c>
       <c r="E14" t="n">
-        <v>-730654</v>
+        <v>-248166</v>
       </c>
       <c r="F14" t="n">
         <v>2137366</v>
       </c>
       <c r="G14" t="n">
-        <v>2104859</v>
+        <v>2137366</v>
       </c>
       <c r="H14" t="n">
         <v>18197202</v>
@@ -936,13 +936,13 @@
         <v>706234</v>
       </c>
       <c r="E15" t="n">
-        <v>-61279</v>
+        <v>706234</v>
       </c>
       <c r="F15" t="n">
         <v>-67579</v>
       </c>
       <c r="G15" t="n">
-        <v>-389938</v>
+        <v>-67579</v>
       </c>
       <c r="H15" t="n">
         <v>-20159274</v>
@@ -956,140 +956,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 21,504 千)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>11649726</v>
+        <v>336215</v>
       </c>
       <c r="E16" t="n">
-        <v>-5488548</v>
+        <v>336215</v>
       </c>
       <c r="F16" t="n">
-        <v>63036168</v>
+        <v>-5881429</v>
       </c>
       <c r="G16" t="n">
-        <v>41532026</v>
+        <v>-5881429</v>
       </c>
       <c r="H16" t="n">
-        <v>167528791</v>
+        <v>-5557712</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>336215</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-333272</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-5881429</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-6068532</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-5557712</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
           <t>勤誠</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -15,384 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-60093999</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-81510738</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-149120709</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-133736579</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-143303455</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -16,911 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-24880920</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-35115989</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-64508776</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-47597399</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-125376217</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>國巨*</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>-23380772</v>
       </c>
       <c r="H2" t="n">
-        <v>12381435</v>
+        <v>10859977</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,357 +501,357 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>19824512</v>
+        <v>6840020</v>
       </c>
       <c r="E3" t="n">
-        <v>19824512</v>
+        <v>6840020</v>
       </c>
       <c r="F3" t="n">
-        <v>-28809176</v>
+        <v>9387896</v>
       </c>
       <c r="G3" t="n">
-        <v>-28809176</v>
+        <v>9387896</v>
       </c>
       <c r="H3" t="n">
-        <v>2235806</v>
+        <v>-25408038</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6840020</v>
+        <v>691927</v>
       </c>
       <c r="E4" t="n">
-        <v>6840020</v>
+        <v>691927</v>
       </c>
       <c r="F4" t="n">
-        <v>9387896</v>
+        <v>-13611431</v>
       </c>
       <c r="G4" t="n">
-        <v>9387896</v>
+        <v>-13611431</v>
       </c>
       <c r="H4" t="n">
-        <v>-59341658</v>
+        <v>-14650300</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>691927</v>
+        <v>-10487691</v>
       </c>
       <c r="E5" t="n">
-        <v>691927</v>
+        <v>-10487691</v>
       </c>
       <c r="F5" t="n">
-        <v>-13611431</v>
+        <v>-8760503</v>
       </c>
       <c r="G5" t="n">
-        <v>-13611431</v>
+        <v>-8760503</v>
       </c>
       <c r="H5" t="n">
-        <v>-15223328</v>
+        <v>52178927</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-14948793</v>
+        <v>2438445</v>
       </c>
       <c r="E6" t="n">
-        <v>-14948793</v>
+        <v>2438445</v>
       </c>
       <c r="F6" t="n">
-        <v>-70176095</v>
+        <v>-9809566</v>
       </c>
       <c r="G6" t="n">
-        <v>-70176095</v>
+        <v>-9809566</v>
       </c>
       <c r="H6" t="n">
-        <v>30432069</v>
+        <v>-14521444</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-10487691</v>
+        <v>64886427</v>
       </c>
       <c r="E7" t="n">
-        <v>-10487691</v>
+        <v>64886427</v>
       </c>
       <c r="F7" t="n">
-        <v>-8760503</v>
+        <v>35195333</v>
       </c>
       <c r="G7" t="n">
-        <v>-8760503</v>
+        <v>35195333</v>
       </c>
       <c r="H7" t="n">
-        <v>50365983</v>
+        <v>-75809962</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2438445</v>
+        <v>2895022</v>
       </c>
       <c r="E8" t="n">
-        <v>2438445</v>
+        <v>2895022</v>
       </c>
       <c r="F8" t="n">
-        <v>-9809566</v>
+        <v>1547177</v>
       </c>
       <c r="G8" t="n">
-        <v>-9809566</v>
+        <v>1547177</v>
       </c>
       <c r="H8" t="n">
-        <v>-12764189</v>
+        <v>-11981961</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>64886427</v>
+        <v>19824512</v>
       </c>
       <c r="E9" t="n">
-        <v>64886427</v>
+        <v>19824512</v>
       </c>
       <c r="F9" t="n">
-        <v>35195333</v>
+        <v>-28809176</v>
       </c>
       <c r="G9" t="n">
-        <v>35195333</v>
+        <v>-28809176</v>
       </c>
       <c r="H9" t="n">
-        <v>-57677779</v>
+        <v>-30090756</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1721666</v>
+        <v>43551893</v>
       </c>
       <c r="E10" t="n">
-        <v>-1721666</v>
+        <v>43551893</v>
       </c>
       <c r="F10" t="n">
-        <v>669085</v>
+        <v>-70272245</v>
       </c>
       <c r="G10" t="n">
-        <v>669085</v>
+        <v>-70272245</v>
       </c>
       <c r="H10" t="n">
-        <v>-11669557</v>
+        <v>-143040965</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2895022</v>
+        <v>417934</v>
       </c>
       <c r="E11" t="n">
-        <v>2895022</v>
+        <v>417934</v>
       </c>
       <c r="F11" t="n">
-        <v>1547177</v>
+        <v>-1843368</v>
       </c>
       <c r="G11" t="n">
-        <v>1547177</v>
+        <v>-1843368</v>
       </c>
       <c r="H11" t="n">
-        <v>-16568139</v>
+        <v>-13304323</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>43551893</v>
+        <v>-248166</v>
       </c>
       <c r="E12" t="n">
-        <v>43551893</v>
+        <v>-248166</v>
       </c>
       <c r="F12" t="n">
-        <v>-70272245</v>
+        <v>2137366</v>
       </c>
       <c r="G12" t="n">
-        <v>-70272245</v>
+        <v>2137366</v>
       </c>
       <c r="H12" t="n">
-        <v>-106928256</v>
+        <v>17800543</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,126 +863,56 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>417934</v>
+        <v>706234</v>
       </c>
       <c r="E13" t="n">
-        <v>417934</v>
+        <v>706234</v>
       </c>
       <c r="F13" t="n">
-        <v>-1843368</v>
+        <v>-67579</v>
       </c>
       <c r="G13" t="n">
-        <v>-1843368</v>
+        <v>-67579</v>
       </c>
       <c r="H13" t="n">
-        <v>-15163645</v>
+        <v>-17531743</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-248166</v>
+        <v>336215</v>
       </c>
       <c r="E14" t="n">
-        <v>-248166</v>
+        <v>336215</v>
       </c>
       <c r="F14" t="n">
-        <v>2137366</v>
+        <v>-5881429</v>
       </c>
       <c r="G14" t="n">
-        <v>2137366</v>
+        <v>-5881429</v>
       </c>
       <c r="H14" t="n">
-        <v>18197202</v>
+        <v>-4821499</v>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>建準</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>706234</v>
-      </c>
-      <c r="E15" t="n">
-        <v>706234</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-67579</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-67579</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-20159274</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>長榮航太</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>336215</v>
-      </c>
-      <c r="E16" t="n">
-        <v>336215</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-5881429</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-5881429</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-5557712</v>
-      </c>
-      <c r="I16" t="inlineStr">
         <is>
           <t>勤誠</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,182 +466,182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 34,011 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>5596562</v>
+        <v>4400649</v>
       </c>
       <c r="E2" t="n">
-        <v>5596562</v>
+        <v>-14948793</v>
       </c>
       <c r="F2" t="n">
-        <v>-23380772</v>
+        <v>-36164965</v>
       </c>
       <c r="G2" t="n">
-        <v>-23380772</v>
+        <v>-70176095</v>
       </c>
       <c r="H2" t="n">
-        <v>10859977</v>
+        <v>-31703878</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>6840020</v>
+        <v>7514271</v>
       </c>
       <c r="E3" t="n">
-        <v>6840020</v>
+        <v>5596562</v>
       </c>
       <c r="F3" t="n">
-        <v>9387896</v>
+        <v>-17378308</v>
       </c>
       <c r="G3" t="n">
-        <v>9387896</v>
+        <v>-23380772</v>
       </c>
       <c r="H3" t="n">
-        <v>-25408038</v>
+        <v>19292744</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -13,761 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>691927</v>
+        <v>-14238175</v>
       </c>
       <c r="E4" t="n">
-        <v>691927</v>
+        <v>-10487691</v>
       </c>
       <c r="F4" t="n">
-        <v>-13611431</v>
+        <v>-22521282</v>
       </c>
       <c r="G4" t="n">
-        <v>-13611431</v>
+        <v>-8760503</v>
       </c>
       <c r="H4" t="n">
-        <v>-14650300</v>
+        <v>42136439</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 28,669 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-10487691</v>
+        <v>52752728</v>
       </c>
       <c r="E5" t="n">
-        <v>-10487691</v>
+        <v>64886427</v>
       </c>
       <c r="F5" t="n">
-        <v>-8760503</v>
+        <v>63864807</v>
       </c>
       <c r="G5" t="n">
-        <v>-8760503</v>
+        <v>35195333</v>
       </c>
       <c r="H5" t="n">
-        <v>52178927</v>
+        <v>-88015706</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 18,180 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2438445</v>
+        <v>32916595</v>
       </c>
       <c r="E6" t="n">
-        <v>2438445</v>
+        <v>19824512</v>
       </c>
       <c r="F6" t="n">
-        <v>-9809566</v>
+        <v>-10628730</v>
       </c>
       <c r="G6" t="n">
-        <v>-9809566</v>
+        <v>-28809176</v>
       </c>
       <c r="H6" t="n">
-        <v>-14521444</v>
+        <v>-20428418</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,65 +653,65 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>64886427</v>
+        <v>4650760</v>
       </c>
       <c r="E7" t="n">
-        <v>64886427</v>
+        <v>6840020</v>
       </c>
       <c r="F7" t="n">
-        <v>35195333</v>
+        <v>11464578</v>
       </c>
       <c r="G7" t="n">
-        <v>35195333</v>
+        <v>9387896</v>
       </c>
       <c r="H7" t="n">
-        <v>-75809962</v>
+        <v>-18438558</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2895022</v>
+        <v>248399</v>
       </c>
       <c r="E8" t="n">
-        <v>2895022</v>
+        <v>691927</v>
       </c>
       <c r="F8" t="n">
-        <v>1547177</v>
+        <v>-12565968</v>
       </c>
       <c r="G8" t="n">
-        <v>1547177</v>
+        <v>-13611431</v>
       </c>
       <c r="H8" t="n">
-        <v>-11981961</v>
+        <v>-15023414</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,135 +723,135 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>19824512</v>
+        <v>2421578</v>
       </c>
       <c r="E9" t="n">
-        <v>19824512</v>
+        <v>2438445</v>
       </c>
       <c r="F9" t="n">
-        <v>-28809176</v>
+        <v>-7826694</v>
       </c>
       <c r="G9" t="n">
-        <v>-28809176</v>
+        <v>-9809566</v>
       </c>
       <c r="H9" t="n">
-        <v>-30090756</v>
+        <v>-15380997</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>43551893</v>
+        <v>1282984</v>
       </c>
       <c r="E10" t="n">
-        <v>43551893</v>
+        <v>2895022</v>
       </c>
       <c r="F10" t="n">
-        <v>-70272245</v>
+        <v>1991456</v>
       </c>
       <c r="G10" t="n">
-        <v>-70272245</v>
+        <v>1547177</v>
       </c>
       <c r="H10" t="n">
-        <v>-143040965</v>
+        <v>-10304157</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>417934</v>
+        <v>25853028</v>
       </c>
       <c r="E11" t="n">
-        <v>417934</v>
+        <v>43551893</v>
       </c>
       <c r="F11" t="n">
-        <v>-1843368</v>
+        <v>-72111831</v>
       </c>
       <c r="G11" t="n">
-        <v>-1843368</v>
+        <v>-70272245</v>
       </c>
       <c r="H11" t="n">
-        <v>-13304323</v>
+        <v>-104706063</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-248166</v>
+        <v>723683</v>
       </c>
       <c r="E12" t="n">
-        <v>-248166</v>
+        <v>706234</v>
       </c>
       <c r="F12" t="n">
-        <v>2137366</v>
+        <v>312925</v>
       </c>
       <c r="G12" t="n">
-        <v>2137366</v>
+        <v>-67579</v>
       </c>
       <c r="H12" t="n">
-        <v>17800543</v>
+        <v>-17067362</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,58 +863,163 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>706234</v>
+        <v>515793</v>
       </c>
       <c r="E13" t="n">
-        <v>706234</v>
+        <v>417934</v>
       </c>
       <c r="F13" t="n">
-        <v>-67579</v>
+        <v>-1454024</v>
       </c>
       <c r="G13" t="n">
-        <v>-67579</v>
+        <v>-1843368</v>
       </c>
       <c r="H13" t="n">
-        <v>-17531743</v>
+        <v>-12539378</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-603053</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-248166</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1524590</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2137366</v>
+      </c>
+      <c r="H14" t="n">
+        <v>17457308</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>8210</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C15" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
+        <v>386236</v>
+      </c>
+      <c r="E15" t="n">
         <v>336215</v>
       </c>
-      <c r="E14" t="n">
-        <v>336215</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="F15" t="n">
+        <v>-5896131</v>
+      </c>
+      <c r="G15" t="n">
         <v>-5881429</v>
       </c>
-      <c r="G14" t="n">
-        <v>-5881429</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-4821499</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="H15" t="n">
+        <v>-5131309</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>勤誠</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>🟢 5d 翻綠</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2152995</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-324570</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-4955314</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-4287981</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2808964</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>全友</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 14,705 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>21914657</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11649726</v>
+      </c>
+      <c r="F17" t="n">
+        <v>77741477</v>
+      </c>
+      <c r="G17" t="n">
+        <v>63036168</v>
+      </c>
+      <c r="H17" t="n">
+        <v>151351231</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,105 +466,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 34,011 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>4400649</v>
+        <v>13059088</v>
       </c>
       <c r="E2" t="n">
-        <v>-14948793</v>
+        <v>7514271</v>
       </c>
       <c r="F2" t="n">
-        <v>-36164965</v>
+        <v>-13209452</v>
       </c>
       <c r="G2" t="n">
-        <v>-70176095</v>
+        <v>-17378308</v>
       </c>
       <c r="H2" t="n">
-        <v>-31703878</v>
+        <v>14063843</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7514271</v>
+        <v>179790</v>
       </c>
       <c r="E3" t="n">
-        <v>5596562</v>
+        <v>-4145877</v>
       </c>
       <c r="F3" t="n">
-        <v>-17378308</v>
+        <v>-18859172</v>
       </c>
       <c r="G3" t="n">
-        <v>-23380772</v>
+        <v>-23928714</v>
       </c>
       <c r="H3" t="n">
-        <v>19292744</v>
+        <v>-37692021</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -13,761 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -23,767 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-14238175</v>
+        <v>15352374</v>
       </c>
       <c r="E4" t="n">
-        <v>-10487691</v>
+        <v>4400649</v>
       </c>
       <c r="F4" t="n">
-        <v>-22521282</v>
+        <v>-59932421</v>
       </c>
       <c r="G4" t="n">
-        <v>-8760503</v>
+        <v>-36164965</v>
       </c>
       <c r="H4" t="n">
-        <v>42136439</v>
+        <v>-16248893</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
@@ -576,26 +576,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 28,669 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 13,441 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
+        <v>64790795</v>
+      </c>
+      <c r="E5" t="n">
         <v>52752728</v>
       </c>
-      <c r="E5" t="n">
-        <v>64886427</v>
-      </c>
       <c r="F5" t="n">
+        <v>77305516</v>
+      </c>
+      <c r="G5" t="n">
         <v>63864807</v>
       </c>
-      <c r="G5" t="n">
-        <v>35195333</v>
-      </c>
       <c r="H5" t="n">
-        <v>-88015706</v>
+        <v>-78040549</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -611,26 +611,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 18,180 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 14,767 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
+        <v>43911841</v>
+      </c>
+      <c r="E6" t="n">
         <v>32916595</v>
       </c>
-      <c r="E6" t="n">
-        <v>19824512</v>
-      </c>
       <c r="F6" t="n">
+        <v>4138318</v>
+      </c>
+      <c r="G6" t="n">
         <v>-10628730</v>
       </c>
-      <c r="G6" t="n">
-        <v>-28809176</v>
-      </c>
       <c r="H6" t="n">
-        <v>-20428418</v>
+        <v>-24753076</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
+        <v>5905166</v>
+      </c>
+      <c r="E7" t="n">
         <v>4650760</v>
       </c>
-      <c r="E7" t="n">
-        <v>6840020</v>
-      </c>
       <c r="F7" t="n">
+        <v>12172514</v>
+      </c>
+      <c r="G7" t="n">
         <v>11464578</v>
       </c>
-      <c r="G7" t="n">
-        <v>9387896</v>
-      </c>
       <c r="H7" t="n">
-        <v>-18438558</v>
+        <v>-12287197</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
+        <v>5383841</v>
+      </c>
+      <c r="E8" t="n">
         <v>248399</v>
       </c>
-      <c r="E8" t="n">
-        <v>691927</v>
-      </c>
       <c r="F8" t="n">
+        <v>-8290413</v>
+      </c>
+      <c r="G8" t="n">
         <v>-12565968</v>
       </c>
-      <c r="G8" t="n">
-        <v>-13611431</v>
-      </c>
       <c r="H8" t="n">
-        <v>-15023414</v>
+        <v>-11088474</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -711,70 +711,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2421578</v>
+        <v>-12502716</v>
       </c>
       <c r="E9" t="n">
-        <v>2438445</v>
+        <v>-14238175</v>
       </c>
       <c r="F9" t="n">
-        <v>-7826694</v>
+        <v>-26421193</v>
       </c>
       <c r="G9" t="n">
-        <v>-9809566</v>
+        <v>-22521282</v>
       </c>
       <c r="H9" t="n">
-        <v>-15380997</v>
+        <v>39226834</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1282984</v>
+        <v>324181</v>
       </c>
       <c r="E10" t="n">
-        <v>2895022</v>
+        <v>2421578</v>
       </c>
       <c r="F10" t="n">
-        <v>1991456</v>
+        <v>-7714710</v>
       </c>
       <c r="G10" t="n">
-        <v>1547177</v>
+        <v>-7826694</v>
       </c>
       <c r="H10" t="n">
-        <v>-10304157</v>
+        <v>-16034877</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
+        <v>52037033</v>
+      </c>
+      <c r="E11" t="n">
         <v>25853028</v>
       </c>
-      <c r="E11" t="n">
-        <v>43551893</v>
-      </c>
       <c r="F11" t="n">
+        <v>-66672899</v>
+      </c>
+      <c r="G11" t="n">
         <v>-72111831</v>
       </c>
-      <c r="G11" t="n">
-        <v>-70272245</v>
-      </c>
       <c r="H11" t="n">
-        <v>-104706063</v>
+        <v>-96478272</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -816,42 +816,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>723683</v>
+        <v>-650363</v>
       </c>
       <c r="E12" t="n">
-        <v>706234</v>
+        <v>-603053</v>
       </c>
       <c r="F12" t="n">
-        <v>312925</v>
+        <v>1289656</v>
       </c>
       <c r="G12" t="n">
-        <v>-67579</v>
+        <v>1524590</v>
       </c>
       <c r="H12" t="n">
-        <v>-17067362</v>
+        <v>17494996</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,30 +863,30 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>515793</v>
+        <v>419617</v>
       </c>
       <c r="E13" t="n">
-        <v>417934</v>
+        <v>-77573</v>
       </c>
       <c r="F13" t="n">
-        <v>-1454024</v>
+        <v>-606924</v>
       </c>
       <c r="G13" t="n">
-        <v>-1843368</v>
+        <v>-1072851</v>
       </c>
       <c r="H13" t="n">
-        <v>-12539378</v>
+        <v>-15472352</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,126 +898,231 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-603053</v>
+        <v>188020</v>
       </c>
       <c r="E14" t="n">
-        <v>-248166</v>
+        <v>-53547</v>
       </c>
       <c r="F14" t="n">
-        <v>1524590</v>
+        <v>-1055916</v>
       </c>
       <c r="G14" t="n">
-        <v>2137366</v>
+        <v>-1544958</v>
       </c>
       <c r="H14" t="n">
-        <v>17457308</v>
+        <v>-20066514</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>386236</v>
+        <v>366519</v>
       </c>
       <c r="E15" t="n">
-        <v>336215</v>
+        <v>723683</v>
       </c>
       <c r="F15" t="n">
-        <v>-5896131</v>
+        <v>-19000</v>
       </c>
       <c r="G15" t="n">
-        <v>-5881429</v>
+        <v>312925</v>
       </c>
       <c r="H15" t="n">
-        <v>-5131309</v>
+        <v>-14536132</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2152995</v>
+        <v>501246</v>
       </c>
       <c r="E16" t="n">
-        <v>-324570</v>
+        <v>386236</v>
       </c>
       <c r="F16" t="n">
-        <v>-4955314</v>
+        <v>-5886855</v>
       </c>
       <c r="G16" t="n">
-        <v>-4287981</v>
+        <v>-5896131</v>
       </c>
       <c r="H16" t="n">
-        <v>2808964</v>
+        <v>-5653228</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14,705 千)</t>
+          <t>📉 20d 巨變(減碼 -10,298 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
+        <v>-33006598</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-39666288</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-156708020</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-146409636</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-155289027</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -11,798 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16283869</v>
+      </c>
+      <c r="E18" t="n">
+        <v>20279222</v>
+      </c>
+      <c r="F18" t="n">
+        <v>65946637</v>
+      </c>
+      <c r="G18" t="n">
+        <v>77744958</v>
+      </c>
+      <c r="H18" t="n">
+        <v>146767536</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 12,275 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-6341705</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-15836215</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-54776946</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-67052193</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-80905909</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 15,224 千)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>58278336</v>
+      </c>
+      <c r="E20" t="n">
         <v>21914657</v>
       </c>
-      <c r="E17" t="n">
-        <v>11649726</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="F20" t="n">
+        <v>92965129</v>
+      </c>
+      <c r="G20" t="n">
         <v>77741477</v>
       </c>
-      <c r="G17" t="n">
-        <v>63036168</v>
-      </c>
-      <c r="H17" t="n">
-        <v>151351231</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H20" t="n">
+        <v>120808124</v>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -478,19 +478,19 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
+        <v>6967092</v>
+      </c>
+      <c r="E2" t="n">
         <v>13059088</v>
       </c>
-      <c r="E2" t="n">
-        <v>7514271</v>
-      </c>
       <c r="F2" t="n">
+        <v>-12477026</v>
+      </c>
+      <c r="G2" t="n">
         <v>-13209452</v>
       </c>
-      <c r="G2" t="n">
-        <v>-17378308</v>
-      </c>
       <c r="H2" t="n">
-        <v>14063843</v>
+        <v>11142678</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,140 +501,140 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 25,614 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>179790</v>
+        <v>24948891</v>
       </c>
       <c r="E3" t="n">
-        <v>-4145877</v>
+        <v>15352374</v>
       </c>
       <c r="F3" t="n">
-        <v>-18859172</v>
+        <v>-34318230</v>
       </c>
       <c r="G3" t="n">
-        <v>-23928714</v>
+        <v>-59932421</v>
       </c>
       <c r="H3" t="n">
-        <v>-37692021</v>
+        <v>-10587419</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -23,767 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -15,985 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>15352374</v>
+        <v>23865979</v>
       </c>
       <c r="E4" t="n">
-        <v>4400649</v>
+        <v>64790795</v>
       </c>
       <c r="F4" t="n">
-        <v>-59932421</v>
+        <v>61320795</v>
       </c>
       <c r="G4" t="n">
-        <v>-36164965</v>
+        <v>77305516</v>
       </c>
       <c r="H4" t="n">
-        <v>-16248893</v>
+        <v>-86152186</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 13,441 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 27,214 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>64790795</v>
+        <v>51524775</v>
       </c>
       <c r="E5" t="n">
-        <v>52752728</v>
+        <v>52037033</v>
       </c>
       <c r="F5" t="n">
-        <v>77305516</v>
+        <v>-39458810</v>
       </c>
       <c r="G5" t="n">
-        <v>63864807</v>
+        <v>-66672899</v>
       </c>
       <c r="H5" t="n">
-        <v>-78040549</v>
+        <v>-93136771</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 14,767 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>43911841</v>
+        <v>195314</v>
       </c>
       <c r="E6" t="n">
-        <v>32916595</v>
+        <v>-388619</v>
       </c>
       <c r="F6" t="n">
-        <v>4138318</v>
+        <v>-9093289</v>
       </c>
       <c r="G6" t="n">
-        <v>-10628730</v>
+        <v>-8964305</v>
       </c>
       <c r="H6" t="n">
-        <v>-24753076</v>
+        <v>-13419408</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
@@ -653,19 +653,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
+        <v>6519383</v>
+      </c>
+      <c r="E7" t="n">
         <v>5905166</v>
       </c>
-      <c r="E7" t="n">
-        <v>4650760</v>
-      </c>
       <c r="F7" t="n">
+        <v>17968436</v>
+      </c>
+      <c r="G7" t="n">
         <v>12172514</v>
       </c>
-      <c r="G7" t="n">
-        <v>11464578</v>
-      </c>
       <c r="H7" t="n">
-        <v>-12287197</v>
+        <v>-10845328</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
+        <v>4360578</v>
+      </c>
+      <c r="E8" t="n">
         <v>5383841</v>
       </c>
-      <c r="E8" t="n">
-        <v>248399</v>
-      </c>
       <c r="F8" t="n">
+        <v>-6413522</v>
+      </c>
+      <c r="G8" t="n">
         <v>-8290413</v>
       </c>
-      <c r="G8" t="n">
-        <v>-12565968</v>
-      </c>
       <c r="H8" t="n">
-        <v>-11088474</v>
+        <v>-11301761</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -723,19 +723,19 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
+        <v>-14048823</v>
+      </c>
+      <c r="E9" t="n">
         <v>-12502716</v>
       </c>
-      <c r="E9" t="n">
-        <v>-14238175</v>
-      </c>
       <c r="F9" t="n">
+        <v>-31831378</v>
+      </c>
+      <c r="G9" t="n">
         <v>-26421193</v>
       </c>
-      <c r="G9" t="n">
-        <v>-22521282</v>
-      </c>
       <c r="H9" t="n">
-        <v>39226834</v>
+        <v>35722957</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -746,147 +746,147 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>324181</v>
+        <v>859211</v>
       </c>
       <c r="E10" t="n">
-        <v>2421578</v>
+        <v>419617</v>
       </c>
       <c r="F10" t="n">
-        <v>-7714710</v>
+        <v>188582</v>
       </c>
       <c r="G10" t="n">
-        <v>-7826694</v>
+        <v>-606924</v>
       </c>
       <c r="H10" t="n">
-        <v>-16034877</v>
+        <v>-15098448</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>52037033</v>
+        <v>159311</v>
       </c>
       <c r="E11" t="n">
-        <v>25853028</v>
+        <v>856344</v>
       </c>
       <c r="F11" t="n">
-        <v>-66672899</v>
+        <v>2052714</v>
       </c>
       <c r="G11" t="n">
-        <v>-72111831</v>
+        <v>2110317</v>
       </c>
       <c r="H11" t="n">
-        <v>-96478272</v>
+        <v>-10154672</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-650363</v>
+        <v>29767427</v>
       </c>
       <c r="E12" t="n">
-        <v>-603053</v>
+        <v>43911841</v>
       </c>
       <c r="F12" t="n">
-        <v>1289656</v>
+        <v>2469826</v>
       </c>
       <c r="G12" t="n">
-        <v>1524590</v>
+        <v>4138318</v>
       </c>
       <c r="H12" t="n">
-        <v>17494996</v>
+        <v>-30829518</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>419617</v>
+        <v>404853</v>
       </c>
       <c r="E13" t="n">
-        <v>-77573</v>
+        <v>366519</v>
       </c>
       <c r="F13" t="n">
-        <v>-606924</v>
+        <v>64004</v>
       </c>
       <c r="G13" t="n">
-        <v>-1072851</v>
+        <v>-19000</v>
       </c>
       <c r="H13" t="n">
-        <v>-15472352</v>
+        <v>-14339128</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,30 +898,30 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>188020</v>
+        <v>-66463</v>
       </c>
       <c r="E14" t="n">
-        <v>-53547</v>
+        <v>95567</v>
       </c>
       <c r="F14" t="n">
-        <v>-1055916</v>
+        <v>4676608</v>
       </c>
       <c r="G14" t="n">
-        <v>-1544958</v>
+        <v>5215486</v>
       </c>
       <c r="H14" t="n">
-        <v>-20066514</v>
+        <v>11461558</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,163 +933,163 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>366519</v>
+        <v>-271349</v>
       </c>
       <c r="E15" t="n">
-        <v>723683</v>
+        <v>-650363</v>
       </c>
       <c r="F15" t="n">
-        <v>-19000</v>
+        <v>901767</v>
       </c>
       <c r="G15" t="n">
-        <v>312925</v>
+        <v>1289656</v>
       </c>
       <c r="H15" t="n">
-        <v>-14536132</v>
+        <v>17476870</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>501246</v>
+        <v>705794</v>
       </c>
       <c r="E16" t="n">
-        <v>386236</v>
+        <v>188020</v>
       </c>
       <c r="F16" t="n">
-        <v>-5886855</v>
+        <v>-742013</v>
       </c>
       <c r="G16" t="n">
-        <v>-5896131</v>
+        <v>-1055916</v>
       </c>
       <c r="H16" t="n">
-        <v>-5653228</v>
+        <v>-19831429</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -10,298 千)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-33006598</v>
+        <v>653476</v>
       </c>
       <c r="E17" t="n">
-        <v>-39666288</v>
+        <v>501246</v>
       </c>
       <c r="F17" t="n">
-        <v>-156708020</v>
+        <v>-5636722</v>
       </c>
       <c r="G17" t="n">
-        <v>-146409636</v>
+        <v>-5886855</v>
       </c>
       <c r="H17" t="n">
-        <v>-155289027</v>
+        <v>-5505008</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11,798 千)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>16283869</v>
+        <v>1914258</v>
       </c>
       <c r="E18" t="n">
-        <v>20279222</v>
+        <v>2663833</v>
       </c>
       <c r="F18" t="n">
-        <v>65946637</v>
+        <v>-5508003</v>
       </c>
       <c r="G18" t="n">
-        <v>77744958</v>
+        <v>-4896851</v>
       </c>
       <c r="H18" t="n">
-        <v>146767536</v>
+        <v>4055250</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 12,275 千)</t>
+          <t>📈 20d 巨變(加碼 14,360 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-6341705</v>
+        <v>16270527</v>
       </c>
       <c r="E19" t="n">
-        <v>-15836215</v>
+        <v>16283869</v>
       </c>
       <c r="F19" t="n">
-        <v>-54776946</v>
+        <v>80306596</v>
       </c>
       <c r="G19" t="n">
-        <v>-67052193</v>
+        <v>65946637</v>
       </c>
       <c r="H19" t="n">
-        <v>-80905909</v>
+        <v>149222513</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
@@ -1101,26 +1101,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 15,224 千)</t>
+          <t>📈 20d 巨變(加碼 32,144 千)</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
+        <v>72174503</v>
+      </c>
+      <c r="E20" t="n">
         <v>58278336</v>
       </c>
-      <c r="E20" t="n">
-        <v>21914657</v>
-      </c>
       <c r="F20" t="n">
+        <v>125108814</v>
+      </c>
+      <c r="G20" t="n">
         <v>92965129</v>
       </c>
-      <c r="G20" t="n">
-        <v>77741477</v>
-      </c>
       <c r="H20" t="n">
-        <v>120808124</v>
+        <v>135127453</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,175 +466,175 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -21,044 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>6967092</v>
+        <v>-9013934</v>
       </c>
       <c r="E2" t="n">
-        <v>13059088</v>
+        <v>23865979</v>
       </c>
       <c r="F2" t="n">
-        <v>-12477026</v>
+        <v>40276522</v>
       </c>
       <c r="G2" t="n">
-        <v>-13209452</v>
+        <v>61320795</v>
       </c>
       <c r="H2" t="n">
-        <v>11142678</v>
+        <v>-99116719</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 25,614 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>24948891</v>
+        <v>-79285</v>
       </c>
       <c r="E3" t="n">
-        <v>15352374</v>
+        <v>6967092</v>
       </c>
       <c r="F3" t="n">
-        <v>-34318230</v>
+        <v>-16298266</v>
       </c>
       <c r="G3" t="n">
-        <v>-59932421</v>
+        <v>-12477026</v>
       </c>
       <c r="H3" t="n">
-        <v>-10587419</v>
+        <v>8215565</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -15,985 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -11,432 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>23865979</v>
+        <v>-26270154</v>
       </c>
       <c r="E4" t="n">
-        <v>64790795</v>
+        <v>-14048823</v>
       </c>
       <c r="F4" t="n">
-        <v>61320795</v>
+        <v>-43263508</v>
       </c>
       <c r="G4" t="n">
-        <v>77305516</v>
+        <v>-31831378</v>
       </c>
       <c r="H4" t="n">
-        <v>-86152186</v>
+        <v>23566844</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 27,214 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>51524775</v>
+        <v>105524</v>
       </c>
       <c r="E5" t="n">
-        <v>52037033</v>
+        <v>195314</v>
       </c>
       <c r="F5" t="n">
-        <v>-39458810</v>
+        <v>-7607240</v>
       </c>
       <c r="G5" t="n">
-        <v>-66672899</v>
+        <v>-9093289</v>
       </c>
       <c r="H5" t="n">
-        <v>-93136771</v>
+        <v>-13542968</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>195314</v>
+        <v>-1923575</v>
       </c>
       <c r="E6" t="n">
-        <v>-388619</v>
+        <v>-271349</v>
       </c>
       <c r="F6" t="n">
-        <v>-9093289</v>
+        <v>-624843</v>
       </c>
       <c r="G6" t="n">
-        <v>-8964305</v>
+        <v>901767</v>
       </c>
       <c r="H6" t="n">
-        <v>-13419408</v>
+        <v>15741145</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
@@ -653,19 +653,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
+        <v>7479751</v>
+      </c>
+      <c r="E7" t="n">
         <v>6519383</v>
       </c>
-      <c r="E7" t="n">
-        <v>5905166</v>
-      </c>
       <c r="F7" t="n">
+        <v>21342160</v>
+      </c>
+      <c r="G7" t="n">
         <v>17968436</v>
       </c>
-      <c r="G7" t="n">
-        <v>12172514</v>
-      </c>
       <c r="H7" t="n">
-        <v>-10845328</v>
+        <v>-8302780</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
+        <v>766882</v>
+      </c>
+      <c r="E8" t="n">
         <v>4360578</v>
       </c>
-      <c r="E8" t="n">
-        <v>5383841</v>
-      </c>
       <c r="F8" t="n">
+        <v>-9416557</v>
+      </c>
+      <c r="G8" t="n">
         <v>-6413522</v>
       </c>
-      <c r="G8" t="n">
-        <v>-8290413</v>
-      </c>
       <c r="H8" t="n">
-        <v>-11301761</v>
+        <v>-15126000</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -711,42 +711,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-14048823</v>
+        <v>17759683</v>
       </c>
       <c r="E9" t="n">
-        <v>-12502716</v>
+        <v>24948891</v>
       </c>
       <c r="F9" t="n">
-        <v>-31831378</v>
+        <v>-39974155</v>
       </c>
       <c r="G9" t="n">
-        <v>-26421193</v>
+        <v>-34318230</v>
       </c>
       <c r="H9" t="n">
-        <v>35722957</v>
+        <v>-13961752</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,30 +758,30 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>859211</v>
+        <v>-900988</v>
       </c>
       <c r="E10" t="n">
-        <v>419617</v>
+        <v>159311</v>
       </c>
       <c r="F10" t="n">
-        <v>188582</v>
+        <v>1411138</v>
       </c>
       <c r="G10" t="n">
-        <v>-606924</v>
+        <v>2052714</v>
       </c>
       <c r="H10" t="n">
-        <v>-15098448</v>
+        <v>-10893922</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,58 +793,58 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>159311</v>
+        <v>22615691</v>
       </c>
       <c r="E11" t="n">
-        <v>856344</v>
+        <v>29767427</v>
       </c>
       <c r="F11" t="n">
-        <v>2052714</v>
+        <v>3597120</v>
       </c>
       <c r="G11" t="n">
-        <v>2110317</v>
+        <v>2469826</v>
       </c>
       <c r="H11" t="n">
-        <v>-10154672</v>
+        <v>-33761534</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>29767427</v>
+        <v>17960068</v>
       </c>
       <c r="E12" t="n">
-        <v>43911841</v>
+        <v>51524775</v>
       </c>
       <c r="F12" t="n">
-        <v>2469826</v>
+        <v>-45942281</v>
       </c>
       <c r="G12" t="n">
-        <v>4138318</v>
+        <v>-39458810</v>
       </c>
       <c r="H12" t="n">
-        <v>-30829518</v>
+        <v>-96529198</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
@@ -863,19 +863,19 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
+        <v>523051</v>
+      </c>
+      <c r="E13" t="n">
         <v>404853</v>
       </c>
-      <c r="E13" t="n">
-        <v>366519</v>
-      </c>
       <c r="F13" t="n">
+        <v>487214</v>
+      </c>
+      <c r="G13" t="n">
         <v>64004</v>
       </c>
-      <c r="G13" t="n">
-        <v>-19000</v>
-      </c>
       <c r="H13" t="n">
-        <v>-14339128</v>
+        <v>-13986905</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -886,42 +886,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-66463</v>
+        <v>1353564</v>
       </c>
       <c r="E14" t="n">
-        <v>95567</v>
+        <v>-2498136</v>
       </c>
       <c r="F14" t="n">
-        <v>4676608</v>
+        <v>-5760257</v>
       </c>
       <c r="G14" t="n">
-        <v>5215486</v>
+        <v>-5911520</v>
       </c>
       <c r="H14" t="n">
-        <v>11461558</v>
+        <v>-1398917</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,196 +933,161 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-271349</v>
+        <v>-800070</v>
       </c>
       <c r="E15" t="n">
-        <v>-650363</v>
+        <v>-66463</v>
       </c>
       <c r="F15" t="n">
-        <v>901767</v>
+        <v>3361993</v>
       </c>
       <c r="G15" t="n">
-        <v>1289656</v>
+        <v>4676608</v>
       </c>
       <c r="H15" t="n">
-        <v>17476870</v>
+        <v>10888170</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>705794</v>
+        <v>2396262</v>
       </c>
       <c r="E16" t="n">
-        <v>188020</v>
+        <v>1914258</v>
       </c>
       <c r="F16" t="n">
-        <v>-742013</v>
+        <v>-5780470</v>
       </c>
       <c r="G16" t="n">
-        <v>-1055916</v>
+        <v>-5508003</v>
       </c>
       <c r="H16" t="n">
-        <v>-19831429</v>
+        <v>4583883</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>📉 20d 巨變(減碼 -8,163 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>653476</v>
+        <v>-19925720</v>
       </c>
       <c r="E17" t="n">
-        <v>501246</v>
+        <v>-11507214</v>
       </c>
       <c r="F17" t="n">
-        <v>-5636722</v>
+        <v>-45319194</v>
       </c>
       <c r="G17" t="n">
-        <v>-5886855</v>
+        <v>-37155770</v>
       </c>
       <c r="H17" t="n">
-        <v>-5505008</v>
+        <v>-61587654</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>📈 20d 巨變(加碼 8,353 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1914258</v>
+        <v>18982549</v>
       </c>
       <c r="E18" t="n">
-        <v>2663833</v>
+        <v>11450232</v>
       </c>
       <c r="F18" t="n">
-        <v>-5508003</v>
+        <v>69712230</v>
       </c>
       <c r="G18" t="n">
-        <v>-4896851</v>
+        <v>61358747</v>
       </c>
       <c r="H18" t="n">
-        <v>4055250</v>
+        <v>153510002</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14,360 千)</t>
+          <t>📉 20d 巨變(減碼 -10,577 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>16270527</v>
+        <v>57262044</v>
       </c>
       <c r="E19" t="n">
-        <v>16283869</v>
+        <v>72174503</v>
       </c>
       <c r="F19" t="n">
-        <v>80306596</v>
+        <v>114531813</v>
       </c>
       <c r="G19" t="n">
-        <v>65946637</v>
+        <v>125108814</v>
       </c>
       <c r="H19" t="n">
-        <v>149222513</v>
+        <v>131941200</v>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 32,144 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>72174503</v>
-      </c>
-      <c r="E20" t="n">
-        <v>58278336</v>
-      </c>
-      <c r="F20" t="n">
-        <v>125108814</v>
-      </c>
-      <c r="G20" t="n">
-        <v>92965129</v>
-      </c>
-      <c r="H20" t="n">
-        <v>135127453</v>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>
